--- a/docs/結合試験項目一覧.xlsx
+++ b/docs/結合試験項目一覧.xlsx
@@ -7,10 +7,10 @@
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="正常系（IF結合）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="異常系" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="トランザクション整合" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="結合シナリオ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="正常系（基本の動き）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="異常系（障害・不正入力）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="保存の整合性" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="通しシナリオ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -3873,15 +3873,15 @@
     <col width="3.33203125" customWidth="1" style="42" min="1" max="1"/>
     <col width="6.58203125" bestFit="1" customWidth="1" style="42" min="2" max="2"/>
     <col width="7.33203125" bestFit="1" customWidth="1" style="42" min="3" max="4"/>
-    <col width="18" customWidth="1" style="42" min="5" max="6"/>
+    <col width="16" customWidth="1" style="42" min="5" max="6"/>
     <col width="18" customWidth="1" style="53" min="6" max="6"/>
     <col width="33.83203125" customWidth="1" style="42" min="7" max="7"/>
     <col width="8.58203125" customWidth="1" style="42" min="8" max="8"/>
-    <col width="42" bestFit="1" customWidth="1" style="42" min="9" max="9"/>
+    <col width="46" bestFit="1" customWidth="1" style="42" min="9" max="9"/>
     <col width="49.33203125" bestFit="1" customWidth="1" style="42" min="10" max="10"/>
     <col width="75.9140625" customWidth="1" style="42" min="11" max="11"/>
     <col width="8.58203125" customWidth="1" style="42" min="12" max="12"/>
-    <col width="16" bestFit="1" customWidth="1" style="42" min="13" max="13"/>
+    <col width="13" bestFit="1" customWidth="1" style="42" min="13" max="13"/>
     <col width="11.75" bestFit="1" customWidth="1" style="42" min="14" max="14"/>
     <col width="8.58203125" customWidth="1" style="42" min="15" max="16"/>
     <col width="9.25" customWidth="1" style="42" min="17" max="17"/>
@@ -3892,7 +3892,7 @@
     <row r="1" ht="18" customHeight="1" s="53">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>●正常系（IF結合）</t>
+          <t>●正常系（基本の動き）</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="C3" s="21" t="inlineStr">
         <is>
-          <t>詳細設計書のIF（モジュール間・外部境界）ごとの正常結合の確認</t>
+          <t>基本の操作が、画面の表示どおりに動くことを確認する</t>
         </is>
       </c>
       <c r="D3" s="22" t="n"/>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C4" s="42" t="inlineStr">
         <is>
-          <t>シード投入済み。ローカルHTTPサーバ経由で起動（file:// 不可）</t>
+          <t>設定画面から「デモデータを投入」済み。起動はコマンド「python3 -m http.server 8010」→ブラウザで http://127.0.0.1:8010/ を開く（ファイルのダブルクリックでは開かない）</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>「自動」列＝tests/smoke.js・guard.js（CI）で毎回検証。初回とリリース判定時は手動でエビデンスを取得する</t>
+          <t>「自動＋手動」の行は自動テストでも毎回検証済み（手動では見た目と操作感を確認する）。IF・参考資料列はレビュー用の対応記号なので、実施時は気にしなくてよい</t>
         </is>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30.4" customHeight="1" s="53">
+    <row r="9" ht="43.59999999999999" customHeight="1" s="53">
       <c r="B9" s="8" t="n">
         <v>1</v>
       </c>
@@ -4061,17 +4061,17 @@
       </c>
       <c r="E9" s="56" t="inlineStr">
         <is>
-          <t>S-7 申込フォーム</t>
+          <t>参加者の申込</t>
         </is>
       </c>
       <c r="F9" s="56" t="inlineStr">
         <is>
-          <t>申込確定</t>
+          <t>申込フォーム</t>
         </is>
       </c>
       <c r="G9" s="56" t="inlineStr">
         <is>
-          <t>申込むボタン</t>
+          <t>「申込む」ボタン</t>
         </is>
       </c>
       <c r="H9" s="57" t="inlineStr">
@@ -4081,17 +4081,17 @@
       </c>
       <c r="I9" s="56" t="inlineStr">
         <is>
-          <t>入力→確認→申込む</t>
+          <t>参加者ビューで受付中のイベントを開き「申込む」→氏名・カナ・メールを入力→「確認へ進む」→内容を確かめて「申込む」</t>
         </is>
       </c>
       <c r="J9" s="56" t="inlineStr">
         <is>
-          <t>公開中・受付中・残席あり</t>
+          <t>受付中で残席があるイベント</t>
         </is>
       </c>
       <c r="K9" s="56" t="inlineStr">
         <is>
-          <t>persons / applications / savedTokens が各1件増え、token が3者で一致する。完了画面に確認URLが出る</t>
+          <t>「申込が完了しました」の画面になり、確認用URLが表示される。主催者ビューの申込一覧に1件増え、残席が1減る。マイ申込にも表示される</t>
         </is>
       </c>
       <c r="L9" s="57" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="M9" s="56" t="inlineStr">
         <is>
-          <t>IT-01・F-16〜19</t>
+          <t>IT-01</t>
         </is>
       </c>
       <c r="N9" s="57" t="n"/>
@@ -4126,17 +4126,17 @@
       </c>
       <c r="E10" s="56" t="inlineStr">
         <is>
-          <t>S-4 申込タブ</t>
+          <t>当日受付</t>
         </is>
       </c>
       <c r="F10" s="56" t="inlineStr">
         <is>
-          <t>チェックイン</t>
+          <t>申込一覧</t>
         </is>
       </c>
       <c r="G10" s="56" t="inlineStr">
         <is>
-          <t>行内ボタン</t>
+          <t>「チェックイン」ボタン</t>
         </is>
       </c>
       <c r="H10" s="57" t="inlineStr">
@@ -4146,13 +4146,13 @@
       </c>
       <c r="I10" s="56" t="inlineStr">
         <is>
-          <t>チェックイン→受付取消</t>
+          <t>イベント詳細の「申込」タブで対象者の「チェックイン」を押す→続けて「受付取消」を押す</t>
         </is>
       </c>
       <c r="J10" s="56" t="inlineStr"/>
       <c r="K10" s="56" t="inlineStr">
         <is>
-          <t>status・checkinAt が更新され、一覧と固定表示の残席・受付数が追随する。トースト表示</t>
+          <t>状態が「チェックイン済」に変わり、画面上部の受付数・残席の表示も追いかけて変わる。取り消すと元に戻る。右下に完了メッセージが出る</t>
         </is>
       </c>
       <c r="L10" s="57" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="M10" s="56" t="inlineStr">
         <is>
-          <t>IT-02・F-24</t>
+          <t>IT-02</t>
         </is>
       </c>
       <c r="N10" s="57" t="n"/>
@@ -4187,17 +4187,17 @@
       </c>
       <c r="E11" s="56" t="inlineStr">
         <is>
-          <t>S-9 マイ申込</t>
+          <t>参加者の申込</t>
         </is>
       </c>
       <c r="F11" s="56" t="inlineStr">
         <is>
-          <t>キャンセル</t>
+          <t>キャンセルと再申込</t>
         </is>
       </c>
       <c r="G11" s="56" t="inlineStr">
         <is>
-          <t>キャンセルボタン</t>
+          <t>「申込をキャンセル」</t>
         </is>
       </c>
       <c r="H11" s="57" t="inlineStr">
@@ -4207,17 +4207,17 @@
       </c>
       <c r="I11" s="56" t="inlineStr">
         <is>
-          <t>キャンセル→同一人物で再申込</t>
+          <t>マイ申込の詳細で「申込をキャンセル」→確認→同じ人がもう一度同じイベントに申込む</t>
         </is>
       </c>
       <c r="J11" s="56" t="inlineStr">
         <is>
-          <t>有効な申込がある状態</t>
+          <t>申込済みの人がいる状態</t>
         </is>
       </c>
       <c r="K11" s="56" t="inlineStr">
         <is>
-          <t>残席が1回復する。再申込は新レコードで成功し、旧レコードは cancelled のまま残る</t>
+          <t>キャンセルすると残席が1増える。もう一度の申込は問題なく成功する。主催者の一覧には、キャンセルした記録も残ったまま新しい申込が増える</t>
         </is>
       </c>
       <c r="L11" s="57" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="M11" s="56" t="inlineStr">
         <is>
-          <t>IT-03・F-25/F-42</t>
+          <t>IT-03</t>
         </is>
       </c>
       <c r="N11" s="57" t="n"/>
@@ -4252,17 +4252,17 @@
       </c>
       <c r="E12" s="56" t="inlineStr">
         <is>
-          <t>S-4 申込タブ</t>
+          <t>当日受付</t>
         </is>
       </c>
       <c r="F12" s="56" t="inlineStr">
         <is>
-          <t>内容修正</t>
+          <t>申込内容の修正</t>
         </is>
       </c>
       <c r="G12" s="56" t="inlineStr">
         <is>
-          <t>修正モーダル</t>
+          <t>「内容を修正」</t>
         </is>
       </c>
       <c r="H12" s="57" t="inlineStr">
@@ -4272,13 +4272,17 @@
       </c>
       <c r="I12" s="56" t="inlineStr">
         <is>
-          <t>複数申込を持つ人の氏名・メールを修正</t>
-        </is>
-      </c>
-      <c r="J12" s="56" t="inlineStr"/>
+          <t>申込一覧で行をクリックして開き「内容を修正」→氏名とメールアドレスを変えて保存</t>
+        </is>
+      </c>
+      <c r="J12" s="56" t="inlineStr">
+        <is>
+          <t>同じ人が複数のイベントに申込んでいる状態</t>
+        </is>
+      </c>
       <c r="K12" s="56" t="inlineStr">
         <is>
-          <t>persons 更新と当人の全申込の searchText 再計算が同時に行われ、修正後の氏名で検索がヒットする</t>
+          <t>修正が保存され、同じ人の別イベントの申込にも新しい氏名が反映される。新しい氏名で検索するとヒットする</t>
         </is>
       </c>
       <c r="L12" s="57" t="inlineStr">
@@ -4288,7 +4292,7 @@
       </c>
       <c r="M12" s="56" t="inlineStr">
         <is>
-          <t>IT-04・F-26</t>
+          <t>IT-04</t>
         </is>
       </c>
       <c r="N12" s="57" t="n"/>
@@ -4313,17 +4317,17 @@
       </c>
       <c r="E13" s="56" t="inlineStr">
         <is>
-          <t>S-6 公開ページ</t>
+          <t>公開ページ</t>
         </is>
       </c>
       <c r="F13" s="56" t="inlineStr">
         <is>
-          <t>時期表示</t>
+          <t>申込ボタンの文言</t>
         </is>
       </c>
       <c r="G13" s="56" t="inlineStr">
         <is>
-          <t>申込ボタン</t>
+          <t>時期による切替</t>
         </is>
       </c>
       <c r="H13" s="57" t="inlineStr">
@@ -4333,17 +4337,17 @@
       </c>
       <c r="I13" s="56" t="inlineStr">
         <is>
-          <t>5状態のイベントの公開ページを開く</t>
+          <t>中止・開催済・受付終了・受付前・受付中の5つのイベントの公開ページをそれぞれ開く</t>
         </is>
       </c>
       <c r="J13" s="56" t="inlineStr">
         <is>
-          <t>中止・開催済・受付終了・受付前・受付中</t>
+          <t>デモデータに各状態のイベントあり</t>
         </is>
       </c>
       <c r="K13" s="56" t="inlineStr">
         <is>
-          <t>Domain.timing の評価順どおりの表示。ボタン文言・活性が applyButtonLabel に一致する</t>
+          <t>ボタンが順に「中止されました」「終了しました」「受付終了」「〇/〇 から受付開始」「申込む」になり、押せるのは受付中だけ</t>
         </is>
       </c>
       <c r="L13" s="57" t="inlineStr">
@@ -4353,7 +4357,7 @@
       </c>
       <c r="M13" s="56" t="inlineStr">
         <is>
-          <t>IT-05・F-05/F-08</t>
+          <t>IT-05</t>
         </is>
       </c>
       <c r="N13" s="57" t="n"/>
@@ -4366,7 +4370,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="30.4" customHeight="1" s="53">
+    <row r="14" ht="56.8" customHeight="1" s="53">
       <c r="B14" s="8" t="n">
         <v>1</v>
       </c>
@@ -4378,17 +4382,17 @@
       </c>
       <c r="E14" s="56" t="inlineStr">
         <is>
-          <t>S-3 ウィザード</t>
+          <t>イベント作成</t>
         </is>
       </c>
       <c r="F14" s="56" t="inlineStr">
         <is>
-          <t>保存</t>
+          <t>保存と公開</t>
         </is>
       </c>
       <c r="G14" s="56" t="inlineStr">
         <is>
-          <t>保存して次へ</t>
+          <t>「保存して次へ」「公開する」</t>
         </is>
       </c>
       <c r="H14" s="57" t="inlineStr">
@@ -4398,17 +4402,13 @@
       </c>
       <c r="I14" s="56" t="inlineStr">
         <is>
-          <t>各ステップ保存→公開</t>
-        </is>
-      </c>
-      <c r="J14" s="56" t="inlineStr">
-        <is>
-          <t>タイトル空／公開済みで公開範囲を後退</t>
-        </is>
-      </c>
+          <t>①イベント名を空のまま「保存して次へ」 ②公開済みイベントの編集で公開範囲を「限定公開」に変えて保存 ③締切を開催日より後にして「公開前チェック」</t>
+        </is>
+      </c>
+      <c r="J14" s="56" t="inlineStr"/>
       <c r="K14" s="56" t="inlineStr">
         <is>
-          <t>タイトル空はフィールド直下エラー。公開済みの一般公開→限定公開は拒否（下書きは自由）。締切&gt;開催日は検出。公開時は確認モーダル</t>
+          <t>①名前の欄の下にエラーが出る ②「一般公開から限定公開へは戻せません」と拒否される（下書きの間は変えられる） ③締切の矛盾が検出される。公開時には確認画面が出る</t>
         </is>
       </c>
       <c r="L14" s="57" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="M14" s="56" t="inlineStr">
         <is>
-          <t>IT-06・F-66/F-06</t>
+          <t>IT-06</t>
         </is>
       </c>
       <c r="N14" s="57" t="n"/>
@@ -4443,12 +4443,12 @@
       </c>
       <c r="E15" s="56" t="inlineStr">
         <is>
-          <t>S-3 ウィザード</t>
+          <t>イベント作成</t>
         </is>
       </c>
       <c r="F15" s="56" t="inlineStr">
         <is>
-          <t>定員変更</t>
+          <t>定員の変更</t>
         </is>
       </c>
       <c r="G15" s="56" t="inlineStr">
@@ -4463,13 +4463,13 @@
       </c>
       <c r="I15" s="56" t="inlineStr">
         <is>
-          <t>有効申込5件のイベントで定員を4に変更して保存</t>
+          <t>申込が5件入っているイベントの定員を4に変えて保存</t>
         </is>
       </c>
       <c r="J15" s="56" t="inlineStr"/>
       <c r="K15" s="56" t="inlineStr">
         <is>
-          <t>エラーバナーで拒否され、events は更新されない</t>
+          <t>「定員を4人にはできません。すでに5件の有効な申込があります」のエラーが出て、保存されない</t>
         </is>
       </c>
       <c r="L15" s="57" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="M15" s="56" t="inlineStr">
         <is>
-          <t>IT-07・F-41</t>
+          <t>IT-07</t>
         </is>
       </c>
       <c r="N15" s="57" t="n"/>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="E16" s="56" t="inlineStr">
         <is>
-          <t>S-4 概要・編集</t>
+          <t>イベント詳細</t>
         </is>
       </c>
       <c r="F16" s="56" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="G16" s="56" t="inlineStr">
         <is>
-          <t>複製ボタン</t>
+          <t>「複製」ボタン</t>
         </is>
       </c>
       <c r="H16" s="57" t="inlineStr">
@@ -4524,13 +4524,13 @@
       </c>
       <c r="I16" s="56" t="inlineStr">
         <is>
-          <t>複製を実行</t>
+          <t>「概要・編集」タブで「複製」→確認画面で「複製する」</t>
         </is>
       </c>
       <c r="J16" s="56" t="inlineStr"/>
       <c r="K16" s="56" t="inlineStr">
         <is>
-          <t>下書きが生成され copiedFromId に元イベントを記録。申込・お知らせ・運営タスクは複製されない</t>
+          <t>「（コピー）」付きの下書きイベントが作られる。申込・お知らせ・運営タスクはコピーされない</t>
         </is>
       </c>
       <c r="L16" s="57" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="M16" s="56" t="inlineStr">
         <is>
-          <t>IT-08・F-94</t>
+          <t>IT-08</t>
         </is>
       </c>
       <c r="N16" s="57" t="n"/>
@@ -4565,12 +4565,12 @@
       </c>
       <c r="E17" s="56" t="inlineStr">
         <is>
-          <t>S-4 運営スレッド</t>
+          <t>運営スレッド</t>
         </is>
       </c>
       <c r="F17" s="56" t="inlineStr">
         <is>
-          <t>未読</t>
+          <t>未読の表示</t>
         </is>
       </c>
       <c r="G17" s="56" t="inlineStr">
@@ -4585,13 +4585,13 @@
       </c>
       <c r="I17" s="56" t="inlineStr">
         <is>
-          <t>イベントAで投稿→Bを開く→Aを再度開く</t>
+          <t>イベントAのスレッドに投稿→イベントBを開く→一覧に戻る→Aをもう一度開く</t>
         </is>
       </c>
       <c r="J17" s="56" t="inlineStr"/>
       <c r="K17" s="56" t="inlineStr">
         <is>
-          <t>未読は readStates（eventId:channel）との突合で算出。開くと既読化しバッジが消える。別イベントと混ざらない</t>
+          <t>Aの一覧カードとスレッドタブに未読の件数が付き、Bには付かない。スレッドを開くと件数が消え、以降の新しい投稿だけがまた未読になる</t>
         </is>
       </c>
       <c r="L17" s="57" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="M17" s="56" t="inlineStr">
         <is>
-          <t>IT-09・F-79c</t>
+          <t>IT-09</t>
         </is>
       </c>
       <c r="N17" s="57" t="n"/>
@@ -4626,17 +4626,17 @@
       </c>
       <c r="E18" s="56" t="inlineStr">
         <is>
-          <t>S-4 運営Q&amp;A</t>
+          <t>運営Q&amp;A</t>
         </is>
       </c>
       <c r="F18" s="56" t="inlineStr">
         <is>
-          <t>解消</t>
+          <t>疑問の解消</t>
         </is>
       </c>
       <c r="G18" s="56" t="inlineStr">
         <is>
-          <t>解決にするボタン</t>
+          <t>「解決にする」</t>
         </is>
       </c>
       <c r="H18" s="57" t="inlineStr">
@@ -4646,13 +4646,13 @@
       </c>
       <c r="I18" s="56" t="inlineStr">
         <is>
-          <t>疑問を登録→回答→解消</t>
+          <t>疑問を登録→回答を書いて「解決にする」</t>
         </is>
       </c>
       <c r="J18" s="56" t="inlineStr"/>
       <c r="K18" s="56" t="inlineStr">
         <is>
-          <t>resolved が更新され、未解決件数が一覧カード・要対応から消える</t>
+          <t>「解決済み」の表示に変わり、イベント一覧カードの「未解決Q&amp;A」の数が減る</t>
         </is>
       </c>
       <c r="L18" s="57" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="M18" s="56" t="inlineStr">
         <is>
-          <t>IT-10・E-1</t>
+          <t>IT-10</t>
         </is>
       </c>
       <c r="N18" s="57" t="n"/>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1" s="53">
+    <row r="19" ht="30.4" customHeight="1" s="53">
       <c r="B19" s="8" t="n">
         <v>1</v>
       </c>
@@ -4687,17 +4687,17 @@
       </c>
       <c r="E19" s="56" t="inlineStr">
         <is>
-          <t>S-4 お知らせ</t>
+          <t>お知らせ</t>
         </is>
       </c>
       <c r="F19" s="56" t="inlineStr">
         <is>
-          <t>掲示</t>
+          <t>参加者への掲示</t>
         </is>
       </c>
       <c r="G19" s="56" t="inlineStr">
         <is>
-          <t>お知らせを出す</t>
+          <t>「お知らせを出す」</t>
         </is>
       </c>
       <c r="H19" s="57" t="inlineStr">
@@ -4707,13 +4707,13 @@
       </c>
       <c r="I19" s="56" t="inlineStr">
         <is>
-          <t>投稿→参加者ビューで確認</t>
+          <t>「お知らせ」タブで件名を入れて「お知らせを出す」→参加者ビューで公開ページとマイ申込を見る</t>
         </is>
       </c>
       <c r="J19" s="56" t="inlineStr"/>
       <c r="K19" s="56" t="inlineStr">
         <is>
-          <t>公開ページとマイ申込に掲示される。運営スレッド・Q&amp;Aは参加者ビューに出ない</t>
+          <t>両方の画面に掲示される。逆に、運営スレッド・Q&amp;A・タスクは参加者からは一切見えない</t>
         </is>
       </c>
       <c r="L19" s="57" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="M19" s="56" t="inlineStr">
         <is>
-          <t>IT-11・E-4</t>
+          <t>IT-11</t>
         </is>
       </c>
       <c r="N19" s="57" t="n"/>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="30.4" customHeight="1" s="53">
+    <row r="20" ht="43.59999999999999" customHeight="1" s="53">
       <c r="B20" s="8" t="n">
         <v>1</v>
       </c>
@@ -4748,17 +4748,17 @@
       </c>
       <c r="E20" s="56" t="inlineStr">
         <is>
-          <t>S-4 運営タスク</t>
+          <t>運営タスク</t>
         </is>
       </c>
       <c r="F20" s="56" t="inlineStr">
         <is>
-          <t>進捗の伝播</t>
+          <t>ボードとタイムライン</t>
         </is>
       </c>
       <c r="G20" s="56" t="inlineStr">
         <is>
-          <t>ボード／タイムライン</t>
+          <t>ドラッグ操作</t>
         </is>
       </c>
       <c r="H20" s="57" t="inlineStr">
@@ -4768,13 +4768,13 @@
       </c>
       <c r="I20" s="56" t="inlineStr">
         <is>
-          <t>タスク作成→ボードでドラッグ→リロード</t>
+          <t>タスクを追加→ボードでカードを別の列へドラッグ→ページを再読み込み→「タイムライン」表示に切替</t>
         </is>
       </c>
       <c r="J20" s="56" t="inlineStr"/>
       <c r="K20" s="56" t="inlineStr">
         <is>
-          <t>状態4段が遷移し order が10刻みで保存されリロード後も順序保持。S-4チップ・一覧カードの進捗バー・ダッシュボードに反映</t>
+          <t>ドラッグで状態が変わりそのまま保存される。再読み込みしても並び順が保たれる。上部の進捗表示、イベント一覧の「準備」バーにも反映される</t>
         </is>
       </c>
       <c r="L20" s="57" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="M20" s="56" t="inlineStr">
         <is>
-          <t>IT-12・E-2</t>
+          <t>IT-12</t>
         </is>
       </c>
       <c r="N20" s="57" t="n"/>
@@ -4809,12 +4809,12 @@
       </c>
       <c r="E21" s="56" t="inlineStr">
         <is>
-          <t>S-4 マニュアル</t>
+          <t>マニュアル</t>
         </is>
       </c>
       <c r="F21" s="56" t="inlineStr">
         <is>
-          <t>3ビュー</t>
+          <t>3つの表示</t>
         </is>
       </c>
       <c r="G21" s="56" t="inlineStr">
@@ -4829,17 +4829,13 @@
       </c>
       <c r="I21" s="56" t="inlineStr">
         <is>
-          <t>見出し・表・引用・リンクを含む本文で切替</t>
-        </is>
-      </c>
-      <c r="J21" s="56" t="inlineStr">
-        <is>
-          <t>本文あり</t>
-        </is>
-      </c>
+          <t>見出し・表・箇条書き・リンクを含む本文を書いて保存→編集・分割・プレビューを切り替える</t>
+        </is>
+      </c>
+      <c r="J21" s="56" t="inlineStr"/>
       <c r="K21" s="56" t="inlineStr">
         <is>
-          <t>自前 Util.markdown で描画され、本文があれば次回はプレビューで開く。分割ビューで入力中にカーソルが飛ばない</t>
+          <t>整形されて読みやすく表示される。本文があるときは次からプレビューで開く。分割表示で入力中に文字カーソルが先頭へ飛ばない</t>
         </is>
       </c>
       <c r="L21" s="57" t="inlineStr">
@@ -4849,7 +4845,7 @@
       </c>
       <c r="M21" s="56" t="inlineStr">
         <is>
-          <t>IT-13・F-99</t>
+          <t>IT-13</t>
         </is>
       </c>
       <c r="N21" s="57" t="n"/>
@@ -4874,12 +4870,12 @@
       </c>
       <c r="E22" s="56" t="inlineStr">
         <is>
-          <t>S-4 ファイル</t>
+          <t>ファイル共有</t>
         </is>
       </c>
       <c r="F22" s="56" t="inlineStr">
         <is>
-          <t>Blobの往復</t>
+          <t>追加と取り出し</t>
         </is>
       </c>
       <c r="G22" s="56" t="inlineStr">
@@ -4894,17 +4890,13 @@
       </c>
       <c r="I22" s="56" t="inlineStr">
         <is>
-          <t>画像・PDFを追加→一覧→ダウンロード→削除</t>
-        </is>
-      </c>
-      <c r="J22" s="56" t="inlineStr">
-        <is>
-          <t>R-02のため手動必須</t>
-        </is>
-      </c>
+          <t>画像とPDFを追加→一覧からダウンロード→削除</t>
+        </is>
+      </c>
+      <c r="J22" s="56" t="inlineStr"/>
       <c r="K22" s="56" t="inlineStr">
         <is>
-          <t>Blob がそのまま保存され、再取得して開ける。一覧の名前・サイズ・種別は Blob 非依存で表示される</t>
+          <t>追加したファイルが名前・サイズつきで一覧に出る。ダウンロードすると元と同じ内容で開ける。削除は確認のうえで消える</t>
         </is>
       </c>
       <c r="L22" s="57" t="inlineStr">
@@ -4914,7 +4906,7 @@
       </c>
       <c r="M22" s="56" t="inlineStr">
         <is>
-          <t>IT-14・F-102</t>
+          <t>IT-14</t>
         </is>
       </c>
       <c r="N22" s="57" t="n"/>
@@ -4927,7 +4919,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="30.4" customHeight="1" s="53">
+    <row r="23" ht="43.59999999999999" customHeight="1" s="53">
       <c r="B23" s="8" t="n">
         <v>1</v>
       </c>
@@ -4939,7 +4931,7 @@
       </c>
       <c r="E23" s="56" t="inlineStr">
         <is>
-          <t>S-10 参加者名簿</t>
+          <t>参加者名簿</t>
         </is>
       </c>
       <c r="F23" s="56" t="inlineStr">
@@ -4959,13 +4951,13 @@
       </c>
       <c r="I23" s="56" t="inlineStr">
         <is>
-          <t>admin で解除→横断集計→参加者ビューへ切替</t>
+          <t>「参加者」タブ→パスワード「admin」で解除→人数・参加回数を確認→参加者ビューへ切替→主催者ビューに戻る</t>
         </is>
       </c>
       <c r="J23" s="56" t="inlineStr"/>
       <c r="K23" s="56" t="inlineStr">
         <is>
-          <t>合計申込・来場回数・最終申込日が実データと一致。ビュー切替でロックが復帰。保護の限界の注記が表示されている</t>
+          <t>参加回数・来場回数・最終申込日が実際の申込と合っている。ビューを切り替えると再びロックされる。「この保護の限界」の説明文が画面に出ている</t>
         </is>
       </c>
       <c r="L23" s="57" t="inlineStr">
@@ -4975,7 +4967,7 @@
       </c>
       <c r="M23" s="56" t="inlineStr">
         <is>
-          <t>IT-15・F-92/F-101</t>
+          <t>IT-15</t>
         </is>
       </c>
       <c r="N23" s="57" t="n"/>
@@ -5000,12 +4992,12 @@
       </c>
       <c r="E24" s="56" t="inlineStr">
         <is>
-          <t>S-1 ダッシュボード</t>
+          <t>ダッシュボード</t>
         </is>
       </c>
       <c r="F24" s="56" t="inlineStr">
         <is>
-          <t>集計</t>
+          <t>全体の集計</t>
         </is>
       </c>
       <c r="G24" s="56" t="inlineStr">
@@ -5020,13 +5012,13 @@
       </c>
       <c r="I24" s="56" t="inlineStr">
         <is>
-          <t>シード投入後に表示</t>
+          <t>デモデータ投入後にダッシュボードを表示する</t>
         </is>
       </c>
       <c r="J24" s="56" t="inlineStr"/>
       <c r="K24" s="56" t="inlineStr">
         <is>
-          <t>要対応の対象は本日・明日開催／満席・定員間近／下書き放置で、次の行動と残作業（期限超過・未対応タスク・未解決Q&amp;A）を添える。未読はイベント一覧カード側。ヒートマップは中止イベント除外・キャンセル含む</t>
+          <t>要対応リストには「本日／明日開催・満席・定員間近・放置中の下書き」が出て、それぞれ「次に何をするか」が書いてある。ヒートマップは中止イベントの申込を数えない。カレンダーに開催日の帯が出てクリックで詳細へ飛べる</t>
         </is>
       </c>
       <c r="L24" s="57" t="inlineStr">
@@ -5036,7 +5028,7 @@
       </c>
       <c r="M24" s="56" t="inlineStr">
         <is>
-          <t>IT-16・F-30/31/31b/103/100</t>
+          <t>IT-16</t>
         </is>
       </c>
       <c r="N24" s="57" t="n"/>
@@ -5049,7 +5041,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="30.4" customHeight="1" s="53">
+    <row r="25" ht="43.59999999999999" customHeight="1" s="53">
       <c r="B25" s="8" t="n">
         <v>1</v>
       </c>
@@ -5066,12 +5058,12 @@
       </c>
       <c r="F25" s="56" t="inlineStr">
         <is>
-          <t>URL復帰</t>
+          <t>URLから開く</t>
         </is>
       </c>
       <c r="G25" s="56" t="inlineStr">
         <is>
-          <t>?ticket= / ?event= / ?preview=</t>
+          <t>3種類のURL</t>
         </is>
       </c>
       <c r="H25" s="57" t="inlineStr">
@@ -5081,17 +5073,17 @@
       </c>
       <c r="I25" s="56" t="inlineStr">
         <is>
-          <t>3種のURLを直接開く</t>
+          <t>確認用URL（?ticket=…）・イベントURL（?event=…）・プレビューURL（?preview=…）をアドレスバーに直接入力して開く</t>
         </is>
       </c>
       <c r="J25" s="56" t="inlineStr">
         <is>
-          <t>正常値</t>
+          <t>正しいURLを使用</t>
         </is>
       </c>
       <c r="K25" s="56" t="inlineStr">
         <is>
-          <t>S-9詳細／S-6／プレビューへ遷移。?ticket= は控えを作成。URLは解析直後に戻り、再読込で二重処理しない</t>
+          <t>順に、申込の詳細／公開ページ／下書きのプレビューが開く。アドレスバーのURLはすぐ元に戻り、その場で再読み込みしても同じ処理が二重に走らない</t>
         </is>
       </c>
       <c r="L25" s="57" t="inlineStr">
@@ -5101,7 +5093,7 @@
       </c>
       <c r="M25" s="56" t="inlineStr">
         <is>
-          <t>IT-17・F-97</t>
+          <t>IT-17</t>
         </is>
       </c>
       <c r="N25" s="57" t="n"/>
@@ -5114,7 +5106,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="30.4" customHeight="1" s="53">
+    <row r="26" ht="43.59999999999999" customHeight="1" s="53">
       <c r="B26" s="8" t="n">
         <v>1</v>
       </c>
@@ -5126,12 +5118,12 @@
       </c>
       <c r="E26" s="56" t="inlineStr">
         <is>
-          <t>S-4 告知</t>
+          <t>告知</t>
         </is>
       </c>
       <c r="F26" s="56" t="inlineStr">
         <is>
-          <t>共有</t>
+          <t>共有とリンク</t>
         </is>
       </c>
       <c r="G26" s="56" t="inlineStr">
@@ -5146,13 +5138,13 @@
       </c>
       <c r="I26" s="56" t="inlineStr">
         <is>
-          <t>URL・投稿文をコピー。X／LINE／地図／ロゴを押す</t>
+          <t>「告知」タブでURLと投稿文をコピー→メモ帳に貼り付けて確認→「Xで共有」「LINEで共有」、公開ページの「地図を開く」、左上の会社ロゴを押す</t>
         </is>
       </c>
       <c r="J26" s="56" t="inlineStr"/>
       <c r="K26" s="56" t="inlineStr">
         <is>
-          <t>クリップボードに正しく入る。外部リンクは新しいタブ（rel=noopener）で正しい先が開く</t>
+          <t>コピーした文字が正しく貼り付けられる。各リンクはすべて新しいタブで、正しいページ（投稿画面・地図・会社サイト）が開く</t>
         </is>
       </c>
       <c r="L26" s="57" t="inlineStr">
@@ -5162,7 +5154,7 @@
       </c>
       <c r="M26" s="56" t="inlineStr">
         <is>
-          <t>IT-18・F-10〜15</t>
+          <t>IT-18</t>
         </is>
       </c>
       <c r="N26" s="57" t="n"/>
@@ -5187,12 +5179,12 @@
       </c>
       <c r="E27" s="56" t="inlineStr">
         <is>
-          <t>S-9→S-4</t>
+          <t>当日受付</t>
         </is>
       </c>
       <c r="F27" s="56" t="inlineStr">
         <is>
-          <t>QR受付</t>
+          <t>QRでの受付</t>
         </is>
       </c>
       <c r="G27" s="56" t="inlineStr">
@@ -5207,17 +5199,17 @@
       </c>
       <c r="I27" s="56" t="inlineStr">
         <is>
-          <t>マイ申込のQRを表示→受付画面で読取</t>
+          <t>マイ申込で「QRを表示」→主催者ビューの申込タブで「QRで受付」→カメラに画面のQRをかざす</t>
         </is>
       </c>
       <c r="J27" s="56" t="inlineStr">
         <is>
-          <t>カメラ許可</t>
+          <t>カメラ付き端末・カメラ許可</t>
         </is>
       </c>
       <c r="K27" s="56" t="inlineStr">
         <is>
-          <t>同梱ライブラリ生成のQRが jsQR で読め、氏名検索受付と同じ setCheckin に合流する</t>
+          <t>読み取ると「〇〇さんを受付しました」と出て、申込一覧の状態がチェックイン済みに変わる（氏名検索での受付と同じ結果になる）</t>
         </is>
       </c>
       <c r="L27" s="57" t="inlineStr">
@@ -5227,7 +5219,7 @@
       </c>
       <c r="M27" s="56" t="inlineStr">
         <is>
-          <t>IT-19・F-95</t>
+          <t>IT-19</t>
         </is>
       </c>
       <c r="N27" s="57" t="n"/>
@@ -5240,7 +5232,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="30.4" customHeight="1" s="53">
+    <row r="28" ht="43.59999999999999" customHeight="1" s="53">
       <c r="B28" s="8" t="n">
         <v>1</v>
       </c>
@@ -5252,7 +5244,7 @@
       </c>
       <c r="E28" s="56" t="inlineStr">
         <is>
-          <t>S-9 マイ申込</t>
+          <t>マイ申込</t>
         </is>
       </c>
       <c r="F28" s="56" t="inlineStr">
@@ -5272,13 +5264,17 @@
       </c>
       <c r="I28" s="56" t="inlineStr">
         <is>
-          <t>abc@example.com / abc123 でログイン→一覧→ログアウト</t>
-        </is>
-      </c>
-      <c r="J28" s="56" t="inlineStr"/>
+          <t>参加者ビューで「マイ申込」→「abc@example.com」「abc123」でログイン→一覧を見る→ログアウト</t>
+        </is>
+      </c>
+      <c r="J28" s="56" t="inlineStr">
+        <is>
+          <t>デモデータ投入済み</t>
+        </is>
+      </c>
       <c r="K28" s="56" t="inlineStr">
         <is>
-          <t>一覧は personId 起点で別人の申込が並ばない。状態はセッション内のみ。主催者ビューへ戻るとログアウトする</t>
+          <t>本人（田中 太郎）の申込だけが並び、他の人の申込は出ない。ログアウト・再読み込み・主催者ビューへの切替のどれでもログイン状態は消える</t>
         </is>
       </c>
       <c r="L28" s="57" t="inlineStr">
@@ -5288,7 +5284,7 @@
       </c>
       <c r="M28" s="56" t="inlineStr">
         <is>
-          <t>IT-20・F-107</t>
+          <t>IT-20</t>
         </is>
       </c>
       <c r="N28" s="57" t="n"/>
@@ -5301,7 +5297,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="30.4" customHeight="1" s="53">
+    <row r="29" ht="43.59999999999999" customHeight="1" s="53">
       <c r="B29" s="8" t="n">
         <v>1</v>
       </c>
@@ -5313,17 +5309,17 @@
       </c>
       <c r="E29" s="56" t="inlineStr">
         <is>
-          <t>参加者一覧</t>
+          <t>イベントを探す</t>
         </is>
       </c>
       <c r="F29" s="56" t="inlineStr">
         <is>
-          <t>絞り込み</t>
+          <t>一覧の絞り込み</t>
         </is>
       </c>
       <c r="G29" s="56" t="inlineStr">
         <is>
-          <t>イベントを探す</t>
+          <t>参加者向け一覧</t>
         </is>
       </c>
       <c r="H29" s="57" t="inlineStr">
@@ -5333,17 +5329,17 @@
       </c>
       <c r="I29" s="56" t="inlineStr">
         <is>
-          <t>6状態のイベントを用意して一覧表示</t>
+          <t>受付前・受付中・満席・受付終了・開催済・中止のイベントがある状態で、参加者ビューの一覧を見る</t>
         </is>
       </c>
       <c r="J29" s="56" t="inlineStr">
         <is>
-          <t>受付前・受付中・満席・受付終了・開催済・中止</t>
+          <t>デモデータに各状態あり</t>
         </is>
       </c>
       <c r="K29" s="56" t="inlineStr">
         <is>
-          <t>受付中・受付前のみ表示される（満席は出す。申込のみ不可）。判定は Domain.timing 経由</t>
+          <t>一覧に出るのは「受付中」「受付前」「満席」だけ。締切を過ぎたもの・開催済み・中止・下書き・限定公開は出ない</t>
         </is>
       </c>
       <c r="L29" s="57" t="inlineStr">
@@ -5353,7 +5349,7 @@
       </c>
       <c r="M29" s="56" t="inlineStr">
         <is>
-          <t>IT-25・F-83b</t>
+          <t>IT-25</t>
         </is>
       </c>
       <c r="N29" s="57" t="n"/>
@@ -5378,17 +5374,17 @@
       </c>
       <c r="E30" s="56" t="inlineStr">
         <is>
-          <t>S-5 設定</t>
+          <t>設定</t>
         </is>
       </c>
       <c r="F30" s="56" t="inlineStr">
         <is>
-          <t>シード・初期化</t>
+          <t>初期化とデモデータ</t>
         </is>
       </c>
       <c r="G30" s="56" t="inlineStr">
         <is>
-          <t>ボタン</t>
+          <t>2つのボタン</t>
         </is>
       </c>
       <c r="H30" s="57" t="inlineStr">
@@ -5398,13 +5394,13 @@
       </c>
       <c r="I30" s="56" t="inlineStr">
         <is>
-          <t>初期化→シード投入</t>
+          <t>設定→「データベースを初期化」→確認→「デモデータを投入」</t>
         </is>
       </c>
       <c r="J30" s="56" t="inlineStr"/>
       <c r="K30" s="56" t="inlineStr">
         <is>
-          <t>初期化前に確認モーダルが出る。件数が F-33b どおり（イベント40・参加者24・申込約220）。初期化→再投入が通る。連続投入は申込等が重複するため初期化→投入で運用する</t>
+          <t>初期化の前に確認画面が出る。投入後はイベント40件・参加者24人・申込約220件になる。※投入は必ず「初期化→投入」の順で行う（初期化せず2回投入すると申込などが重複する）</t>
         </is>
       </c>
       <c r="L30" s="57" t="inlineStr">
@@ -5414,7 +5410,7 @@
       </c>
       <c r="M30" s="56" t="inlineStr">
         <is>
-          <t>IT-21・F-32/F-33</t>
+          <t>IT-21</t>
         </is>
       </c>
       <c r="N30" s="57" t="n"/>
@@ -5427,7 +5423,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1" s="53">
+    <row r="31" ht="30.4" customHeight="1" s="53">
       <c r="B31" s="8" t="n">
         <v>1</v>
       </c>
@@ -5444,12 +5440,12 @@
       </c>
       <c r="F31" s="56" t="inlineStr">
         <is>
-          <t>フォント</t>
+          <t>文字の見た目</t>
         </is>
       </c>
       <c r="G31" s="56" t="inlineStr">
         <is>
-          <t>Jost</t>
+          <t>書体</t>
         </is>
       </c>
       <c r="H31" s="57" t="inlineStr">
@@ -5459,13 +5455,13 @@
       </c>
       <c r="I31" s="56" t="inlineStr">
         <is>
-          <t>通常状態で主催者・参加者ビューを表示</t>
+          <t>主催者・参加者の各画面を表示して、英数字と日本語の見た目を確認する</t>
         </is>
       </c>
       <c r="J31" s="56" t="inlineStr"/>
       <c r="K31" s="56" t="inlineStr">
         <is>
-          <t>英数字に Jost が適用され、日本語はシステム書体。表示崩れなし</t>
+          <t>英数字は会社サイトと同じ書体（Jost）、日本語は端末の標準書体で表示され、崩れが無い</t>
         </is>
       </c>
       <c r="L31" s="57" t="inlineStr">
@@ -5488,7 +5484,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="30.4" customHeight="1" s="53">
+    <row r="32" ht="43.59999999999999" customHeight="1" s="53">
       <c r="B32" s="8" t="n">
         <v>1</v>
       </c>
@@ -5505,12 +5501,12 @@
       </c>
       <c r="F32" s="56" t="inlineStr">
         <is>
-          <t>viewport</t>
+          <t>スマホでの表示</t>
         </is>
       </c>
       <c r="G32" s="56" t="inlineStr">
         <is>
-          <t>ビュー切替</t>
+          <t>参加者ビュー</t>
         </is>
       </c>
       <c r="H32" s="57" t="inlineStr">
@@ -5520,13 +5516,13 @@
       </c>
       <c r="I32" s="56" t="inlineStr">
         <is>
-          <t>主催者⇄参加者を切替。スマホ幅で参加者ビュー表示</t>
+          <t>参加者ビューをスマートフォン（または F12 → スマホ表示アイコン）で開く。主催者ビューも同様に確認する</t>
         </is>
       </c>
       <c r="J32" s="56" t="inlineStr"/>
       <c r="K32" s="56" t="inlineStr">
         <is>
-          <t>主催者は width=1024 固定、参加者は device-width。スマホ用CSSが主催者ビューに漏れず、参加者の入力欄は16px以上</t>
+          <t>参加者の画面はスマホの幅に収まり、入力欄をタップしても画面が勝手に拡大しない。主催者の画面はPC向けの幅のまま（スマホ対応しない仕様）</t>
         </is>
       </c>
       <c r="L32" s="57" t="inlineStr">
@@ -5536,7 +5532,7 @@
       </c>
       <c r="M32" s="56" t="inlineStr">
         <is>
-          <t>IT-23・F-81/F-81b</t>
+          <t>IT-23</t>
         </is>
       </c>
       <c r="N32" s="57" t="n"/>
@@ -5566,12 +5562,12 @@
       </c>
       <c r="F33" s="56" t="inlineStr">
         <is>
-          <t>描画の直列化</t>
+          <t>画面の切替</t>
         </is>
       </c>
       <c r="G33" s="56" t="inlineStr">
         <is>
-          <t>画面切替</t>
+          <t>連続切替</t>
         </is>
       </c>
       <c r="H33" s="57" t="inlineStr">
@@ -5581,13 +5577,13 @@
       </c>
       <c r="I33" s="56" t="inlineStr">
         <is>
-          <t>画面・タブを高速に連続切替（詳細⇄一覧を連打）</t>
+          <t>画面やタブをすばやく何度も切り替える（イベント詳細⇄一覧を連打するなど）</t>
         </is>
       </c>
       <c r="J33" s="56" t="inlineStr"/>
       <c r="K33" s="56" t="inlineStr">
         <is>
-          <t>最後に要求した画面が表示される（古い描画が後から上書きしない）</t>
+          <t>最後に押した画面が表示されたまま安定する（前に押した画面が遅れて出てきて上書きしない）</t>
         </is>
       </c>
       <c r="L33" s="57" t="inlineStr">
@@ -5650,11 +5646,11 @@
     <col width="23.75" bestFit="1" customWidth="1" style="42" min="6" max="6"/>
     <col width="31.9140625" bestFit="1" customWidth="1" style="42" min="7" max="7"/>
     <col width="8.6640625" customWidth="1" style="42" min="8" max="8"/>
-    <col width="42" bestFit="1" customWidth="1" style="42" min="9" max="9"/>
+    <col width="46" bestFit="1" customWidth="1" style="42" min="9" max="9"/>
     <col width="35.75" bestFit="1" customWidth="1" style="42" min="10" max="10"/>
     <col width="71.33203125" bestFit="1" customWidth="1" style="42" min="11" max="11"/>
     <col width="8.6640625" customWidth="1" style="42" min="12" max="12"/>
-    <col width="16" customWidth="1" style="42" min="13" max="13"/>
+    <col width="13" customWidth="1" style="42" min="13" max="13"/>
     <col width="8.6640625" customWidth="1" style="42" min="14" max="17"/>
     <col width="25.25" bestFit="1" customWidth="1" style="42" min="18" max="18"/>
     <col width="8.6640625" customWidth="1" style="42" min="19" max="16384"/>
@@ -5663,7 +5659,7 @@
     <row r="1" ht="22.5" customHeight="1" s="53">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>●異常系（ダウン・タイムアウト・不正データ）</t>
+          <t>●異常系（通信障害・おかしな入力）</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5671,7 @@
       </c>
       <c r="C3" s="28" t="inlineStr">
         <is>
-          <t>連携先の障害・不正入力時に、劣化が局所化されエラーが提示されることの確認</t>
+          <t>通信が切れたときや、おかしな値を入れられたときに、壊れず・だまされず・意味の分かるエラーが出ることを確認する</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5683,7 @@
       </c>
       <c r="C4" s="42" t="inlineStr">
         <is>
-          <t>ネットワーク異常は DevTools（Offline / Request blocking / Throttling）で再現する</t>
+          <t>通信の遮断・低速化は、ブラウザの開発者ツール（F12 → Network タブ）で再現する。具体的なやり方は各行の手順に書いてある</t>
         </is>
       </c>
     </row>
@@ -5699,7 +5695,7 @@
       </c>
       <c r="C5" s="30" t="inlineStr">
         <is>
-          <t>サーバ無し構成のため「連携先」はCDN・ブラウザAPI・URL・CSVに読み替える（結合試験仕様書 1-1）</t>
+          <t>このシステムはサーバを持たないため、「連携先」とは QR部品の配布元（CDN）・ブラウザの機能（カメラ・保存領域・コピー）・URL・CSVを開く表計算ソフトを指す</t>
         </is>
       </c>
     </row>
@@ -5829,17 +5825,17 @@
       </c>
       <c r="E9" s="56" t="inlineStr">
         <is>
-          <t>外部連携</t>
+          <t>QRで受付</t>
         </is>
       </c>
       <c r="F9" s="56" t="inlineStr">
         <is>
-          <t>CDN</t>
+          <t>部品が取得できない</t>
         </is>
       </c>
       <c r="G9" s="56" t="inlineStr">
         <is>
-          <t>jsQR の読込</t>
+          <t>QR読み取り部品（CDN）</t>
         </is>
       </c>
       <c r="H9" s="57" t="inlineStr">
@@ -5849,7 +5845,7 @@
       </c>
       <c r="I9" s="56" t="inlineStr">
         <is>
-          <t>Request blocking で CDN を遮断→QR読取を開く</t>
+          <t>F12 → Network → 「jsQR」のURLを右クリック→「Block request URL」→「QRで受付」を押す</t>
         </is>
       </c>
       <c r="J9" s="56" t="inlineStr">
@@ -5859,7 +5855,7 @@
       </c>
       <c r="K9" s="56" t="inlineStr">
         <is>
-          <t>QR読取のみエラー表示で失敗し、氏名検索の受付・他機能は無影響（劣化の局所化）</t>
+          <t>QR読み取りだけが「CDNに接続できません」等のエラーになる。氏名検索での受付やその他の機能は普通に使える</t>
         </is>
       </c>
       <c r="L9" s="57" t="inlineStr">
@@ -5869,7 +5865,7 @@
       </c>
       <c r="M9" s="56" t="inlineStr">
         <is>
-          <t>AB-01・R-01</t>
+          <t>AB-01</t>
         </is>
       </c>
       <c r="N9" s="57" t="n"/>
@@ -5882,7 +5878,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1" s="53">
+    <row r="10" ht="30.4" customHeight="1" s="53">
       <c r="B10" s="58" t="n">
         <v>2</v>
       </c>
@@ -5894,17 +5890,17 @@
       </c>
       <c r="E10" s="56" t="inlineStr">
         <is>
-          <t>外部連携</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="F10" s="56" t="inlineStr">
         <is>
-          <t>フォント</t>
+          <t>書体が取得できない</t>
         </is>
       </c>
       <c r="G10" s="56" t="inlineStr">
         <is>
-          <t>Jost の取得</t>
+          <t>フォント配布元</t>
         </is>
       </c>
       <c r="H10" s="57" t="inlineStr">
@@ -5914,7 +5910,7 @@
       </c>
       <c r="I10" s="56" t="inlineStr">
         <is>
-          <t>フォント配布元を遮断→再読込</t>
+          <t>F12 → Network → 「fonts.gstatic.com」をブロック→ページを再読み込み</t>
         </is>
       </c>
       <c r="J10" s="56" t="inlineStr">
@@ -5924,7 +5920,7 @@
       </c>
       <c r="K10" s="56" t="inlineStr">
         <is>
-          <t>システム書体で全画面が表示継続。機能影響なし</t>
+          <t>英数字が標準の書体に変わるだけで、画面のレイアウトも機能も正常に使える</t>
         </is>
       </c>
       <c r="L10" s="57" t="inlineStr">
@@ -5947,7 +5943,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1" s="53">
+    <row r="11" ht="30.4" customHeight="1" s="53">
       <c r="B11" s="58" t="n">
         <v>2</v>
       </c>
@@ -5959,17 +5955,17 @@
       </c>
       <c r="E11" s="56" t="inlineStr">
         <is>
-          <t>S-4 申込タブ</t>
+          <t>QRで受付</t>
         </is>
       </c>
       <c r="F11" s="56" t="inlineStr">
         <is>
-          <t>QR受付</t>
+          <t>カメラが使えない</t>
         </is>
       </c>
       <c r="G11" s="56" t="inlineStr">
         <is>
-          <t>カメラ</t>
+          <t>カメラ許可</t>
         </is>
       </c>
       <c r="H11" s="57" t="inlineStr">
@@ -5979,7 +5975,7 @@
       </c>
       <c r="I11" s="56" t="inlineStr">
         <is>
-          <t>カメラ許可を拒否／カメラ無し端末で実行</t>
+          <t>ブラウザのカメラ許可を「ブロック」にして「QRで受付」を押す</t>
         </is>
       </c>
       <c r="J11" s="56" t="inlineStr">
@@ -5989,7 +5985,7 @@
       </c>
       <c r="K11" s="56" t="inlineStr">
         <is>
-          <t>エラーメッセージを表示し、氏名検索受付へ誘導される</t>
+          <t>「カメラを起動できません…氏名検索での受付をご利用ください」の案内が出て、氏名検索で受付を続けられる</t>
         </is>
       </c>
       <c r="L11" s="57" t="inlineStr">
@@ -6029,12 +6025,12 @@
       </c>
       <c r="F12" s="56" t="inlineStr">
         <is>
-          <t>起動</t>
+          <t>保存機能が使えない</t>
         </is>
       </c>
       <c r="G12" s="56" t="inlineStr">
         <is>
-          <t>IndexedDB</t>
+          <t>ブラウザの保存領域</t>
         </is>
       </c>
       <c r="H12" s="57" t="inlineStr">
@@ -6044,7 +6040,7 @@
       </c>
       <c r="I12" s="56" t="inlineStr">
         <is>
-          <t>プライベートモード等 IndexedDB 不可の状態で起動</t>
+          <t>データ保存が制限された状態（例: 一部ブラウザのシークレットモード）でページを開く</t>
         </is>
       </c>
       <c r="J12" s="56" t="inlineStr">
@@ -6054,7 +6050,7 @@
       </c>
       <c r="K12" s="56" t="inlineStr">
         <is>
-          <t>白画面ではなくエラーが提示される（挙動を記録し、必要なら不具合票へ）</t>
+          <t>真っ白な画面にならず、エラーの案内が表示される（表示内容をそのまま備考に記録する）</t>
         </is>
       </c>
       <c r="L12" s="57" t="inlineStr">
@@ -6077,7 +6073,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1" s="53">
+    <row r="13" ht="30.4" customHeight="1" s="53">
       <c r="B13" s="58" t="n">
         <v>2</v>
       </c>
@@ -6089,17 +6085,17 @@
       </c>
       <c r="E13" s="56" t="inlineStr">
         <is>
-          <t>S-4 告知</t>
+          <t>告知</t>
         </is>
       </c>
       <c r="F13" s="56" t="inlineStr">
         <is>
-          <t>コピー</t>
+          <t>コピーできない</t>
         </is>
       </c>
       <c r="G13" s="56" t="inlineStr">
         <is>
-          <t>クリップボード</t>
+          <t>クリップボード許可</t>
         </is>
       </c>
       <c r="H13" s="57" t="inlineStr">
@@ -6109,7 +6105,7 @@
       </c>
       <c r="I13" s="56" t="inlineStr">
         <is>
-          <t>権限を拒否した状態でコピー</t>
+          <t>ブラウザのクリップボード許可を拒否した状態で「コピー」を押す</t>
         </is>
       </c>
       <c r="J13" s="56" t="inlineStr">
@@ -6119,7 +6115,7 @@
       </c>
       <c r="K13" s="56" t="inlineStr">
         <is>
-          <t>失敗が利用者に分かる（成功トーストを出さない）</t>
+          <t>「コピーできませんでした」と表示される（成功したかのようなメッセージを出さない）</t>
         </is>
       </c>
       <c r="L13" s="57" t="inlineStr">
@@ -6142,7 +6138,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1" s="53">
+    <row r="14" ht="30.4" customHeight="1" s="53">
       <c r="B14" s="58" t="n">
         <v>2</v>
       </c>
@@ -6154,17 +6150,17 @@
       </c>
       <c r="E14" s="56" t="inlineStr">
         <is>
-          <t>S-4 ファイル</t>
+          <t>ファイル共有</t>
         </is>
       </c>
       <c r="F14" s="56" t="inlineStr">
         <is>
-          <t>容量</t>
+          <t>容量がいっぱい</t>
         </is>
       </c>
       <c r="G14" s="56" t="inlineStr">
         <is>
-          <t>ストレージ quota</t>
+          <t>ブラウザの保存容量</t>
         </is>
       </c>
       <c r="H14" s="57" t="inlineStr">
@@ -6174,7 +6170,7 @@
       </c>
       <c r="I14" s="56" t="inlineStr">
         <is>
-          <t>大きなファイルを繰り返し追加し quota 超過</t>
+          <t>大きなファイル（20MB近く）を何度も追加して、ブラウザの保存容量を使い切る</t>
         </is>
       </c>
       <c r="J14" s="56" t="inlineStr">
@@ -6184,7 +6180,7 @@
       </c>
       <c r="K14" s="56" t="inlineStr">
         <is>
-          <t>エラーが提示され、既存データは壊れない</t>
+          <t>エラーの案内が出るだけで、それまでに保存したデータは壊れない</t>
         </is>
       </c>
       <c r="L14" s="57" t="inlineStr">
@@ -6219,17 +6215,17 @@
       </c>
       <c r="E15" s="56" t="inlineStr">
         <is>
-          <t>S-4 申込タブ</t>
+          <t>QRで受付</t>
         </is>
       </c>
       <c r="F15" s="56" t="inlineStr">
         <is>
-          <t>QR受付</t>
+          <t>回線が遅い</t>
         </is>
       </c>
       <c r="G15" s="56" t="inlineStr">
         <is>
-          <t>CDN 低速応答</t>
+          <t>部品の読み込み待ち</t>
         </is>
       </c>
       <c r="H15" s="57" t="inlineStr">
@@ -6239,7 +6235,7 @@
       </c>
       <c r="I15" s="56" t="inlineStr">
         <is>
-          <t>Slow 3G に絞って QR読取を開く</t>
+          <t>F12 → Network → 速度を「Slow 3G」にして「QRで受付」を押す</t>
         </is>
       </c>
       <c r="J15" s="56" t="inlineStr">
@@ -6249,7 +6245,7 @@
       </c>
       <c r="K15" s="56" t="inlineStr">
         <is>
-          <t>読込中の状態が分かる。完了後に動作し、再度開いても二重読込しない（loadScript）</t>
+          <t>読み込み中であることが分かる表示が出る。読み込みが終われば動作する。一度閉じてもう一度開いても、二重に読み込まない</t>
         </is>
       </c>
       <c r="L15" s="57" t="inlineStr">
@@ -6272,7 +6268,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1" s="53">
+    <row r="16" ht="30.4" customHeight="1" s="53">
       <c r="B16" s="58" t="n">
         <v>2</v>
       </c>
@@ -6284,17 +6280,17 @@
       </c>
       <c r="E16" s="56" t="inlineStr">
         <is>
-          <t>共通</t>
+          <t>URLから開く</t>
         </is>
       </c>
       <c r="F16" s="56" t="inlineStr">
         <is>
-          <t>URL復帰</t>
+          <t>確認URLの改ざん</t>
         </is>
       </c>
       <c r="G16" s="56" t="inlineStr">
         <is>
-          <t>?ticket= 改変</t>
+          <t>?ticket=</t>
         </is>
       </c>
       <c r="H16" s="57" t="inlineStr">
@@ -6304,7 +6300,7 @@
       </c>
       <c r="I16" s="56" t="inlineStr">
         <is>
-          <t>存在しない／形式不正なトークンで開く</t>
+          <t>確認用URLの ?ticket= の後ろをでたらめな文字に書き換えて開く</t>
         </is>
       </c>
       <c r="J16" s="56" t="inlineStr">
@@ -6314,7 +6310,7 @@
       </c>
       <c r="K16" s="56" t="inlineStr">
         <is>
-          <t>エラー表示で通常画面へ。他人の申込・内部情報が漏れない</t>
+          <t>「この確認URLに対応する申込が見つかりません」と出て通常の画面に戻る。他人の申込内容は絶対に出ない</t>
         </is>
       </c>
       <c r="L16" s="57" t="inlineStr">
@@ -6337,7 +6333,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1" s="53">
+    <row r="17" ht="30.4" customHeight="1" s="53">
       <c r="B17" s="58" t="n">
         <v>2</v>
       </c>
@@ -6349,17 +6345,17 @@
       </c>
       <c r="E17" s="56" t="inlineStr">
         <is>
-          <t>共通</t>
+          <t>URLから開く</t>
         </is>
       </c>
       <c r="F17" s="56" t="inlineStr">
         <is>
-          <t>URL復帰</t>
+          <t>イベントURLの改ざん</t>
         </is>
       </c>
       <c r="G17" s="56" t="inlineStr">
         <is>
-          <t>?event= 改変</t>
+          <t>?event=</t>
         </is>
       </c>
       <c r="H17" s="57" t="inlineStr">
@@ -6369,7 +6365,7 @@
       </c>
       <c r="I17" s="56" t="inlineStr">
         <is>
-          <t>不存在・下書き・限定公開・中止のIDで開く</t>
+          <t>?event= に ①存在しないID ②下書きのID ③限定公開のID ④中止のID を入れて開く</t>
         </is>
       </c>
       <c r="J17" s="56" t="inlineStr">
@@ -6379,7 +6375,7 @@
       </c>
       <c r="K17" s="56" t="inlineStr">
         <is>
-          <t>不存在・下書きは見えない。限定公開は表示（F-65）。中止は状態を表示</t>
+          <t>①②は「表示できません」。③は表示される（URLを知る人には見せる仕様）。④は「中止されました」と表示される</t>
         </is>
       </c>
       <c r="L17" s="57" t="inlineStr">
@@ -6389,7 +6385,7 @@
       </c>
       <c r="M17" s="56" t="inlineStr">
         <is>
-          <t>AB-09・F-65</t>
+          <t>AB-09</t>
         </is>
       </c>
       <c r="N17" s="57" t="n"/>
@@ -6402,7 +6398,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1" s="53">
+    <row r="18" ht="30.4" customHeight="1" s="53">
       <c r="B18" s="58" t="n">
         <v>2</v>
       </c>
@@ -6414,17 +6410,17 @@
       </c>
       <c r="E18" s="56" t="inlineStr">
         <is>
-          <t>S-9 マイ申込</t>
+          <t>マイ申込</t>
         </is>
       </c>
       <c r="F18" s="56" t="inlineStr">
         <is>
-          <t>確認URL</t>
+          <t>キャンセル済みの確認URL</t>
         </is>
       </c>
       <c r="G18" s="56" t="inlineStr">
         <is>
-          <t>キャンセル済みの ?ticket=</t>
+          <t>?ticket=</t>
         </is>
       </c>
       <c r="H18" s="57" t="inlineStr">
@@ -6434,7 +6430,7 @@
       </c>
       <c r="I18" s="56" t="inlineStr">
         <is>
-          <t>キャンセル済み申込の確認URLを開く</t>
+          <t>キャンセル済みの申込の確認URLを開く</t>
         </is>
       </c>
       <c r="J18" s="56" t="inlineStr">
@@ -6444,7 +6440,7 @@
       </c>
       <c r="K18" s="56" t="inlineStr">
         <is>
-          <t>キャンセル済みである旨を表示し、操作に進めない</t>
+          <t>「キャンセルされました」と表示され、受付用QRなどの操作には進めない</t>
         </is>
       </c>
       <c r="L18" s="57" t="inlineStr">
@@ -6454,7 +6450,7 @@
       </c>
       <c r="M18" s="56" t="inlineStr">
         <is>
-          <t>AB-10・F-43</t>
+          <t>AB-10</t>
         </is>
       </c>
       <c r="N18" s="57" t="n"/>
@@ -6467,7 +6463,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="43.59999999999999" customHeight="1" s="53">
+    <row r="19" ht="70" customHeight="1" s="53">
       <c r="B19" s="58" t="n">
         <v>2</v>
       </c>
@@ -6484,7 +6480,7 @@
       </c>
       <c r="F19" s="56" t="inlineStr">
         <is>
-          <t>XSS</t>
+          <t>スクリプトの埋め込み</t>
         </is>
       </c>
       <c r="G19" s="56" t="inlineStr">
@@ -6499,7 +6495,7 @@
       </c>
       <c r="I19" s="56" t="inlineStr">
         <is>
-          <t>氏名・回答・スレッド・お知らせに &lt;script&gt; 等を入力。マニュアルに javascript: リンク</t>
+          <t>氏名・質問の回答・スレッド・お知らせに「&lt;script&gt;alert(1)&lt;/script&gt;」等を入力し、各画面（一覧・公開ページ・マイ申込・名簿・CSV）で表示。マニュアルに「[リンク](javascript:alert(1))」と書く</t>
         </is>
       </c>
       <c r="J19" s="56" t="inlineStr">
@@ -6509,7 +6505,7 @@
       </c>
       <c r="K19" s="56" t="inlineStr">
         <is>
-          <t>スクリプトは実行されず文字列として表示（Util.esc）。リンク化されない（https? のみ）</t>
+          <t>入力した文字がそのまま文字として表示される（ポップアップ等が勝手に動かない）。javascript: のリンクはリンクにならない</t>
         </is>
       </c>
       <c r="L19" s="57" t="inlineStr">
@@ -6544,17 +6540,17 @@
       </c>
       <c r="E20" s="56" t="inlineStr">
         <is>
-          <t>S-4／S-10</t>
+          <t>CSV出力</t>
         </is>
       </c>
       <c r="F20" s="56" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>数式の埋め込み</t>
         </is>
       </c>
       <c r="G20" s="56" t="inlineStr">
         <is>
-          <t>数式注入</t>
+          <t>氏名欄</t>
         </is>
       </c>
       <c r="H20" s="57" t="inlineStr">
@@ -6564,7 +6560,7 @@
       </c>
       <c r="I20" s="56" t="inlineStr">
         <is>
-          <t>氏名を =1+1・@cmd 等にして CSV 出力→表計算で開く</t>
+          <t>氏名を「=1+1」「@abc」などにして申込→申込一覧または名簿のCSVを出力してExcelで開く</t>
         </is>
       </c>
       <c r="J20" s="56" t="inlineStr">
@@ -6574,7 +6570,7 @@
       </c>
       <c r="K20" s="56" t="inlineStr">
         <is>
-          <t>先頭に ' が付与され、数式として実行されない</t>
+          <t>セルが計算されず、入力した文字のまま表示される（先頭に ' が付いて数式扱いされない）</t>
         </is>
       </c>
       <c r="L20" s="57" t="inlineStr">
@@ -6584,7 +6580,7 @@
       </c>
       <c r="M20" s="56" t="inlineStr">
         <is>
-          <t>AB-12・F-49b</t>
+          <t>AB-12</t>
         </is>
       </c>
       <c r="N20" s="57" t="n"/>
@@ -6597,7 +6593,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1" s="53">
+    <row r="21" ht="30.4" customHeight="1" s="53">
       <c r="B21" s="58" t="n">
         <v>2</v>
       </c>
@@ -6609,17 +6605,17 @@
       </c>
       <c r="E21" s="56" t="inlineStr">
         <is>
-          <t>S-7 申込フォーム</t>
+          <t>参加者の申込</t>
         </is>
       </c>
       <c r="F21" s="56" t="inlineStr">
         <is>
-          <t>名寄せ</t>
+          <t>メールの表記ゆれ</t>
         </is>
       </c>
       <c r="G21" s="56" t="inlineStr">
         <is>
-          <t>メール表記ゆれ</t>
+          <t>メール欄</t>
         </is>
       </c>
       <c r="H21" s="57" t="inlineStr">
@@ -6629,7 +6625,7 @@
       </c>
       <c r="I21" s="56" t="inlineStr">
         <is>
-          <t>前後空白・大文字混じりのメールで申込</t>
+          <t>「 ABC@Example.com 」のように大文字・前後スペース入りのメールで申込む</t>
         </is>
       </c>
       <c r="J21" s="56" t="inlineStr">
@@ -6639,7 +6635,7 @@
       </c>
       <c r="K21" s="56" t="inlineStr">
         <is>
-          <t>trim＋小文字化で既存の同一人物に名寄せされる。それ以上の正規化はしない</t>
+          <t>既存の「abc@example.com」と同じ人として名簿に1人にまとまる（別人としては増えない）</t>
         </is>
       </c>
       <c r="L21" s="57" t="inlineStr">
@@ -6662,7 +6658,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1" s="53">
+    <row r="22" ht="30.4" customHeight="1" s="53">
       <c r="B22" s="58" t="n">
         <v>2</v>
       </c>
@@ -6674,17 +6670,17 @@
       </c>
       <c r="E22" s="56" t="inlineStr">
         <is>
-          <t>S-4 申込タブ</t>
+          <t>当日受付</t>
         </is>
       </c>
       <c r="F22" s="56" t="inlineStr">
         <is>
-          <t>内容修正</t>
+          <t>メールの重複</t>
         </is>
       </c>
       <c r="G22" s="56" t="inlineStr">
         <is>
-          <t>emailKey 衝突</t>
+          <t>申込内容の修正</t>
         </is>
       </c>
       <c r="H22" s="57" t="inlineStr">
@@ -6694,7 +6690,7 @@
       </c>
       <c r="I22" s="56" t="inlineStr">
         <is>
-          <t>別人が使用中のメールアドレスに変更</t>
+          <t>申込の修正で、別の人がすでに使っているメールアドレスに変更する</t>
         </is>
       </c>
       <c r="J22" s="56" t="inlineStr">
@@ -6704,7 +6700,7 @@
       </c>
       <c r="K22" s="56" t="inlineStr">
         <is>
-          <t>拒否され、persons / applications とも無変更（誤統合の防止）</t>
+          <t>「このメールアドレスは別の参加者に登録されています」と拒否され、何も変わらない</t>
         </is>
       </c>
       <c r="L22" s="57" t="inlineStr">
@@ -6739,17 +6735,17 @@
       </c>
       <c r="E23" s="56" t="inlineStr">
         <is>
-          <t>S-7 申込フォーム</t>
+          <t>参加者の申込</t>
         </is>
       </c>
       <c r="F23" s="56" t="inlineStr">
         <is>
-          <t>定員</t>
+          <t>満席ちょうど</t>
         </is>
       </c>
       <c r="G23" s="56" t="inlineStr">
         <is>
-          <t>残席境界</t>
+          <t>残席の境界</t>
         </is>
       </c>
       <c r="H23" s="57" t="inlineStr">
@@ -6759,7 +6755,7 @@
       </c>
       <c r="I23" s="56" t="inlineStr">
         <is>
-          <t>残1で申込→残0でさらに申込</t>
+          <t>残席1のイベントに1人申込む→続けてもう1人申込もうとする</t>
         </is>
       </c>
       <c r="J23" s="56" t="inlineStr">
@@ -6769,7 +6765,7 @@
       </c>
       <c r="K23" s="56" t="inlineStr">
         <is>
-          <t>残1は成功。残0は「定員に達したため申込できません」。キャンセルすると再び申込可</t>
+          <t>1人目は成功する。2人目は「定員に達したため申込できません」。誰かがキャンセルすると、また申込めるようになる</t>
         </is>
       </c>
       <c r="L23" s="57" t="inlineStr">
@@ -6779,7 +6775,7 @@
       </c>
       <c r="M23" s="56" t="inlineStr">
         <is>
-          <t>AB-15・F-18</t>
+          <t>AB-15</t>
         </is>
       </c>
       <c r="N23" s="57" t="n"/>
@@ -6792,7 +6788,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="30.4" customHeight="1" s="53">
+    <row r="24" ht="43.59999999999999" customHeight="1" s="53">
       <c r="B24" s="58" t="n">
         <v>2</v>
       </c>
@@ -6804,17 +6800,17 @@
       </c>
       <c r="E24" s="56" t="inlineStr">
         <is>
-          <t>S-6 公開ページ</t>
+          <t>公開ページ</t>
         </is>
       </c>
       <c r="F24" s="56" t="inlineStr">
         <is>
-          <t>時刻境界</t>
+          <t>締切の瞬間</t>
         </is>
       </c>
       <c r="G24" s="56" t="inlineStr">
         <is>
-          <t>締切・受付開始</t>
+          <t>日付の境界</t>
         </is>
       </c>
       <c r="H24" s="57" t="inlineStr">
@@ -6824,7 +6820,7 @@
       </c>
       <c r="I24" s="56" t="inlineStr">
         <is>
-          <t>締切日 23:59 と翌日 0:00、受付開始日 0:00 前後で表示</t>
+          <t>締切日の23:59と翌日0:00、受付開始日の0:00の前後で公開ページを確認する（イベントの締切設定を今日・昨日に変えて再現してよい）</t>
         </is>
       </c>
       <c r="J24" s="56" t="inlineStr">
@@ -6834,7 +6830,7 @@
       </c>
       <c r="K24" s="56" t="inlineStr">
         <is>
-          <t>締切日 23:59:59 まで受付中。受付開始日 0:00 から受付中。日付のみ文字列の UTC 解釈ズレが無い</t>
+          <t>締切日の夜23:59までは申込め、日付が変わると「受付終了」になる。受付開始日は0:00から申込める</t>
         </is>
       </c>
       <c r="L24" s="57" t="inlineStr">
@@ -6844,7 +6840,7 @@
       </c>
       <c r="M24" s="56" t="inlineStr">
         <is>
-          <t>AB-16・F-45/F-45b</t>
+          <t>AB-16</t>
         </is>
       </c>
       <c r="N24" s="57" t="n"/>
@@ -6857,7 +6853,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1" s="53">
+    <row r="25" ht="30.4" customHeight="1" s="53">
       <c r="B25" s="58" t="n">
         <v>2</v>
       </c>
@@ -6869,17 +6865,17 @@
       </c>
       <c r="E25" s="56" t="inlineStr">
         <is>
-          <t>S-7 申込フォーム</t>
+          <t>参加者の申込</t>
         </is>
       </c>
       <c r="F25" s="56" t="inlineStr">
         <is>
-          <t>重複申込</t>
+          <t>二重申込</t>
         </is>
       </c>
       <c r="G25" s="56" t="inlineStr">
         <is>
-          <t>検証順4</t>
+          <t>同じ人の再申込</t>
         </is>
       </c>
       <c r="H25" s="57" t="inlineStr">
@@ -6889,7 +6885,7 @@
       </c>
       <c r="I25" s="56" t="inlineStr">
         <is>
-          <t>有効な申込がある人が同一イベントに再申込</t>
+          <t>申込済みの人が、同じイベントにもう一度申込む</t>
         </is>
       </c>
       <c r="J25" s="56" t="inlineStr">
@@ -6899,7 +6895,7 @@
       </c>
       <c r="K25" s="56" t="inlineStr">
         <is>
-          <t>「既に申込済みです」で拒否。キャンセル済みなら成功する</t>
+          <t>「このイベントには既に申込済みです」と拒否される。キャンセル済みの人なら申込める</t>
         </is>
       </c>
       <c r="L25" s="57" t="inlineStr">
@@ -6909,7 +6905,7 @@
       </c>
       <c r="M25" s="56" t="inlineStr">
         <is>
-          <t>AB-17・F-17</t>
+          <t>AB-17</t>
         </is>
       </c>
       <c r="N25" s="57" t="n"/>
@@ -6934,17 +6930,17 @@
       </c>
       <c r="E26" s="56" t="inlineStr">
         <is>
-          <t>S-7 申込フォーム</t>
+          <t>参加者の申込</t>
         </is>
       </c>
       <c r="F26" s="56" t="inlineStr">
         <is>
-          <t>非公開への申込</t>
+          <t>公開前・中止後の申込</t>
         </is>
       </c>
       <c r="G26" s="56" t="inlineStr">
         <is>
-          <t>検証順1</t>
+          <t>下書き・中止イベント</t>
         </is>
       </c>
       <c r="H26" s="57" t="inlineStr">
@@ -6954,7 +6950,7 @@
       </c>
       <c r="I26" s="56" t="inlineStr">
         <is>
-          <t>下書き・中止イベントへ申込を実行</t>
+          <t>下書き・中止イベントのURLから申込を試す</t>
         </is>
       </c>
       <c r="J26" s="56" t="inlineStr">
@@ -6964,7 +6960,7 @@
       </c>
       <c r="K26" s="56" t="inlineStr">
         <is>
-          <t>「このイベントには申込できません」で拒否</t>
+          <t>「このイベントには申込できません」と拒否される</t>
         </is>
       </c>
       <c r="L26" s="57" t="inlineStr">
@@ -6999,17 +6995,17 @@
       </c>
       <c r="E27" s="56" t="inlineStr">
         <is>
-          <t>S-7 申込フォーム</t>
+          <t>参加者の申込</t>
         </is>
       </c>
       <c r="F27" s="56" t="inlineStr">
         <is>
-          <t>検証順序</t>
+          <t>理由の優先順位</t>
         </is>
       </c>
       <c r="G27" s="56" t="inlineStr">
         <is>
-          <t>複数条件の同時成立</t>
+          <t>中止かつ満席</t>
         </is>
       </c>
       <c r="H27" s="57" t="inlineStr">
@@ -7019,7 +7015,7 @@
       </c>
       <c r="I27" s="56" t="inlineStr">
         <is>
-          <t>中止かつ満席のイベントに申込</t>
+          <t>中止していて、かつ満席でもあるイベントに申込を試す</t>
         </is>
       </c>
       <c r="J27" s="56" t="inlineStr">
@@ -7029,7 +7025,7 @@
       </c>
       <c r="K27" s="56" t="inlineStr">
         <is>
-          <t>詳細設計書 5-1 の評価順で最初に該当した理由が表示される（中止が「満席」と誤報されない）</t>
+          <t>断りの理由は「中止」と表示される（「満席」と誤って出ない）※自動テストで確認済み</t>
         </is>
       </c>
       <c r="L27" s="57" t="inlineStr">
@@ -7064,17 +7060,17 @@
       </c>
       <c r="E28" s="56" t="inlineStr">
         <is>
-          <t>S-4 ファイル</t>
+          <t>ファイル共有</t>
         </is>
       </c>
       <c r="F28" s="56" t="inlineStr">
         <is>
-          <t>サイズ上限</t>
+          <t>サイズ超過</t>
         </is>
       </c>
       <c r="G28" s="56" t="inlineStr">
         <is>
-          <t>20MB 超</t>
+          <t>20MBの上限</t>
         </is>
       </c>
       <c r="H28" s="57" t="inlineStr">
@@ -7084,7 +7080,7 @@
       </c>
       <c r="I28" s="56" t="inlineStr">
         <is>
-          <t>20MB を超えるファイルを追加</t>
+          <t>20MBを超えるファイルを追加する</t>
         </is>
       </c>
       <c r="J28" s="56" t="inlineStr">
@@ -7094,7 +7090,7 @@
       </c>
       <c r="K28" s="56" t="inlineStr">
         <is>
-          <t>拒否メッセージが表示され、DB に書き込まれない</t>
+          <t>「20MBを超えるファイルは追加できません」と出て、追加されない</t>
         </is>
       </c>
       <c r="L28" s="57" t="inlineStr">
@@ -7104,7 +7100,7 @@
       </c>
       <c r="M28" s="56" t="inlineStr">
         <is>
-          <t>AB-20・F-102</t>
+          <t>AB-20</t>
         </is>
       </c>
       <c r="N28" s="57" t="n"/>
@@ -7153,15 +7149,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="8.6640625" customWidth="1" style="42" min="1" max="4"/>
-    <col width="18" bestFit="1" customWidth="1" style="42" min="5" max="5"/>
+    <col width="16" bestFit="1" customWidth="1" style="42" min="5" max="5"/>
     <col width="18" bestFit="1" customWidth="1" style="42" min="6" max="6"/>
-    <col width="26" bestFit="1" customWidth="1" style="42" min="7" max="7"/>
+    <col width="22" bestFit="1" customWidth="1" style="42" min="7" max="7"/>
     <col width="8.6640625" customWidth="1" style="42" min="8" max="8"/>
-    <col width="42" bestFit="1" customWidth="1" style="42" min="9" max="9"/>
-    <col width="22" bestFit="1" customWidth="1" style="42" min="10" max="10"/>
+    <col width="46" bestFit="1" customWidth="1" style="42" min="9" max="9"/>
+    <col width="20" bestFit="1" customWidth="1" style="42" min="10" max="10"/>
     <col width="71.83203125" bestFit="1" customWidth="1" style="42" min="11" max="11"/>
     <col width="8.6640625" customWidth="1" style="42" min="12" max="12"/>
-    <col width="16" customWidth="1" style="42" min="13" max="13"/>
+    <col width="13" customWidth="1" style="42" min="13" max="13"/>
     <col width="8.6640625" customWidth="1" style="42" min="14" max="14"/>
     <col width="9" bestFit="1" customWidth="1" style="42" min="15" max="15"/>
     <col width="8.6640625" customWidth="1" style="42" min="16" max="16"/>
@@ -7173,7 +7169,7 @@
     <row r="1" ht="22.5" customHeight="1" s="53">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>●トランザクション整合</t>
+          <t>●保存の整合性（中途半端に保存されないこと）</t>
         </is>
       </c>
     </row>
@@ -7185,7 +7181,7 @@
       </c>
       <c r="C3" s="28" t="inlineStr">
         <is>
-          <t>複数ストアをまたぐ更新（bulkPut の全使用場面）の原子性の確認</t>
+          <t>1回の操作で複数の場所に保存されるデータが、一部だけ保存された中途半端な状態にならないことを確認する</t>
         </is>
       </c>
     </row>
@@ -7197,7 +7193,7 @@
       </c>
       <c r="C4" s="42" t="inlineStr">
         <is>
-          <t>DevTools → Application → IndexedDB で更新前後の件数・内容を観察する</t>
+          <t>判定は「画面に見える結果」と「ページを再読み込みしても同じか」で行う</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7205,7 @@
       </c>
       <c r="C5" s="30" t="inlineStr">
         <is>
-          <t>TX-04 は自動テスト不可（fake-indexeddb が Blob 非対応 / R-02）のため手動必須</t>
+          <t>※印の行は自動テストで検証済み。手動での再現が難しい行は実施不要（結果欄に「自動」と記入する）</t>
         </is>
       </c>
     </row>
@@ -7327,7 +7323,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30.4" customHeight="1" s="53">
+    <row r="9" ht="43.59999999999999" customHeight="1" s="53">
       <c r="B9" s="58" t="n">
         <v>3</v>
       </c>
@@ -7339,17 +7335,17 @@
       </c>
       <c r="E9" s="56" t="inlineStr">
         <is>
-          <t>申込確定</t>
+          <t>参加者の申込</t>
         </is>
       </c>
       <c r="F9" s="56" t="inlineStr">
         <is>
-          <t>bulkPut</t>
+          <t>申込1件の保存</t>
         </is>
       </c>
       <c r="G9" s="56" t="inlineStr">
         <is>
-          <t>persons / applications / savedTokens</t>
+          <t>成功時と拒否時</t>
         </is>
       </c>
       <c r="H9" s="57" t="inlineStr">
@@ -7359,13 +7355,13 @@
       </c>
       <c r="I9" s="56" t="inlineStr">
         <is>
-          <t>申込成功時と拒否時（定員0等）で3ストアを観察</t>
+          <t>①普通に申込む ②満席のイベントで申込を試す（拒否される）→どちらも後にページを再読み込み</t>
         </is>
       </c>
       <c r="J9" s="56" t="inlineStr"/>
       <c r="K9" s="56" t="inlineStr">
         <is>
-          <t>成功：3ストアが揃って+1（トークン一致）。拒否：いずれも増えない（検証はトランザクション外・書き込みは1回）</t>
+          <t>①申込一覧・参加者名簿・マイ申込のすべてに反映され、再読み込み後も残っている ②どこにも増えておらず、再読み込みしても現れない（一部だけ保存された状態にならない）</t>
         </is>
       </c>
       <c r="L9" s="57" t="inlineStr">
@@ -7400,17 +7396,17 @@
       </c>
       <c r="E10" s="56" t="inlineStr">
         <is>
-          <t>申込者修正</t>
+          <t>当日受付</t>
         </is>
       </c>
       <c r="F10" s="56" t="inlineStr">
         <is>
-          <t>bulkPut</t>
+          <t>修正の反映</t>
         </is>
       </c>
       <c r="G10" s="56" t="inlineStr">
         <is>
-          <t>persons ＋ 当人の全 applications</t>
+          <t>本人の全申込</t>
         </is>
       </c>
       <c r="H10" s="57" t="inlineStr">
@@ -7420,13 +7416,13 @@
       </c>
       <c r="I10" s="56" t="inlineStr">
         <is>
-          <t>複数申込を持つ人を修正／emailKey 衝突で拒否</t>
+          <t>複数イベントに申込んでいる人の氏名を修正する／別の人のメールに変えて拒否させる</t>
         </is>
       </c>
       <c r="J10" s="56" t="inlineStr"/>
       <c r="K10" s="56" t="inlineStr">
         <is>
-          <t>成功：searchText まで同時更新。拒否：両ストアとも無変更</t>
+          <t>成功時はその人の全部の申込に新しい氏名が反映される。拒否時はどの画面も何も変わらない</t>
         </is>
       </c>
       <c r="L10" s="57" t="inlineStr">
@@ -7461,17 +7457,17 @@
       </c>
       <c r="E11" s="56" t="inlineStr">
         <is>
-          <t>タスク並べ替え</t>
+          <t>運営タスク</t>
         </is>
       </c>
       <c r="F11" s="56" t="inlineStr">
         <is>
-          <t>bulkPut</t>
+          <t>並べ替えの保存</t>
         </is>
       </c>
       <c r="G11" s="56" t="inlineStr">
         <is>
-          <t>tasks</t>
+          <t>ドラッグ後</t>
         </is>
       </c>
       <c r="H11" s="57" t="inlineStr">
@@ -7481,13 +7477,13 @@
       </c>
       <c r="I11" s="56" t="inlineStr">
         <is>
-          <t>ボードでドラッグ→drop→リロード</t>
+          <t>カードを何枚かドラッグで動かす→ページを再読み込みする</t>
         </is>
       </c>
       <c r="J11" s="56" t="inlineStr"/>
       <c r="K11" s="56" t="inlineStr">
         <is>
-          <t>変化したレコードのみ保存され、order 10刻みで順序が永続。ドラッグ中に innerHTML の全置換が走らない</t>
+          <t>動かした後の並び順と状態がそのまま残っている（一部のカードだけ元に戻ることがない）</t>
         </is>
       </c>
       <c r="L11" s="57" t="inlineStr">
@@ -7510,7 +7506,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1" s="53">
+    <row r="12" ht="30.4" customHeight="1" s="53">
       <c r="B12" s="58" t="n">
         <v>3</v>
       </c>
@@ -7522,17 +7518,17 @@
       </c>
       <c r="E12" s="56" t="inlineStr">
         <is>
-          <t>ファイル複数追加</t>
+          <t>ファイル共有</t>
         </is>
       </c>
       <c r="F12" s="56" t="inlineStr">
         <is>
-          <t>bulkPut</t>
+          <t>複数追加</t>
         </is>
       </c>
       <c r="G12" s="56" t="inlineStr">
         <is>
-          <t>files</t>
+          <t>一度に複数選択</t>
         </is>
       </c>
       <c r="H12" s="57" t="inlineStr">
@@ -7542,17 +7538,13 @@
       </c>
       <c r="I12" s="56" t="inlineStr">
         <is>
-          <t>複数ファイルを同時に追加</t>
-        </is>
-      </c>
-      <c r="J12" s="56" t="inlineStr">
-        <is>
-          <t>R-02のため手動必須</t>
-        </is>
-      </c>
+          <t>ファイル選択で複数ファイルを一度に選んで追加する</t>
+        </is>
+      </c>
+      <c r="J12" s="56" t="inlineStr"/>
       <c r="K12" s="56" t="inlineStr">
         <is>
-          <t>全件が保存され一覧とストアが一致。途中失敗時に中途半端な件数にならない</t>
+          <t>選んだ全部が一覧に追加される。もし失敗した場合も、一部だけ追加された中途半端な状態にならない</t>
         </is>
       </c>
       <c r="L12" s="57" t="inlineStr">
@@ -7587,17 +7579,17 @@
       </c>
       <c r="E13" s="56" t="inlineStr">
         <is>
-          <t>シード投入</t>
+          <t>設定</t>
         </is>
       </c>
       <c r="F13" s="56" t="inlineStr">
         <is>
-          <t>bulkPut</t>
+          <t>デモデータの投入</t>
         </is>
       </c>
       <c r="G13" s="56" t="inlineStr">
         <is>
-          <t>全ストア</t>
+          <t>初期化→投入</t>
         </is>
       </c>
       <c r="H13" s="57" t="inlineStr">
@@ -7607,13 +7599,13 @@
       </c>
       <c r="I13" s="56" t="inlineStr">
         <is>
-          <t>初期化→シード投入→件数確認</t>
+          <t>「初期化→デモデータを投入」を2回繰り返す</t>
         </is>
       </c>
       <c r="J13" s="56" t="inlineStr"/>
       <c r="K13" s="56" t="inlineStr">
         <is>
-          <t>全ストアが1トランザクションで投入され件数一致。初期化→再投入で件数が同一に戻る</t>
+          <t>毎回同じ件数（イベント40件・参加者24人）になる ※自動テストでも検証済み</t>
         </is>
       </c>
       <c r="L13" s="57" t="inlineStr">
@@ -7636,7 +7628,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="30.4" customHeight="1" s="53">
+    <row r="14" ht="43.59999999999999" customHeight="1" s="53">
       <c r="B14" s="58" t="n">
         <v>3</v>
       </c>
@@ -7648,17 +7640,17 @@
       </c>
       <c r="E14" s="56" t="inlineStr">
         <is>
-          <t>スキーマ移行</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="F14" s="56" t="inlineStr">
         <is>
-          <t>onupgradeneeded</t>
+          <t>データの引き継ぎ</t>
         </is>
       </c>
       <c r="G14" s="56" t="inlineStr">
         <is>
-          <t>v1→v5（create-if-missing）</t>
+          <t>バージョンアップ</t>
         </is>
       </c>
       <c r="H14" s="57" t="inlineStr">
@@ -7668,13 +7660,13 @@
       </c>
       <c r="I14" s="56" t="inlineStr">
         <is>
-          <t>旧バージョン相当の DB がある状態で v5 を開く</t>
+          <t>（手動での再現は不要）古い版のデータがある状態で新しい版を開いてもデータが消えないことは、自動テストが毎回検証している</t>
         </is>
       </c>
       <c r="J14" s="56" t="inlineStr"/>
       <c r="K14" s="56" t="inlineStr">
         <is>
-          <t>既存データを保持したまま新ストアが追加される。ticketTypes は削除済み</t>
+          <t>自動テストの結果（CI）が全件成功していること。手動実施は不要——結果欄に「自動」と記入する</t>
         </is>
       </c>
       <c r="L14" s="57" t="inlineStr">
@@ -7697,7 +7689,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="30.4" customHeight="1" s="53">
+    <row r="15" ht="43.59999999999999" customHeight="1" s="53">
       <c r="B15" s="58" t="n">
         <v>3</v>
       </c>
@@ -7709,17 +7701,17 @@
       </c>
       <c r="E15" s="56" t="inlineStr">
         <is>
-          <t>排他なしの既知制限</t>
+          <t>参加者の申込</t>
         </is>
       </c>
       <c r="F15" s="56" t="inlineStr">
         <is>
-          <t>同時申込</t>
+          <t>2画面から同時申込</t>
         </is>
       </c>
       <c r="G15" s="56" t="inlineStr">
         <is>
-          <t>2タブ</t>
+          <t>既知の制限</t>
         </is>
       </c>
       <c r="H15" s="57" t="inlineStr">
@@ -7729,7 +7721,7 @@
       </c>
       <c r="I15" s="56" t="inlineStr">
         <is>
-          <t>2タブで同時に残1のイベントへ申込</t>
+          <t>ブラウザのタブを2つ開き、残席1の同じイベントに両方からほぼ同時に申込む</t>
         </is>
       </c>
       <c r="J15" s="56" t="inlineStr">
@@ -7739,7 +7731,7 @@
       </c>
       <c r="K15" s="56" t="inlineStr">
         <is>
-          <t>定員超過が起こり得る（単一ブラウザ前提・排他なし）。結果を記録し、サーバ移行時の課題として受容</t>
+          <t>両方成功して定員を超えることが「起こり得る」。これは1台のパソコンで動かす前提による既知の制限なので、起きた事実を備考に記録するだけでよい（不具合ではない）</t>
         </is>
       </c>
       <c r="L15" s="57" t="inlineStr">
@@ -7749,7 +7741,7 @@
       </c>
       <c r="M15" s="56" t="inlineStr">
         <is>
-          <t>TX-07・詳細7-9</t>
+          <t>TX-07</t>
         </is>
       </c>
       <c r="N15" s="57" t="n"/>
@@ -7808,7 +7800,7 @@
     <col width="8.6640625" customWidth="1" style="42" min="1" max="1"/>
     <col width="6.58203125" customWidth="1" style="42" min="2" max="2"/>
     <col width="6.9140625" customWidth="1" style="42" min="3" max="4"/>
-    <col width="30" bestFit="1" customWidth="1" style="42" min="5" max="5"/>
+    <col width="26" bestFit="1" customWidth="1" style="42" min="5" max="5"/>
     <col width="22.75" bestFit="1" customWidth="1" style="42" min="6" max="6"/>
     <col width="27.25" bestFit="1" customWidth="1" style="42" min="7" max="7"/>
     <col width="8.6640625" customWidth="1" style="42" min="8" max="8"/>
@@ -7816,7 +7808,7 @@
     <col width="27.25" bestFit="1" customWidth="1" style="42" min="10" max="10"/>
     <col width="78.5" bestFit="1" customWidth="1" style="42" min="11" max="11"/>
     <col width="8.6640625" customWidth="1" style="42" min="12" max="12"/>
-    <col width="16" customWidth="1" style="42" min="13" max="13"/>
+    <col width="13" customWidth="1" style="42" min="13" max="13"/>
     <col width="9" customWidth="1" style="42" min="14" max="14"/>
     <col width="8.6640625" customWidth="1" style="42" min="15" max="17"/>
     <col width="25.25" bestFit="1" customWidth="1" style="42" min="18" max="18"/>
@@ -7826,7 +7818,7 @@
     <row r="1" ht="21" customHeight="1" s="53">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>●結合シナリオ（業務の一巡）</t>
+          <t>●通しシナリオ（業務の一巡）</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7830,7 @@
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>利用者の一連の操作でIF結合を通しで確認する（詳細設計書4章・受け入れ確認4-5 対応）</t>
+          <t>実際のイベント運営の流れを最初から最後まで通して、途中で止まらないことを確認する</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7842,7 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>各シナリオの事前条件は「条件」列に記載</t>
+          <t>必要な事前準備は各行の「条件」列に記載</t>
         </is>
       </c>
     </row>
@@ -7862,7 +7854,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>網羅性・IF境界のレビュー手順は結合試験仕様書 8章を参照</t>
+          <t>気になる点・引っかかった点は備考欄にメモし、あとで開発者に確認する</t>
         </is>
       </c>
     </row>
@@ -7980,7 +7972,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30.4" customHeight="1" s="53">
+    <row r="9" ht="70" customHeight="1" s="53">
       <c r="B9" s="58" t="n">
         <v>4</v>
       </c>
@@ -7992,12 +7984,12 @@
       </c>
       <c r="E9" s="60" t="inlineStr">
         <is>
-          <t>申込が実データで一周する</t>
+          <t>イベント運営を最初から最後まで通す</t>
         </is>
       </c>
       <c r="F9" s="60" t="inlineStr">
         <is>
-          <t>S-3→S-6→S-7→S-8→S-9→S-4</t>
+          <t>作成→公開→申込→受付→出力→中止</t>
         </is>
       </c>
       <c r="G9" s="60" t="inlineStr">
@@ -8012,17 +8004,17 @@
       </c>
       <c r="I9" s="62" t="inlineStr">
         <is>
-          <t>作成（画像添付・下書き）→締切&gt;開催日の検出→公開→参加者ビュー確認→告知発行→申込→再読込→残席減→検索・受付→修正→CSV→満席拒否→中止表示</t>
+          <t>イベントを作成（画像添付・下書き保存）→締切を開催日より後にして公開を試す（エラーになる）→直して公開→参加者ビューで見えることを確認→告知のURLと投稿文を発行→参加者として申込→ページを再読み込みしてもデータが残る→主催者側で申込が増え残席が減っている→氏名で検索して受付・取消→申込内容を修正→CSVを出力→定員まで申込むと以降は断られる→中止すると参加者側に「中止されました」と出る</t>
         </is>
       </c>
       <c r="J9" s="60" t="inlineStr">
         <is>
-          <t>シード投入済み</t>
+          <t>デモデータ投入済み</t>
         </is>
       </c>
       <c r="K9" s="62" t="inlineStr">
         <is>
-          <t>受け入れ確認 4-5 の14項目が通しで成立し、各ステップで IndexedDB のレコードが整合する</t>
+          <t>全部の手順が途中で止まらずに通り、画面の数字（申込数・残席・受付数）がどの画面でも矛盾しない</t>
         </is>
       </c>
       <c r="L9" s="57" t="inlineStr">
@@ -8032,7 +8024,7 @@
       </c>
       <c r="M9" s="56" t="inlineStr">
         <is>
-          <t>SC-01・4-5</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="N9" s="63" t="n"/>
@@ -8041,11 +8033,11 @@
       <c r="Q9" s="57" t="n"/>
       <c r="R9" s="59" t="inlineStr">
         <is>
-          <t>smoke「D-4 通し」の手動版</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30.4" customHeight="1" s="53">
+          <t>受け入れ確認の14項目に対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="43.59999999999999" customHeight="1" s="53">
       <c r="B10" s="58" t="n">
         <v>4</v>
       </c>
@@ -8057,17 +8049,17 @@
       </c>
       <c r="E10" s="60" t="inlineStr">
         <is>
-          <t>当日受付の分岐網羅</t>
+          <t>当日受付のすべてのパターン</t>
         </is>
       </c>
       <c r="F10" s="60" t="inlineStr">
         <is>
-          <t>S-4 申込タブ</t>
+          <t>申込一覧</t>
         </is>
       </c>
       <c r="G10" s="60" t="inlineStr">
         <is>
-          <t>氏名検索とQRの両経路</t>
+          <t>氏名検索とQRの両方</t>
         </is>
       </c>
       <c r="H10" s="61" t="inlineStr">
@@ -8077,17 +8069,17 @@
       </c>
       <c r="I10" s="62" t="inlineStr">
         <is>
-          <t>未受付・受付済み・キャンセル済みを用意→氏名検索で各分岐→QR読取で同じ分岐→存在しないQRも読ませる</t>
+          <t>未受付・受付済み・キャンセル済みの3人を用意→氏名検索でそれぞれ受付を試す→QRでも同じ3パターンを試す→別イベントのQRも読ませる</t>
         </is>
       </c>
       <c r="J10" s="60" t="inlineStr">
         <is>
-          <t>カメラ許可</t>
+          <t>カメラ付き端末</t>
         </is>
       </c>
       <c r="K10" s="62" t="inlineStr">
         <is>
-          <t>分岐ごとのメッセージが正しく、QR経路と検索経路が同じ setCheckin に合流して結果が一致する</t>
+          <t>受付できるのは未受付の人だけ。受付済みは「受付済みです」、キャンセル済みは「キャンセル済みです」、別イベントのQRは「このイベントの申込ではありません」と出る。検索とQRで結果が同じ</t>
         </is>
       </c>
       <c r="L10" s="57" t="inlineStr">
@@ -8097,7 +8089,7 @@
       </c>
       <c r="M10" s="56" t="inlineStr">
         <is>
-          <t>SC-02・F-24/F-95</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="N10" s="63" t="n"/>
@@ -8118,17 +8110,17 @@
       </c>
       <c r="E11" s="60" t="inlineStr">
         <is>
-          <t>URLからの復帰と共有</t>
+          <t>URLから開く全パターン</t>
         </is>
       </c>
       <c r="F11" s="60" t="inlineStr">
         <is>
-          <t>S-6／S-9</t>
+          <t>公開ページ・マイ申込</t>
         </is>
       </c>
       <c r="G11" s="60" t="inlineStr">
         <is>
-          <t>外部からの入口の全パターン</t>
+          <t>メールやSNSから来た人の入口</t>
         </is>
       </c>
       <c r="H11" s="61" t="inlineStr">
@@ -8138,13 +8130,13 @@
       </c>
       <c r="I11" s="62" t="inlineStr">
         <is>
-          <t>?ticket=（控えあり／なし／不正／キャンセル済み）→?event=（公開／限定公開／下書き／中止／不存在）→?preview=→URL巻き戻し→再読込</t>
+          <t>確認用URL（保存済み／未保存／でたらめ／キャンセル済み）→イベントURL（公開／限定公開／下書き／中止／存在しない）→プレビューURL→開いた後アドレスバーが元に戻る→その場で再読み込み</t>
         </is>
       </c>
       <c r="J11" s="60" t="inlineStr"/>
       <c r="K11" s="62" t="inlineStr">
         <is>
-          <t>?ticket= はログイン無しで通る。限定公開はURL直のみ表示。不正値で情報が漏れず、再読込で二重処理しない</t>
+          <t>確認用URLはログインしていなくても開ける。限定公開はURLを知っていれば見える。でたらめな値では他人の情報が出ない。再読み込みで同じ処理が二重に走らない</t>
         </is>
       </c>
       <c r="L11" s="57" t="inlineStr">
@@ -8154,7 +8146,7 @@
       </c>
       <c r="M11" s="56" t="inlineStr">
         <is>
-          <t>SC-03・F-97/F-65/F-107</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="N11" s="63" t="n"/>
@@ -8175,17 +8167,17 @@
       </c>
       <c r="E12" s="60" t="inlineStr">
         <is>
-          <t>イベント作成〜公開の保存境界</t>
+          <t>イベント作成の入力チェック</t>
         </is>
       </c>
       <c r="F12" s="60" t="inlineStr">
         <is>
-          <t>S-3 ウィザード</t>
+          <t>イベント作成</t>
         </is>
       </c>
       <c r="G12" s="60" t="inlineStr">
         <is>
-          <t>検証と保存の結合</t>
+          <t>保存できる・できないの境目</t>
         </is>
       </c>
       <c r="H12" s="61" t="inlineStr">
@@ -8195,13 +8187,13 @@
       </c>
       <c r="I12" s="62" t="inlineStr">
         <is>
-          <t>タイトル空→公開範囲の後退（公開済み）→締切&gt;開催日→問い合わせ先空で公開→定員&lt;有効申込→正常公開→複製→不可逆確認</t>
+          <t>イベント名空→公開済みの公開範囲を限定公開へ戻す→締切&gt;開催日→問い合わせ先を空で公開→定員&lt;申込数→正常に公開→複製→公開後に下書きへ戻せない・中止を取り消せないことを確認</t>
         </is>
       </c>
       <c r="J12" s="60" t="inlineStr"/>
       <c r="K12" s="62" t="inlineStr">
         <is>
-          <t>エラーの表示位置（直下／バナー／モーダル）が画面共通ルールどおりで、公開後は下書きに戻せない</t>
+          <t>エラーの出る場所が統一されている（入力欄の下／画面上部の赤いバナー／確認画面）。公開後は一方通行で戻せない</t>
         </is>
       </c>
       <c r="L12" s="57" t="inlineStr">
@@ -8211,7 +8203,7 @@
       </c>
       <c r="M12" s="56" t="inlineStr">
         <is>
-          <t>SC-04・F-40〜45b/F-94/F-98b</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="N12" s="63" t="n"/>
@@ -8232,17 +8224,17 @@
       </c>
       <c r="E13" s="60" t="inlineStr">
         <is>
-          <t>キャンセルと再申込</t>
+          <t>キャンセルと申込み直し</t>
         </is>
       </c>
       <c r="F13" s="60" t="inlineStr">
         <is>
-          <t>S-9／S-4</t>
+          <t>マイ申込・申込一覧</t>
         </is>
       </c>
       <c r="G13" s="60" t="inlineStr">
         <is>
-          <t>unique制約を張らない設計の確認</t>
+          <t>記録の残り方</t>
         </is>
       </c>
       <c r="H13" s="61" t="inlineStr">
@@ -8252,13 +8244,13 @@
       </c>
       <c r="I13" s="62" t="inlineStr">
         <is>
-          <t>申込→参加者側からキャンセル→残席回復→再申込→主催者側からもキャンセル→再申込→名簿で名寄せ確認</t>
+          <t>申込→参加者側でキャンセル→残席が戻る→同じ人が申込み直す→主催者側でもキャンセル→もう一度申込み直す→名簿で確認</t>
         </is>
       </c>
       <c r="J13" s="60" t="inlineStr"/>
       <c r="K13" s="62" t="inlineStr">
         <is>
-          <t>旧レコードは cancelled のまま残り、再申込は新トークン。名簿では同一人物に集約される</t>
+          <t>何度キャンセルしても申込み直せる。キャンセルの記録は消えずに残る。名簿では同じ人として1行にまとまっている</t>
         </is>
       </c>
       <c r="L13" s="57" t="inlineStr">
@@ -8268,7 +8260,7 @@
       </c>
       <c r="M13" s="56" t="inlineStr">
         <is>
-          <t>SC-05・F-42</t>
+          <t>SC-05</t>
         </is>
       </c>
       <c r="N13" s="63" t="n"/>
@@ -8289,17 +8281,17 @@
       </c>
       <c r="E14" s="60" t="inlineStr">
         <is>
-          <t>運営コミュニケーションの一巡</t>
+          <t>運営の連絡機能ひととおり</t>
         </is>
       </c>
       <c r="F14" s="60" t="inlineStr">
         <is>
-          <t>S-4／S-6／S-9</t>
+          <t>スレッド・Q&amp;A・お知らせ</t>
         </is>
       </c>
       <c r="G14" s="60" t="inlineStr">
         <is>
-          <t>messages 3チャネルと readStates</t>
+          <t>社内の相談と参加者への連絡</t>
         </is>
       </c>
       <c r="H14" s="61" t="inlineStr">
@@ -8309,13 +8301,13 @@
       </c>
       <c r="I14" s="62" t="inlineStr">
         <is>
-          <t>スレッド投稿→別イベントの未読と混ざらない→既読化→Q&amp;A登録・解消→お知らせ投稿→公開ページ・マイ申込で掲示→参加者に運営タブが無い</t>
+          <t>スレッドに投稿→別イベントに未読が付かないことを確認→開いて未読が消える→Q&amp;Aを登録・解決→お知らせを出す→公開ページとマイ申込に掲示される→参加者ビューに運営のタブが無い</t>
         </is>
       </c>
       <c r="J14" s="60" t="inlineStr"/>
       <c r="K14" s="62" t="inlineStr">
         <is>
-          <t>未読は保存せず都度算出され、チャネル間で混線しない</t>
+          <t>未読の数が正しく付き・消える。お知らせだけが参加者に見え、運営の中身は見えない</t>
         </is>
       </c>
       <c r="L14" s="57" t="inlineStr">
@@ -8325,7 +8317,7 @@
       </c>
       <c r="M14" s="56" t="inlineStr">
         <is>
-          <t>SC-06・E-4/F-31b</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="N14" s="63" t="n"/>
@@ -8334,7 +8326,7 @@
       <c r="Q14" s="57" t="n"/>
       <c r="R14" s="59" t="inlineStr"/>
     </row>
-    <row r="15" ht="30.4" customHeight="1" s="53">
+    <row r="15" ht="43.59999999999999" customHeight="1" s="53">
       <c r="B15" s="58" t="n">
         <v>4</v>
       </c>
@@ -8346,17 +8338,17 @@
       </c>
       <c r="E15" s="60" t="inlineStr">
         <is>
-          <t>運営タスクと進捗の伝播</t>
+          <t>タスクの進み具合が各画面に伝わる</t>
         </is>
       </c>
       <c r="F15" s="60" t="inlineStr">
         <is>
-          <t>S-4→S-2→S-1</t>
+          <t>タスク→一覧→ダッシュボード</t>
         </is>
       </c>
       <c r="G15" s="60" t="inlineStr">
         <is>
-          <t>tasks の更新伝播</t>
+          <t>進捗の連動</t>
         </is>
       </c>
       <c r="H15" s="61" t="inlineStr">
@@ -8366,13 +8358,13 @@
       </c>
       <c r="I15" s="62" t="inlineStr">
         <is>
-          <t>作成（期限あり・なし）→ドラッグ→リロードで順序→タイムライン→期限超過（処理済・完了は除外）→一覧カード→ダッシュボード</t>
+          <t>タスクを作成（期限あり・なし）→ドラッグで進める→再読み込み→タイムライン表示→期限を昨日にして「期限超過」の表示（処理済・完了は超過に数えない）→イベント一覧の準備バー→ダッシュボードの要対応</t>
         </is>
       </c>
       <c r="J15" s="60" t="inlineStr"/>
       <c r="K15" s="62" t="inlineStr">
         <is>
-          <t>進捗が S-4 チップ→一覧カードの進捗バー・要対応見出し→ダッシュボード要対応の残作業表示まで伝播する</t>
+          <t>タスクの状態が、詳細画面の進捗チップ→一覧カードの準備バー→ダッシュボードの残作業表示まで一貫して連動する</t>
         </is>
       </c>
       <c r="L15" s="57" t="inlineStr">
@@ -8382,7 +8374,7 @@
       </c>
       <c r="M15" s="56" t="inlineStr">
         <is>
-          <t>SC-07・E-2/F-31</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="N15" s="63" t="n"/>
@@ -8391,7 +8383,7 @@
       <c r="Q15" s="57" t="n"/>
       <c r="R15" s="59" t="inlineStr"/>
     </row>
-    <row r="16" ht="30.4" customHeight="1" s="53">
+    <row r="16" ht="43.59999999999999" customHeight="1" s="53">
       <c r="B16" s="58" t="n">
         <v>4</v>
       </c>
@@ -8403,17 +8395,17 @@
       </c>
       <c r="E16" s="60" t="inlineStr">
         <is>
-          <t>ログインとトークン認可の併存</t>
+          <t>マイ申込のログイン</t>
         </is>
       </c>
       <c r="F16" s="60" t="inlineStr">
         <is>
-          <t>S-9</t>
+          <t>マイ申込</t>
         </is>
       </c>
       <c r="G16" s="60" t="inlineStr">
         <is>
-          <t>F-107 の2本立て</t>
+          <t>ログインが要る所・要らない所</t>
         </is>
       </c>
       <c r="H16" s="61" t="inlineStr">
@@ -8423,17 +8415,17 @@
       </c>
       <c r="I16" s="62" t="inlineStr">
         <is>
-          <t>未ログインでマイ申込→ログイン→一覧が personId 起点→ログアウト→?ticket= はログイン無し→誤パスワード→再読込で消える</t>
+          <t>ログインせずマイ申込を開く→ログインを求められる→「abc@example.com」「abc123」でログイン→本人の分だけ並ぶ→ログアウト→確認用URLはログイン無しで開ける→間違ったパスワードを試す→再読み込み</t>
         </is>
       </c>
       <c r="J16" s="60" t="inlineStr">
         <is>
-          <t>田中 太郎 abc@example.com / abc123</t>
+          <t>デモデータ投入済み</t>
         </is>
       </c>
       <c r="K16" s="62" t="inlineStr">
         <is>
-          <t>一覧はログイン、個別はトークンという併存が崩れず、限界の注記が画面に出ている</t>
+          <t>一覧はログインが必要、URLから開く1件は不要、という使い分けが成立している。誤入力は「メールアドレスまたはパスワードが違います」（どちらが違うかは言わない）。再読み込みでログアウト状態に戻る</t>
         </is>
       </c>
       <c r="L16" s="57" t="inlineStr">
@@ -8443,7 +8435,7 @@
       </c>
       <c r="M16" s="56" t="inlineStr">
         <is>
-          <t>SC-08・F-107/F-107b</t>
+          <t>SC-08</t>
         </is>
       </c>
       <c r="N16" s="63" t="n"/>
@@ -8452,7 +8444,7 @@
       <c r="Q16" s="57" t="n"/>
       <c r="R16" s="59" t="inlineStr"/>
     </row>
-    <row r="17" ht="30.4" customHeight="1" s="53">
+    <row r="17" ht="43.59999999999999" customHeight="1" s="53">
       <c r="B17" s="58" t="n">
         <v>4</v>
       </c>
@@ -8469,12 +8461,12 @@
       </c>
       <c r="F17" s="60" t="inlineStr">
         <is>
-          <t>S-10</t>
+          <t>参加者名簿</t>
         </is>
       </c>
       <c r="G17" s="60" t="inlineStr">
         <is>
-          <t>横断集計と出力境界</t>
+          <t>集計と出力</t>
         </is>
       </c>
       <c r="H17" s="61" t="inlineStr">
@@ -8484,13 +8476,13 @@
       </c>
       <c r="I17" s="62" t="inlineStr">
         <is>
-          <t>パスワード admin→集計値をシードと突合→正規化検索→CSV出力→表計算で開く→参加者ビュー切替でロック復帰</t>
+          <t>パスワード「admin」で解除→集計値をデモデータと突き合わせ→ひらがな・カタカナどちらでも検索できる→CSVを出力してExcelで開く（文字化けしない・数式にならない）→参加者ビューへ切替→戻るとロックされている</t>
         </is>
       </c>
       <c r="J17" s="60" t="inlineStr"/>
       <c r="K17" s="62" t="inlineStr">
         <is>
-          <t>集計が一致し、CSV は BOM・CRLF・数式無害化を満たす</t>
+          <t>集計が合っており、CSVがそのままExcelで正しく読める。ロックの掛かり直しも機能する</t>
         </is>
       </c>
       <c r="L17" s="57" t="inlineStr">
@@ -8500,7 +8492,7 @@
       </c>
       <c r="M17" s="56" t="inlineStr">
         <is>
-          <t>SC-09・F-92/F-101/F-49b</t>
+          <t>SC-09</t>
         </is>
       </c>
       <c r="N17" s="63" t="n"/>
@@ -8521,17 +8513,17 @@
       </c>
       <c r="E18" s="60" t="inlineStr">
         <is>
-          <t>時期境界の網羅</t>
+          <t>時期の表示が3箇所で一致する</t>
         </is>
       </c>
       <c r="F18" s="60" t="inlineStr">
         <is>
-          <t>S-6／参加者一覧／S-2</t>
+          <t>一覧・公開ページ・主催者一覧</t>
         </is>
       </c>
       <c r="G18" s="60" t="inlineStr">
         <is>
-          <t>timing 5相×表示先3箇所</t>
+          <t>受付前〜中止の見え方</t>
         </is>
       </c>
       <c r="H18" s="61" t="inlineStr">
@@ -8541,13 +8533,13 @@
       </c>
       <c r="I18" s="62" t="inlineStr">
         <is>
-          <t>受付前・受付中・満席・受付終了・開催済・中止を用意→各表示先を確認→締切 23:59／翌 0:00 を跨いで再確認</t>
+          <t>受付前・受付中・満席・受付終了・開催済・中止の6状態を用意→「イベントを探す」→各公開ページのボタン→主催者の一覧バッジ→締切日の前後で表示が切り替わることも確認</t>
         </is>
       </c>
       <c r="J18" s="60" t="inlineStr"/>
       <c r="K18" s="62" t="inlineStr">
         <is>
-          <t>「イベントを探す」は受付中・受付前のみ（満席は出す）。時期は保存されず都度算出で3箇所が整合する</t>
+          <t>3箇所の表示が食い違わない。「イベントを探す」に出るのは受付中・受付前・満席のみ</t>
         </is>
       </c>
       <c r="L18" s="57" t="inlineStr">
@@ -8557,7 +8549,7 @@
       </c>
       <c r="M18" s="56" t="inlineStr">
         <is>
-          <t>SC-10・F-83b/F-45b</t>
+          <t>SC-10</t>
         </is>
       </c>
       <c r="N18" s="63" t="n"/>
@@ -8578,7 +8570,7 @@
       </c>
       <c r="E19" s="60" t="inlineStr">
         <is>
-          <t>外部連携の劣化</t>
+          <t>通信が無くても主要業務が続く</t>
         </is>
       </c>
       <c r="F19" s="60" t="inlineStr">
@@ -8588,7 +8580,7 @@
       </c>
       <c r="G19" s="60" t="inlineStr">
         <is>
-          <t>異常系の通し</t>
+          <t>障害時の通しの動き</t>
         </is>
       </c>
       <c r="H19" s="61" t="inlineStr">
@@ -8598,17 +8590,17 @@
       </c>
       <c r="I19" s="62" t="inlineStr">
         <is>
-          <t>オフライン化→申込・氏名検索受付・CSV が動く→QR読取のみ失敗→フォント不達→カメラ拒否→復帰で回復</t>
+          <t>F12 → Network → Offline にする→画面表示・申込・氏名検索での受付・CSV出力を試す→QR読み取りだけ失敗する→書体が標準に変わる→カメラ拒否→氏名検索で代替→Online に戻すとQRも回復</t>
         </is>
       </c>
       <c r="J19" s="60" t="inlineStr">
         <is>
-          <t>DevToolsで再現</t>
+          <t>デモデータ投入済み</t>
         </is>
       </c>
       <c r="K19" s="62" t="inlineStr">
         <is>
-          <t>劣化が局所化され、誤動作ではなくエラー提示になる（オフライン動作自体は要件外）</t>
+          <t>受付・申込などの主要業務は通信無しでも続けられ、QR読み取りなど一部だけが分かるエラーで止まる</t>
         </is>
       </c>
       <c r="L19" s="57" t="inlineStr">
@@ -8618,7 +8610,7 @@
       </c>
       <c r="M19" s="56" t="inlineStr">
         <is>
-          <t>SC-11・R-01</t>
+          <t>SC-11</t>
         </is>
       </c>
       <c r="N19" s="63" t="n"/>
@@ -8639,17 +8631,17 @@
       </c>
       <c r="E20" s="60" t="inlineStr">
         <is>
-          <t>データの永続と移行</t>
+          <t>データが消えない・消せる</t>
         </is>
       </c>
       <c r="F20" s="60" t="inlineStr">
         <is>
-          <t>S-5／共通</t>
+          <t>設定・全画面</t>
         </is>
       </c>
       <c r="G20" s="60" t="inlineStr">
         <is>
-          <t>永続層の生存境界</t>
+          <t>保存の一生</t>
         </is>
       </c>
       <c r="H20" s="61" t="inlineStr">
@@ -8659,13 +8651,13 @@
       </c>
       <c r="I20" s="62" t="inlineStr">
         <is>
-          <t>データ作成→再読込で保持→初期化（確認モーダル）→空を確認→シード再投入→CI の v5 移行検査</t>
+          <t>申込などのデータを作る→ページを再読み込みして残っている→初期化（確認画面あり）→空になっている→デモデータを投入→また使える</t>
         </is>
       </c>
       <c r="J20" s="60" t="inlineStr"/>
       <c r="K20" s="62" t="inlineStr">
         <is>
-          <t>再読込でデータが保持され、初期化→再投入が受け入れ確認 4-5(14) どおり通る</t>
+          <t>再読み込みではデータが残り、初期化では意図したときだけ消える。初期化→投入がいつでもやり直せる</t>
         </is>
       </c>
       <c r="L20" s="57" t="inlineStr">
@@ -8675,7 +8667,7 @@
       </c>
       <c r="M20" s="56" t="inlineStr">
         <is>
-          <t>SC-12・4-5(1)(7)(14)</t>
+          <t>SC-12</t>
         </is>
       </c>
       <c r="N20" s="63" t="n"/>

--- a/docs/結合試験項目一覧.xlsx
+++ b/docs/結合試験項目一覧.xlsx
@@ -452,7 +452,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -638,6 +638,12 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3926,15 +3932,15 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="42" customHeight="1" s="53">
       <c r="B5" s="12" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>IF・参考資料列はレビュー用の記号（実施時は無視してよい）</t>
+      <c r="C5" s="64" t="inlineStr">
+        <is>
+          <t>IF・参考資料列はレビュー用の記号（実施時は無視してよい）　※備考欄の見方 — 自動: 自動テストが毎回検証（手動実施は不要）／自動＋手動: 動きは自動テストで検証済み・画面の見え方や実機での操作だけ確認する／手動: 自動では確認できないため必ず人が確認する</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4113,11 @@
       <c r="O9" s="57" t="n"/>
       <c r="P9" s="37" t="n"/>
       <c r="Q9" s="57" t="n"/>
-      <c r="R9" s="56" t="inlineStr"/>
+      <c r="R9" s="56" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="30.4" customHeight="1" s="53">
       <c r="B10" s="8" t="n">
@@ -4168,7 +4178,11 @@
       <c r="O10" s="57" t="n"/>
       <c r="P10" s="37" t="n"/>
       <c r="Q10" s="57" t="n"/>
-      <c r="R10" s="56" t="inlineStr"/>
+      <c r="R10" s="56" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1" s="53">
       <c r="B11" s="8" t="n">
@@ -4229,7 +4243,11 @@
       <c r="O11" s="57" t="n"/>
       <c r="P11" s="37" t="n"/>
       <c r="Q11" s="57" t="n"/>
-      <c r="R11" s="56" t="inlineStr"/>
+      <c r="R11" s="56" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1" s="53">
       <c r="B12" s="8" t="n">
@@ -4286,7 +4304,11 @@
       <c r="O12" s="57" t="n"/>
       <c r="P12" s="37" t="n"/>
       <c r="Q12" s="57" t="n"/>
-      <c r="R12" s="56" t="inlineStr"/>
+      <c r="R12" s="56" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1" s="53">
       <c r="B13" s="8" t="n">
@@ -4343,7 +4365,11 @@
       <c r="O13" s="57" t="n"/>
       <c r="P13" s="37" t="n"/>
       <c r="Q13" s="57" t="n"/>
-      <c r="R13" s="56" t="inlineStr"/>
+      <c r="R13" s="56" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1" s="53">
       <c r="B14" s="8" t="n">
@@ -4400,7 +4426,11 @@
       <c r="O14" s="57" t="n"/>
       <c r="P14" s="37" t="n"/>
       <c r="Q14" s="57" t="n"/>
-      <c r="R14" s="56" t="inlineStr"/>
+      <c r="R14" s="56" t="inlineStr">
+        <is>
+          <t>自動</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1" s="53">
       <c r="B15" s="8" t="n">
@@ -4457,7 +4487,11 @@
       <c r="O15" s="57" t="n"/>
       <c r="P15" s="37" t="n"/>
       <c r="Q15" s="57" t="n"/>
-      <c r="R15" s="56" t="inlineStr"/>
+      <c r="R15" s="56" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1" s="53">
       <c r="B16" s="8" t="n">
@@ -4514,7 +4548,11 @@
       <c r="O16" s="57" t="n"/>
       <c r="P16" s="37" t="n"/>
       <c r="Q16" s="57" t="n"/>
-      <c r="R16" s="56" t="inlineStr"/>
+      <c r="R16" s="56" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1" s="53">
       <c r="B17" s="8" t="n">
@@ -4571,7 +4609,11 @@
       <c r="O17" s="57" t="n"/>
       <c r="P17" s="37" t="n"/>
       <c r="Q17" s="57" t="n"/>
-      <c r="R17" s="56" t="inlineStr"/>
+      <c r="R17" s="56" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1" s="53">
       <c r="B18" s="8" t="n">
@@ -4628,7 +4670,11 @@
       <c r="O18" s="57" t="n"/>
       <c r="P18" s="37" t="n"/>
       <c r="Q18" s="57" t="n"/>
-      <c r="R18" s="56" t="inlineStr"/>
+      <c r="R18" s="56" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="14" customHeight="1" s="53"/>
     <row r="30" ht="14" customHeight="1" s="53"/>
@@ -4713,15 +4759,15 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" s="53">
+    <row r="5" ht="42" customHeight="1" s="53">
       <c r="B5" s="12" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="C5" s="30" t="inlineStr">
-        <is>
-          <t>なし</t>
+      <c r="C5" s="65" t="inlineStr">
+        <is>
+          <t>なし　※備考欄の見方 — 自動: 自動テストが毎回検証（手動実施は不要）／自動＋手動: 動きは自動テストで検証済み・画面の見え方や実機での操作だけ確認する／手動: 自動では確認できないため必ず人が確認する</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4940,11 @@
       <c r="O9" s="57" t="n"/>
       <c r="P9" s="37" t="n"/>
       <c r="Q9" s="57" t="n"/>
-      <c r="R9" s="59" t="inlineStr"/>
+      <c r="R9" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="30.4" customHeight="1" s="53">
       <c r="B10" s="58" t="n">
@@ -4955,7 +5005,11 @@
       <c r="O10" s="57" t="n"/>
       <c r="P10" s="37" t="n"/>
       <c r="Q10" s="57" t="n"/>
-      <c r="R10" s="59" t="inlineStr"/>
+      <c r="R10" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1" s="53">
       <c r="B11" s="58" t="n">
@@ -5008,7 +5062,11 @@
       <c r="O11" s="57" t="n"/>
       <c r="P11" s="37" t="n"/>
       <c r="Q11" s="57" t="n"/>
-      <c r="R11" s="59" t="inlineStr"/>
+      <c r="R11" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30.4" customHeight="1" s="53">
       <c r="B12" s="58" t="n">
@@ -5065,7 +5123,11 @@
       <c r="O12" s="57" t="n"/>
       <c r="P12" s="37" t="n"/>
       <c r="Q12" s="57" t="n"/>
-      <c r="R12" s="59" t="inlineStr"/>
+      <c r="R12" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1" s="53">
       <c r="B13" s="58" t="n">
@@ -5122,7 +5184,11 @@
       <c r="O13" s="57" t="n"/>
       <c r="P13" s="37" t="n"/>
       <c r="Q13" s="57" t="n"/>
-      <c r="R13" s="59" t="inlineStr"/>
+      <c r="R13" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1" s="53">
       <c r="B14" s="58" t="n">
@@ -5179,7 +5245,11 @@
       <c r="O14" s="57" t="n"/>
       <c r="P14" s="37" t="n"/>
       <c r="Q14" s="57" t="n"/>
-      <c r="R14" s="59" t="inlineStr"/>
+      <c r="R14" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1" s="53">
       <c r="B15" s="58" t="n">
@@ -5240,7 +5310,11 @@
       <c r="O15" s="57" t="n"/>
       <c r="P15" s="37" t="n"/>
       <c r="Q15" s="57" t="n"/>
-      <c r="R15" s="59" t="inlineStr"/>
+      <c r="R15" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1" s="53">
       <c r="B16" s="58" t="n">
@@ -5297,7 +5371,11 @@
       <c r="O16" s="57" t="n"/>
       <c r="P16" s="37" t="n"/>
       <c r="Q16" s="57" t="n"/>
-      <c r="R16" s="59" t="inlineStr"/>
+      <c r="R16" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1" s="53">
       <c r="B17" s="58" t="n">
@@ -5354,7 +5432,11 @@
       <c r="O17" s="57" t="n"/>
       <c r="P17" s="37" t="n"/>
       <c r="Q17" s="57" t="n"/>
-      <c r="R17" s="59" t="inlineStr"/>
+      <c r="R17" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1" s="53">
       <c r="B18" s="58" t="n">
@@ -5411,7 +5493,11 @@
       <c r="O18" s="57" t="n"/>
       <c r="P18" s="37" t="n"/>
       <c r="Q18" s="57" t="n"/>
-      <c r="R18" s="59" t="inlineStr"/>
+      <c r="R18" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30.4" customHeight="1" s="53">
       <c r="B19" s="58" t="n">
@@ -5468,7 +5554,11 @@
       <c r="O19" s="57" t="n"/>
       <c r="P19" s="37" t="n"/>
       <c r="Q19" s="57" t="n"/>
-      <c r="R19" s="59" t="inlineStr"/>
+      <c r="R19" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30.4" customHeight="1" s="53">
       <c r="B20" s="58" t="n">
@@ -5529,7 +5619,11 @@
       <c r="O20" s="57" t="n"/>
       <c r="P20" s="37" t="n"/>
       <c r="Q20" s="57" t="n"/>
-      <c r="R20" s="59" t="inlineStr"/>
+      <c r="R20" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1" s="53">
       <c r="B21" s="58" t="n">
@@ -5590,7 +5684,11 @@
       <c r="O21" s="57" t="n"/>
       <c r="P21" s="37" t="n"/>
       <c r="Q21" s="57" t="n"/>
-      <c r="R21" s="59" t="inlineStr"/>
+      <c r="R21" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1" s="53"/>
     <row r="23" ht="18" customHeight="1" s="53"/>
@@ -5683,15 +5781,15 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" s="53">
+    <row r="5" ht="42" customHeight="1" s="53">
       <c r="B5" s="12" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="C5" s="30" t="inlineStr">
-        <is>
-          <t>通信を遮断する行は、やり方（F12 → Network での操作）を手順欄に記載</t>
+      <c r="C5" s="65" t="inlineStr">
+        <is>
+          <t>通信を遮断する行は、やり方（F12 → Network での操作）を手順欄に記載　※備考欄の見方 — 自動: 自動テストが毎回検証（手動実施は不要）／自動＋手動: 動きは自動テストで検証済み・画面の見え方や実機での操作だけ確認する／手動: 自動では確認できないため必ず人が確認する</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5962,11 @@
       <c r="O9" s="57" t="n"/>
       <c r="P9" s="37" t="n"/>
       <c r="Q9" s="57" t="n"/>
-      <c r="R9" s="59" t="inlineStr"/>
+      <c r="R9" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1" s="53">
       <c r="B10" s="58" t="n">
@@ -5921,7 +6023,11 @@
       <c r="O10" s="57" t="n"/>
       <c r="P10" s="37" t="n"/>
       <c r="Q10" s="57" t="n"/>
-      <c r="R10" s="59" t="inlineStr"/>
+      <c r="R10" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1" s="53">
       <c r="B11" s="58" t="n">
@@ -5978,7 +6084,11 @@
       <c r="O11" s="57" t="n"/>
       <c r="P11" s="37" t="n"/>
       <c r="Q11" s="57" t="n"/>
-      <c r="R11" s="59" t="inlineStr"/>
+      <c r="R11" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1" s="53">
       <c r="B12" s="58" t="n">
@@ -6035,7 +6145,11 @@
       <c r="O12" s="57" t="n"/>
       <c r="P12" s="37" t="n"/>
       <c r="Q12" s="57" t="n"/>
-      <c r="R12" s="59" t="inlineStr"/>
+      <c r="R12" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1" s="53">
       <c r="B13" s="58" t="n">
@@ -6096,7 +6210,11 @@
       <c r="O13" s="57" t="n"/>
       <c r="P13" s="37" t="n"/>
       <c r="Q13" s="57" t="n"/>
-      <c r="R13" s="59" t="inlineStr"/>
+      <c r="R13" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1" s="53">
       <c r="B14" s="58" t="n">
@@ -6153,7 +6271,11 @@
       <c r="O14" s="57" t="n"/>
       <c r="P14" s="37" t="n"/>
       <c r="Q14" s="57" t="n"/>
-      <c r="R14" s="59" t="inlineStr"/>
+      <c r="R14" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1" s="53">
       <c r="B15" s="58" t="n">
@@ -6210,7 +6332,11 @@
       <c r="O15" s="57" t="n"/>
       <c r="P15" s="37" t="n"/>
       <c r="Q15" s="57" t="n"/>
-      <c r="R15" s="59" t="inlineStr"/>
+      <c r="R15" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1" s="53">
       <c r="B16" s="58" t="n">
@@ -6271,7 +6397,11 @@
       <c r="O16" s="57" t="n"/>
       <c r="P16" s="37" t="n"/>
       <c r="Q16" s="57" t="n"/>
-      <c r="R16" s="59" t="inlineStr"/>
+      <c r="R16" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1" s="53">
       <c r="B17" s="58" t="n">
@@ -6328,7 +6458,11 @@
       <c r="O17" s="57" t="n"/>
       <c r="P17" s="37" t="n"/>
       <c r="Q17" s="57" t="n"/>
-      <c r="R17" s="59" t="inlineStr"/>
+      <c r="R17" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1" s="53">
       <c r="B18" s="58" t="n">
@@ -6389,7 +6523,11 @@
       <c r="O18" s="57" t="n"/>
       <c r="P18" s="37" t="n"/>
       <c r="Q18" s="57" t="n"/>
-      <c r="R18" s="59" t="inlineStr"/>
+      <c r="R18" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1" s="53">
       <c r="B19" s="58" t="n">
@@ -6446,7 +6584,11 @@
       <c r="O19" s="57" t="n"/>
       <c r="P19" s="37" t="n"/>
       <c r="Q19" s="57" t="n"/>
-      <c r="R19" s="59" t="inlineStr"/>
+      <c r="R19" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1" s="53">
       <c r="B20" s="58" t="n">
@@ -6503,7 +6645,11 @@
       <c r="O20" s="57" t="n"/>
       <c r="P20" s="37" t="n"/>
       <c r="Q20" s="57" t="n"/>
-      <c r="R20" s="59" t="inlineStr"/>
+      <c r="R20" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1" s="53">
       <c r="B21" s="58" t="n">
@@ -6560,7 +6706,11 @@
       <c r="O21" s="57" t="n"/>
       <c r="P21" s="37" t="n"/>
       <c r="Q21" s="57" t="n"/>
-      <c r="R21" s="59" t="inlineStr"/>
+      <c r="R21" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30.4" customHeight="1" s="53">
       <c r="B22" s="58" t="n">
@@ -6621,7 +6771,11 @@
       <c r="O22" s="57" t="n"/>
       <c r="P22" s="37" t="n"/>
       <c r="Q22" s="57" t="n"/>
-      <c r="R22" s="59" t="inlineStr"/>
+      <c r="R22" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="30.4" customHeight="1" s="53">
       <c r="B23" s="58" t="n">
@@ -6682,7 +6836,11 @@
       <c r="O23" s="57" t="n"/>
       <c r="P23" s="37" t="n"/>
       <c r="Q23" s="57" t="n"/>
-      <c r="R23" s="59" t="inlineStr"/>
+      <c r="R23" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="30.4" customHeight="1" s="53">
       <c r="B24" s="58" t="n">
@@ -6743,7 +6901,11 @@
       <c r="O24" s="57" t="n"/>
       <c r="P24" s="37" t="n"/>
       <c r="Q24" s="57" t="n"/>
-      <c r="R24" s="59" t="inlineStr"/>
+      <c r="R24" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30.4" customHeight="1" s="53">
       <c r="B25" s="58" t="n">
@@ -6800,7 +6962,11 @@
       <c r="O25" s="57" t="n"/>
       <c r="P25" s="37" t="n"/>
       <c r="Q25" s="57" t="n"/>
-      <c r="R25" s="59" t="inlineStr"/>
+      <c r="R25" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="18" customHeight="1" s="53">
       <c r="B26" s="58" t="n">
@@ -6861,7 +7027,11 @@
       <c r="O26" s="57" t="n"/>
       <c r="P26" s="37" t="n"/>
       <c r="Q26" s="57" t="n"/>
-      <c r="R26" s="59" t="inlineStr"/>
+      <c r="R26" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1" s="53">
       <c r="B27" s="58" t="n">
@@ -6918,7 +7088,11 @@
       <c r="O27" s="57" t="n"/>
       <c r="P27" s="37" t="n"/>
       <c r="Q27" s="57" t="n"/>
-      <c r="R27" s="59" t="inlineStr"/>
+      <c r="R27" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="53">
       <c r="B28" s="58" t="n">
@@ -6975,7 +7149,11 @@
       <c r="O28" s="57" t="n"/>
       <c r="P28" s="37" t="n"/>
       <c r="Q28" s="57" t="n"/>
-      <c r="R28" s="59" t="inlineStr"/>
+      <c r="R28" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="30.4" customHeight="1" s="53">
       <c r="B29" s="58" t="n">
@@ -7036,7 +7214,11 @@
       <c r="O29" s="57" t="n"/>
       <c r="P29" s="37" t="n"/>
       <c r="Q29" s="57" t="n"/>
-      <c r="R29" s="59" t="inlineStr"/>
+      <c r="R29" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="18" customHeight="1" s="53">
       <c r="B30" s="58" t="n">
@@ -7093,7 +7275,11 @@
       <c r="O30" s="57" t="n"/>
       <c r="P30" s="37" t="n"/>
       <c r="Q30" s="57" t="n"/>
-      <c r="R30" s="59" t="inlineStr"/>
+      <c r="R30" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="53">
       <c r="B31" s="58" t="n">
@@ -7150,7 +7336,11 @@
       <c r="O31" s="57" t="n"/>
       <c r="P31" s="37" t="n"/>
       <c r="Q31" s="57" t="n"/>
-      <c r="R31" s="59" t="inlineStr"/>
+      <c r="R31" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="30.4" customHeight="1" s="53">
       <c r="B32" s="58" t="n">
@@ -7207,7 +7397,11 @@
       <c r="O32" s="57" t="n"/>
       <c r="P32" s="37" t="n"/>
       <c r="Q32" s="57" t="n"/>
-      <c r="R32" s="59" t="inlineStr"/>
+      <c r="R32" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="18" customHeight="1" s="53">
       <c r="B33" s="58" t="n">
@@ -7264,7 +7458,11 @@
       <c r="O33" s="57" t="n"/>
       <c r="P33" s="37" t="n"/>
       <c r="Q33" s="57" t="n"/>
-      <c r="R33" s="59" t="inlineStr"/>
+      <c r="R33" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="53">
       <c r="B34" s="58" t="n">
@@ -7321,7 +7519,11 @@
       <c r="O34" s="57" t="n"/>
       <c r="P34" s="37" t="n"/>
       <c r="Q34" s="57" t="n"/>
-      <c r="R34" s="59" t="inlineStr"/>
+      <c r="R34" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="53">
       <c r="B35" s="58" t="n">
@@ -7378,7 +7580,11 @@
       <c r="O35" s="57" t="n"/>
       <c r="P35" s="37" t="n"/>
       <c r="Q35" s="57" t="n"/>
-      <c r="R35" s="59" t="inlineStr"/>
+      <c r="R35" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="18" customHeight="1" s="53">
       <c r="B36" s="58" t="n">
@@ -7435,7 +7641,11 @@
       <c r="O36" s="57" t="n"/>
       <c r="P36" s="37" t="n"/>
       <c r="Q36" s="57" t="n"/>
-      <c r="R36" s="59" t="inlineStr"/>
+      <c r="R36" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="18" customHeight="1" s="53">
       <c r="B37" s="58" t="n">
@@ -7492,7 +7702,11 @@
       <c r="O37" s="57" t="n"/>
       <c r="P37" s="37" t="n"/>
       <c r="Q37" s="57" t="n"/>
-      <c r="R37" s="59" t="inlineStr"/>
+      <c r="R37" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="18" customHeight="1" s="53">
       <c r="B38" s="58" t="n">
@@ -7549,7 +7763,11 @@
       <c r="O38" s="57" t="n"/>
       <c r="P38" s="37" t="n"/>
       <c r="Q38" s="57" t="n"/>
-      <c r="R38" s="59" t="inlineStr"/>
+      <c r="R38" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="18" customHeight="1" s="53">
       <c r="B39" s="58" t="n">
@@ -7606,7 +7824,11 @@
       <c r="O39" s="57" t="n"/>
       <c r="P39" s="37" t="n"/>
       <c r="Q39" s="57" t="n"/>
-      <c r="R39" s="59" t="inlineStr"/>
+      <c r="R39" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="30.4" customHeight="1" s="53">
       <c r="B40" s="58" t="n">
@@ -7667,7 +7889,11 @@
       <c r="O40" s="57" t="n"/>
       <c r="P40" s="37" t="n"/>
       <c r="Q40" s="57" t="n"/>
-      <c r="R40" s="59" t="inlineStr"/>
+      <c r="R40" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="30.4" customHeight="1" s="53">
       <c r="B41" s="58" t="n">
@@ -7724,7 +7950,11 @@
       <c r="O41" s="57" t="n"/>
       <c r="P41" s="37" t="n"/>
       <c r="Q41" s="57" t="n"/>
-      <c r="R41" s="59" t="inlineStr"/>
+      <c r="R41" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="18" customHeight="1" s="53">
       <c r="B42" s="58" t="n">
@@ -7781,7 +8011,11 @@
       <c r="O42" s="57" t="n"/>
       <c r="P42" s="37" t="n"/>
       <c r="Q42" s="57" t="n"/>
-      <c r="R42" s="59" t="inlineStr"/>
+      <c r="R42" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="18" customHeight="1" s="53">
       <c r="B43" s="58" t="n">
@@ -7838,7 +8072,11 @@
       <c r="O43" s="57" t="n"/>
       <c r="P43" s="37" t="n"/>
       <c r="Q43" s="57" t="n"/>
-      <c r="R43" s="59" t="inlineStr"/>
+      <c r="R43" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="18" customHeight="1" s="53">
       <c r="B44" s="58" t="n">
@@ -7899,7 +8137,11 @@
       <c r="O44" s="57" t="n"/>
       <c r="P44" s="37" t="n"/>
       <c r="Q44" s="57" t="n"/>
-      <c r="R44" s="59" t="inlineStr"/>
+      <c r="R44" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="18" customHeight="1" s="53">
       <c r="B45" s="58" t="n">
@@ -7956,7 +8198,11 @@
       <c r="O45" s="57" t="n"/>
       <c r="P45" s="37" t="n"/>
       <c r="Q45" s="57" t="n"/>
-      <c r="R45" s="59" t="inlineStr"/>
+      <c r="R45" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="18" customHeight="1" s="53">
       <c r="B46" s="58" t="n">
@@ -8013,7 +8259,11 @@
       <c r="O46" s="57" t="n"/>
       <c r="P46" s="37" t="n"/>
       <c r="Q46" s="57" t="n"/>
-      <c r="R46" s="59" t="inlineStr"/>
+      <c r="R46" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="18" customHeight="1" s="53">
       <c r="B47" s="58" t="n">
@@ -8074,9 +8324,13 @@
       <c r="O47" s="57" t="n"/>
       <c r="P47" s="37" t="n"/>
       <c r="Q47" s="57" t="n"/>
-      <c r="R47" s="59" t="inlineStr"/>
-    </row>
-    <row r="48" ht="18" customHeight="1" s="53">
+      <c r="R47" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30.4" customHeight="1" s="53">
       <c r="B48" s="58" t="n">
         <v>3</v>
       </c>
@@ -8133,7 +8387,7 @@
       <c r="Q48" s="57" t="n"/>
       <c r="R48" s="59" t="inlineStr">
         <is>
-          <t>手動必須</t>
+          <t>手動（必ず実施）</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8446,11 @@
       <c r="O49" s="57" t="n"/>
       <c r="P49" s="37" t="n"/>
       <c r="Q49" s="57" t="n"/>
-      <c r="R49" s="59" t="inlineStr"/>
+      <c r="R49" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="18" customHeight="1" s="53">
       <c r="B50" s="58" t="n">
@@ -8249,7 +8507,11 @@
       <c r="O50" s="57" t="n"/>
       <c r="P50" s="37" t="n"/>
       <c r="Q50" s="57" t="n"/>
-      <c r="R50" s="59" t="inlineStr"/>
+      <c r="R50" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="18" customHeight="1" s="53">
       <c r="B51" s="58" t="n">
@@ -8306,7 +8568,11 @@
       <c r="O51" s="57" t="n"/>
       <c r="P51" s="37" t="n"/>
       <c r="Q51" s="57" t="n"/>
-      <c r="R51" s="59" t="inlineStr"/>
+      <c r="R51" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="30.4" customHeight="1" s="53">
       <c r="B52" s="58" t="n">
@@ -8363,7 +8629,11 @@
       <c r="O52" s="57" t="n"/>
       <c r="P52" s="37" t="n"/>
       <c r="Q52" s="57" t="n"/>
-      <c r="R52" s="59" t="inlineStr"/>
+      <c r="R52" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="18" customHeight="1" s="53">
       <c r="B53" s="58" t="n">
@@ -8424,7 +8694,11 @@
       <c r="O53" s="57" t="n"/>
       <c r="P53" s="37" t="n"/>
       <c r="Q53" s="57" t="n"/>
-      <c r="R53" s="59" t="inlineStr"/>
+      <c r="R53" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="30.4" customHeight="1" s="53">
       <c r="B54" s="58" t="n">
@@ -8481,7 +8755,11 @@
       <c r="O54" s="57" t="n"/>
       <c r="P54" s="37" t="n"/>
       <c r="Q54" s="57" t="n"/>
-      <c r="R54" s="59" t="inlineStr"/>
+      <c r="R54" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="30.4" customHeight="1" s="53">
       <c r="B55" s="58" t="n">
@@ -8538,7 +8816,11 @@
       <c r="O55" s="57" t="n"/>
       <c r="P55" s="37" t="n"/>
       <c r="Q55" s="57" t="n"/>
-      <c r="R55" s="59" t="inlineStr"/>
+      <c r="R55" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="18" customHeight="1" s="53">
       <c r="B56" s="58" t="n">
@@ -8599,7 +8881,11 @@
       <c r="O56" s="57" t="n"/>
       <c r="P56" s="37" t="n"/>
       <c r="Q56" s="57" t="n"/>
-      <c r="R56" s="59" t="inlineStr"/>
+      <c r="R56" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="18" customHeight="1" s="53">
       <c r="B57" s="58" t="n">
@@ -8660,7 +8946,11 @@
       <c r="O57" s="57" t="n"/>
       <c r="P57" s="37" t="n"/>
       <c r="Q57" s="57" t="n"/>
-      <c r="R57" s="59" t="inlineStr"/>
+      <c r="R57" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="18" customHeight="1" s="53">
       <c r="B58" s="58" t="n">
@@ -8717,7 +9007,11 @@
       <c r="O58" s="57" t="n"/>
       <c r="P58" s="37" t="n"/>
       <c r="Q58" s="57" t="n"/>
-      <c r="R58" s="59" t="inlineStr"/>
+      <c r="R58" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -8792,15 +9086,15 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" s="53">
+    <row r="5" ht="42" customHeight="1" s="53">
       <c r="B5" s="0" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>スマホでの確認は実機か、F12 のスマホ表示アイコンで行う</t>
+      <c r="C5" s="64" t="inlineStr">
+        <is>
+          <t>スマホでの確認は実機か、F12 のスマホ表示アイコンで行う　※備考欄の見方 — 自動: 自動テストが毎回検証（手動実施は不要）／自動＋手動: 動きは自動テストで検証済み・画面の見え方や実機での操作だけ確認する／手動: 自動では確認できないため必ず人が確認する</t>
         </is>
       </c>
     </row>
@@ -8977,7 +9271,11 @@
       <c r="O9" s="57" t="n"/>
       <c r="P9" s="37" t="n"/>
       <c r="Q9" s="57" t="n"/>
-      <c r="R9" s="59" t="inlineStr"/>
+      <c r="R9" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1" s="53">
       <c r="B10" s="58" t="n">
@@ -9034,7 +9332,11 @@
       <c r="O10" s="57" t="n"/>
       <c r="P10" s="37" t="n"/>
       <c r="Q10" s="57" t="n"/>
-      <c r="R10" s="59" t="inlineStr"/>
+      <c r="R10" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30.4" customHeight="1" s="53">
       <c r="B11" s="58" t="n">
@@ -9091,7 +9393,11 @@
       <c r="O11" s="57" t="n"/>
       <c r="P11" s="37" t="n"/>
       <c r="Q11" s="57" t="n"/>
-      <c r="R11" s="59" t="inlineStr"/>
+      <c r="R11" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30.4" customHeight="1" s="53">
       <c r="B12" s="58" t="n">
@@ -9152,7 +9458,11 @@
       <c r="O12" s="57" t="n"/>
       <c r="P12" s="37" t="n"/>
       <c r="Q12" s="57" t="n"/>
-      <c r="R12" s="59" t="inlineStr"/>
+      <c r="R12" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1" s="53">
       <c r="B13" s="58" t="n">
@@ -9213,7 +9523,11 @@
       <c r="O13" s="57" t="n"/>
       <c r="P13" s="37" t="n"/>
       <c r="Q13" s="57" t="n"/>
-      <c r="R13" s="59" t="inlineStr"/>
+      <c r="R13" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1" s="53">
       <c r="B14" s="58" t="n">
@@ -9270,7 +9584,11 @@
       <c r="O14" s="57" t="n"/>
       <c r="P14" s="37" t="n"/>
       <c r="Q14" s="57" t="n"/>
-      <c r="R14" s="59" t="inlineStr"/>
+      <c r="R14" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1" s="53">
       <c r="B15" s="58" t="n">
@@ -9327,7 +9645,11 @@
       <c r="O15" s="57" t="n"/>
       <c r="P15" s="37" t="n"/>
       <c r="Q15" s="57" t="n"/>
-      <c r="R15" s="59" t="inlineStr"/>
+      <c r="R15" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1" s="53">
       <c r="B16" s="58" t="n">
@@ -9384,7 +9706,11 @@
       <c r="O16" s="57" t="n"/>
       <c r="P16" s="37" t="n"/>
       <c r="Q16" s="57" t="n"/>
-      <c r="R16" s="59" t="inlineStr"/>
+      <c r="R16" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1" s="53">
       <c r="B17" s="58" t="n">
@@ -9441,7 +9767,11 @@
       <c r="O17" s="57" t="n"/>
       <c r="P17" s="37" t="n"/>
       <c r="Q17" s="57" t="n"/>
-      <c r="R17" s="59" t="inlineStr"/>
+      <c r="R17" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1" s="53">
       <c r="B18" s="58" t="n">
@@ -9502,7 +9832,11 @@
       <c r="O18" s="57" t="n"/>
       <c r="P18" s="37" t="n"/>
       <c r="Q18" s="57" t="n"/>
-      <c r="R18" s="59" t="inlineStr"/>
+      <c r="R18" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30.4" customHeight="1" s="53">
       <c r="B19" s="58" t="n">
@@ -9563,7 +9897,11 @@
       <c r="O19" s="57" t="n"/>
       <c r="P19" s="37" t="n"/>
       <c r="Q19" s="57" t="n"/>
-      <c r="R19" s="59" t="inlineStr"/>
+      <c r="R19" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1" s="53">
       <c r="B20" s="58" t="n">
@@ -9624,7 +9962,11 @@
       <c r="O20" s="57" t="n"/>
       <c r="P20" s="37" t="n"/>
       <c r="Q20" s="57" t="n"/>
-      <c r="R20" s="59" t="inlineStr"/>
+      <c r="R20" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1" s="53">
       <c r="B21" s="58" t="n">
@@ -9687,7 +10029,7 @@
       <c r="Q21" s="57" t="n"/>
       <c r="R21" s="59" t="inlineStr">
         <is>
-          <t>自動</t>
+          <t>手動</t>
         </is>
       </c>
     </row>
@@ -9750,7 +10092,11 @@
       <c r="O22" s="57" t="n"/>
       <c r="P22" s="37" t="n"/>
       <c r="Q22" s="57" t="n"/>
-      <c r="R22" s="59" t="inlineStr"/>
+      <c r="R22" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1" s="53">
       <c r="B23" s="58" t="n">
@@ -9807,7 +10153,11 @@
       <c r="O23" s="57" t="n"/>
       <c r="P23" s="37" t="n"/>
       <c r="Q23" s="57" t="n"/>
-      <c r="R23" s="59" t="inlineStr"/>
+      <c r="R23" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1" s="53">
       <c r="B24" s="58" t="n">
@@ -9864,7 +10214,11 @@
       <c r="O24" s="57" t="n"/>
       <c r="P24" s="37" t="n"/>
       <c r="Q24" s="57" t="n"/>
-      <c r="R24" s="59" t="inlineStr"/>
+      <c r="R24" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30.4" customHeight="1" s="53">
       <c r="B25" s="58" t="n">
@@ -9921,7 +10275,11 @@
       <c r="O25" s="57" t="n"/>
       <c r="P25" s="37" t="n"/>
       <c r="Q25" s="57" t="n"/>
-      <c r="R25" s="59" t="inlineStr"/>
+      <c r="R25" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="30.4" customHeight="1" s="53">
       <c r="B26" s="58" t="n">
@@ -9978,7 +10336,11 @@
       <c r="O26" s="57" t="n"/>
       <c r="P26" s="37" t="n"/>
       <c r="Q26" s="57" t="n"/>
-      <c r="R26" s="59" t="inlineStr"/>
+      <c r="R26" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1" s="53">
       <c r="B27" s="58" t="n">
@@ -10035,7 +10397,11 @@
       <c r="O27" s="57" t="n"/>
       <c r="P27" s="37" t="n"/>
       <c r="Q27" s="57" t="n"/>
-      <c r="R27" s="59" t="inlineStr"/>
+      <c r="R27" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="30.4" customHeight="1" s="53">
       <c r="B28" s="58" t="n">
@@ -10092,7 +10458,11 @@
       <c r="O28" s="57" t="n"/>
       <c r="P28" s="37" t="n"/>
       <c r="Q28" s="57" t="n"/>
-      <c r="R28" s="59" t="inlineStr"/>
+      <c r="R28" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="53">
       <c r="B29" s="58" t="n">
@@ -10149,7 +10519,11 @@
       <c r="O29" s="57" t="n"/>
       <c r="P29" s="37" t="n"/>
       <c r="Q29" s="57" t="n"/>
-      <c r="R29" s="59" t="inlineStr"/>
+      <c r="R29" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="18" customHeight="1" s="53">
       <c r="B30" s="58" t="n">
@@ -10206,7 +10580,11 @@
       <c r="O30" s="57" t="n"/>
       <c r="P30" s="37" t="n"/>
       <c r="Q30" s="57" t="n"/>
-      <c r="R30" s="59" t="inlineStr"/>
+      <c r="R30" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="53">
       <c r="B31" s="58" t="n">
@@ -10263,7 +10641,11 @@
       <c r="O31" s="57" t="n"/>
       <c r="P31" s="37" t="n"/>
       <c r="Q31" s="57" t="n"/>
-      <c r="R31" s="59" t="inlineStr"/>
+      <c r="R31" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="18" customHeight="1" s="53">
       <c r="B32" s="58" t="n">
@@ -10324,7 +10706,11 @@
       <c r="O32" s="57" t="n"/>
       <c r="P32" s="37" t="n"/>
       <c r="Q32" s="57" t="n"/>
-      <c r="R32" s="59" t="inlineStr"/>
+      <c r="R32" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="18" customHeight="1" s="53">
       <c r="B33" s="58" t="n">
@@ -10381,7 +10767,11 @@
       <c r="O33" s="57" t="n"/>
       <c r="P33" s="37" t="n"/>
       <c r="Q33" s="57" t="n"/>
-      <c r="R33" s="59" t="inlineStr"/>
+      <c r="R33" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -10454,15 +10844,15 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" s="53">
+    <row r="5" ht="42" customHeight="1" s="53">
       <c r="B5" s="0" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>デモデータは必ず「初期化→投入」の順で使う（続けて2回投入するとデータが重複する）</t>
+      <c r="C5" s="64" t="inlineStr">
+        <is>
+          <t>デモデータは必ず「初期化→投入」の順で使う（続けて2回投入するとデータが重複する）　※備考欄の見方 — 自動: 自動テストが毎回検証（手動実施は不要）／自動＋手動: 動きは自動テストで検証済み・画面の見え方や実機での操作だけ確認する／手動: 自動では確認できないため必ず人が確認する</t>
         </is>
       </c>
     </row>
@@ -10635,7 +11025,11 @@
       <c r="O9" s="57" t="n"/>
       <c r="P9" s="37" t="n"/>
       <c r="Q9" s="57" t="n"/>
-      <c r="R9" s="59" t="inlineStr"/>
+      <c r="R9" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1" s="53">
       <c r="B10" s="58" t="n">
@@ -10692,7 +11086,11 @@
       <c r="O10" s="57" t="n"/>
       <c r="P10" s="37" t="n"/>
       <c r="Q10" s="57" t="n"/>
-      <c r="R10" s="59" t="inlineStr"/>
+      <c r="R10" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1" s="53">
       <c r="B11" s="58" t="n">
@@ -10749,7 +11147,11 @@
       <c r="O11" s="57" t="n"/>
       <c r="P11" s="37" t="n"/>
       <c r="Q11" s="57" t="n"/>
-      <c r="R11" s="59" t="inlineStr"/>
+      <c r="R11" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1" s="53">
       <c r="B12" s="58" t="n">
@@ -10806,7 +11208,11 @@
       <c r="O12" s="57" t="n"/>
       <c r="P12" s="37" t="n"/>
       <c r="Q12" s="57" t="n"/>
-      <c r="R12" s="59" t="inlineStr"/>
+      <c r="R12" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1" s="53">
       <c r="B13" s="58" t="n">
@@ -10863,7 +11269,11 @@
       <c r="O13" s="57" t="n"/>
       <c r="P13" s="37" t="n"/>
       <c r="Q13" s="57" t="n"/>
-      <c r="R13" s="59" t="inlineStr"/>
+      <c r="R13" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1" s="53">
       <c r="B14" s="58" t="n">
@@ -10920,7 +11330,11 @@
       <c r="O14" s="57" t="n"/>
       <c r="P14" s="37" t="n"/>
       <c r="Q14" s="57" t="n"/>
-      <c r="R14" s="59" t="inlineStr"/>
+      <c r="R14" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1" s="53">
       <c r="B15" s="58" t="n">
@@ -10977,7 +11391,11 @@
       <c r="O15" s="57" t="n"/>
       <c r="P15" s="37" t="n"/>
       <c r="Q15" s="57" t="n"/>
-      <c r="R15" s="59" t="inlineStr"/>
+      <c r="R15" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1" s="53">
       <c r="B16" s="58" t="n">
@@ -11034,7 +11452,11 @@
       <c r="O16" s="57" t="n"/>
       <c r="P16" s="37" t="n"/>
       <c r="Q16" s="57" t="n"/>
-      <c r="R16" s="59" t="inlineStr"/>
+      <c r="R16" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1" s="53">
       <c r="B17" s="58" t="n">
@@ -11091,7 +11513,11 @@
       <c r="O17" s="57" t="n"/>
       <c r="P17" s="37" t="n"/>
       <c r="Q17" s="57" t="n"/>
-      <c r="R17" s="59" t="inlineStr"/>
+      <c r="R17" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1" s="53">
       <c r="B18" s="58" t="n">
@@ -11148,7 +11574,11 @@
       <c r="O18" s="57" t="n"/>
       <c r="P18" s="37" t="n"/>
       <c r="Q18" s="57" t="n"/>
-      <c r="R18" s="59" t="inlineStr"/>
+      <c r="R18" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="53"/>
     <row r="20" ht="16.5" customHeight="1" s="53"/>
@@ -11220,15 +11650,15 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" s="53">
+    <row r="5" ht="42" customHeight="1" s="53">
       <c r="B5" s="0" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>各画面で共通に成り立つ動きをここに1回だけ記載（個別シートからは省いています）</t>
+      <c r="C5" s="64" t="inlineStr">
+        <is>
+          <t>各画面で共通に成り立つ動きをここに1回だけ記載（個別シートからは省いています）　※備考欄の見方 — 自動: 自動テストが毎回検証（手動実施は不要）／自動＋手動: 動きは自動テストで検証済み・画面の見え方や実機での操作だけ確認する／手動: 自動では確認できないため必ず人が確認する</t>
         </is>
       </c>
     </row>
@@ -11401,7 +11831,11 @@
       <c r="O9" s="57" t="n"/>
       <c r="P9" s="37" t="n"/>
       <c r="Q9" s="57" t="n"/>
-      <c r="R9" s="59" t="inlineStr"/>
+      <c r="R9" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1" s="53">
       <c r="B10" s="58" t="n">
@@ -11462,7 +11896,11 @@
       <c r="O10" s="57" t="n"/>
       <c r="P10" s="37" t="n"/>
       <c r="Q10" s="57" t="n"/>
-      <c r="R10" s="59" t="inlineStr"/>
+      <c r="R10" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1" s="53">
       <c r="B11" s="58" t="n">
@@ -11519,7 +11957,11 @@
       <c r="O11" s="57" t="n"/>
       <c r="P11" s="37" t="n"/>
       <c r="Q11" s="57" t="n"/>
-      <c r="R11" s="59" t="inlineStr"/>
+      <c r="R11" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1" s="53">
       <c r="B12" s="58" t="n">
@@ -11576,7 +12018,11 @@
       <c r="O12" s="57" t="n"/>
       <c r="P12" s="37" t="n"/>
       <c r="Q12" s="57" t="n"/>
-      <c r="R12" s="59" t="inlineStr"/>
+      <c r="R12" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1" s="53">
       <c r="B13" s="58" t="n">
@@ -11637,7 +12083,11 @@
       <c r="O13" s="57" t="n"/>
       <c r="P13" s="37" t="n"/>
       <c r="Q13" s="57" t="n"/>
-      <c r="R13" s="59" t="inlineStr"/>
+      <c r="R13" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1" s="53">
       <c r="B14" s="58" t="n">
@@ -11694,7 +12144,11 @@
       <c r="O14" s="57" t="n"/>
       <c r="P14" s="37" t="n"/>
       <c r="Q14" s="57" t="n"/>
-      <c r="R14" s="59" t="inlineStr"/>
+      <c r="R14" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1" s="53">
       <c r="B15" s="58" t="n">
@@ -11751,7 +12205,11 @@
       <c r="O15" s="57" t="n"/>
       <c r="P15" s="37" t="n"/>
       <c r="Q15" s="57" t="n"/>
-      <c r="R15" s="59" t="inlineStr"/>
+      <c r="R15" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1" s="53">
       <c r="B16" s="58" t="n">
@@ -11808,7 +12266,11 @@
       <c r="O16" s="57" t="n"/>
       <c r="P16" s="37" t="n"/>
       <c r="Q16" s="57" t="n"/>
-      <c r="R16" s="59" t="inlineStr"/>
+      <c r="R16" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1" s="53">
       <c r="B17" s="58" t="n">
@@ -11865,7 +12327,11 @@
       <c r="O17" s="57" t="n"/>
       <c r="P17" s="37" t="n"/>
       <c r="Q17" s="57" t="n"/>
-      <c r="R17" s="59" t="inlineStr"/>
+      <c r="R17" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30.4" customHeight="1" s="53">
       <c r="B18" s="58" t="n">
@@ -11922,7 +12388,11 @@
       <c r="O18" s="57" t="n"/>
       <c r="P18" s="37" t="n"/>
       <c r="Q18" s="57" t="n"/>
-      <c r="R18" s="59" t="inlineStr"/>
+      <c r="R18" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1" s="53">
       <c r="B19" s="58" t="n">
@@ -11979,7 +12449,11 @@
       <c r="O19" s="57" t="n"/>
       <c r="P19" s="37" t="n"/>
       <c r="Q19" s="57" t="n"/>
-      <c r="R19" s="59" t="inlineStr"/>
+      <c r="R19" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1" s="53">
       <c r="B20" s="58" t="n">
@@ -12036,7 +12510,11 @@
       <c r="O20" s="57" t="n"/>
       <c r="P20" s="37" t="n"/>
       <c r="Q20" s="57" t="n"/>
-      <c r="R20" s="59" t="inlineStr"/>
+      <c r="R20" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1" s="53">
       <c r="B21" s="58" t="n">
@@ -12093,7 +12571,11 @@
       <c r="O21" s="57" t="n"/>
       <c r="P21" s="37" t="n"/>
       <c r="Q21" s="57" t="n"/>
-      <c r="R21" s="59" t="inlineStr"/>
+      <c r="R21" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1" s="53">
       <c r="B22" s="58" t="n">
@@ -12154,7 +12636,11 @@
       <c r="O22" s="57" t="n"/>
       <c r="P22" s="37" t="n"/>
       <c r="Q22" s="57" t="n"/>
-      <c r="R22" s="59" t="inlineStr"/>
+      <c r="R22" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1" s="53">
       <c r="B23" s="58" t="n">
@@ -12215,7 +12701,11 @@
       <c r="O23" s="57" t="n"/>
       <c r="P23" s="37" t="n"/>
       <c r="Q23" s="57" t="n"/>
-      <c r="R23" s="59" t="inlineStr"/>
+      <c r="R23" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1" s="53">
       <c r="B24" s="58" t="n">
@@ -12276,7 +12766,11 @@
       <c r="O24" s="57" t="n"/>
       <c r="P24" s="37" t="n"/>
       <c r="Q24" s="57" t="n"/>
-      <c r="R24" s="59" t="inlineStr"/>
+      <c r="R24" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="18" customHeight="1" s="53">
       <c r="B25" s="58" t="n">
@@ -12337,7 +12831,11 @@
       <c r="O25" s="57" t="n"/>
       <c r="P25" s="37" t="n"/>
       <c r="Q25" s="57" t="n"/>
-      <c r="R25" s="59" t="inlineStr"/>
+      <c r="R25" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="30.4" customHeight="1" s="53">
       <c r="B26" s="58" t="n">
@@ -12398,9 +12896,13 @@
       <c r="O26" s="57" t="n"/>
       <c r="P26" s="37" t="n"/>
       <c r="Q26" s="57" t="n"/>
-      <c r="R26" s="59" t="inlineStr"/>
-    </row>
-    <row r="27" ht="18" customHeight="1" s="53">
+      <c r="R26" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30.4" customHeight="1" s="53">
       <c r="B27" s="58" t="n">
         <v>6</v>
       </c>
@@ -12457,7 +12959,7 @@
       <c r="Q27" s="57" t="n"/>
       <c r="R27" s="59" t="inlineStr">
         <is>
-          <t>自動</t>
+          <t>自動（手動不要）</t>
         </is>
       </c>
     </row>
@@ -12516,7 +13018,11 @@
       <c r="O28" s="57" t="n"/>
       <c r="P28" s="37" t="n"/>
       <c r="Q28" s="57" t="n"/>
-      <c r="R28" s="59" t="inlineStr"/>
+      <c r="R28" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="53">
       <c r="B29" s="58" t="n">
@@ -12573,7 +13079,11 @@
       <c r="O29" s="57" t="n"/>
       <c r="P29" s="37" t="n"/>
       <c r="Q29" s="57" t="n"/>
-      <c r="R29" s="59" t="inlineStr"/>
+      <c r="R29" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="18" customHeight="1" s="53">
       <c r="B30" s="58" t="n">
@@ -12630,7 +13140,11 @@
       <c r="O30" s="57" t="n"/>
       <c r="P30" s="37" t="n"/>
       <c r="Q30" s="57" t="n"/>
-      <c r="R30" s="59" t="inlineStr"/>
+      <c r="R30" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="53">
       <c r="B31" s="58" t="n">
@@ -12687,7 +13201,11 @@
       <c r="O31" s="57" t="n"/>
       <c r="P31" s="37" t="n"/>
       <c r="Q31" s="57" t="n"/>
-      <c r="R31" s="59" t="inlineStr"/>
+      <c r="R31" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -12757,15 +13275,15 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" s="53">
+    <row r="5" ht="42" customHeight="1" s="53">
       <c r="B5" s="0" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>気になる点は備考欄にメモし、あとで開発者に確認する</t>
+      <c r="C5" s="64" t="inlineStr">
+        <is>
+          <t>気になる点は備考欄にメモし、あとで開発者に確認する　※備考欄の見方 — 自動: 自動テストが毎回検証（手動実施は不要）／自動＋手動: 動きは自動テストで検証済み・画面の見え方や実機での操作だけ確認する／手動: 自動では確認できないため必ず人が確認する</t>
         </is>
       </c>
     </row>
@@ -12944,7 +13462,7 @@
       <c r="Q9" s="57" t="n"/>
       <c r="R9" s="59" t="inlineStr">
         <is>
-          <t>受け入れ確認の14項目に対応</t>
+          <t>自動＋手動</t>
         </is>
       </c>
     </row>
@@ -13007,7 +13525,11 @@
       <c r="O10" s="57" t="n"/>
       <c r="P10" s="37" t="n"/>
       <c r="Q10" s="57" t="n"/>
-      <c r="R10" s="59" t="inlineStr"/>
+      <c r="R10" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30.4" customHeight="1" s="53">
       <c r="B11" s="58" t="n">
@@ -13064,7 +13586,11 @@
       <c r="O11" s="57" t="n"/>
       <c r="P11" s="37" t="n"/>
       <c r="Q11" s="57" t="n"/>
-      <c r="R11" s="59" t="inlineStr"/>
+      <c r="R11" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30.4" customHeight="1" s="53">
       <c r="B12" s="58" t="n">
@@ -13121,7 +13647,11 @@
       <c r="O12" s="57" t="n"/>
       <c r="P12" s="37" t="n"/>
       <c r="Q12" s="57" t="n"/>
-      <c r="R12" s="59" t="inlineStr"/>
+      <c r="R12" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30.4" customHeight="1" s="53">
       <c r="B13" s="58" t="n">
@@ -13178,7 +13708,11 @@
       <c r="O13" s="57" t="n"/>
       <c r="P13" s="37" t="n"/>
       <c r="Q13" s="57" t="n"/>
-      <c r="R13" s="59" t="inlineStr"/>
+      <c r="R13" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30.4" customHeight="1" s="53">
       <c r="B14" s="58" t="n">
@@ -13235,7 +13769,11 @@
       <c r="O14" s="57" t="n"/>
       <c r="P14" s="37" t="n"/>
       <c r="Q14" s="57" t="n"/>
-      <c r="R14" s="59" t="inlineStr"/>
+      <c r="R14" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30.4" customHeight="1" s="53">
       <c r="B15" s="58" t="n">
@@ -13292,7 +13830,11 @@
       <c r="O15" s="57" t="n"/>
       <c r="P15" s="37" t="n"/>
       <c r="Q15" s="57" t="n"/>
-      <c r="R15" s="59" t="inlineStr"/>
+      <c r="R15" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30.4" customHeight="1" s="53">
       <c r="B16" s="58" t="n">
@@ -13353,7 +13895,11 @@
       <c r="O16" s="57" t="n"/>
       <c r="P16" s="37" t="n"/>
       <c r="Q16" s="57" t="n"/>
-      <c r="R16" s="59" t="inlineStr"/>
+      <c r="R16" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30.4" customHeight="1" s="53">
       <c r="B17" s="58" t="n">
@@ -13410,7 +13956,11 @@
       <c r="O17" s="57" t="n"/>
       <c r="P17" s="37" t="n"/>
       <c r="Q17" s="57" t="n"/>
-      <c r="R17" s="59" t="inlineStr"/>
+      <c r="R17" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30.4" customHeight="1" s="53">
       <c r="B18" s="58" t="n">
@@ -13467,7 +14017,11 @@
       <c r="O18" s="57" t="n"/>
       <c r="P18" s="37" t="n"/>
       <c r="Q18" s="57" t="n"/>
-      <c r="R18" s="59" t="inlineStr"/>
+      <c r="R18" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30.4" customHeight="1" s="53">
       <c r="B19" s="58" t="n">
@@ -13528,7 +14082,11 @@
       <c r="O19" s="57" t="n"/>
       <c r="P19" s="37" t="n"/>
       <c r="Q19" s="57" t="n"/>
-      <c r="R19" s="59" t="inlineStr"/>
+      <c r="R19" s="59" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30.4" customHeight="1" s="53">
       <c r="B20" s="58" t="n">
@@ -13585,7 +14143,11 @@
       <c r="O20" s="57" t="n"/>
       <c r="P20" s="37" t="n"/>
       <c r="Q20" s="57" t="n"/>
-      <c r="R20" s="59" t="inlineStr"/>
+      <c r="R20" s="59" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/docs/結合試験項目一覧.xlsx
+++ b/docs/結合試験項目一覧.xlsx
@@ -10319,7 +10319,7 @@
       <c r="J26" s="60" t="inlineStr"/>
       <c r="K26" s="62" t="inlineStr">
         <is>
-          <t>ログイン画面になる。「探す・申込むには不要」の説明と、保護の限界の注記が出ている</t>
+          <t>ログイン画面になる。保護の限界やデモアカウントなどの説明文は表示されない</t>
         </is>
       </c>
       <c r="L26" s="57" t="inlineStr">
@@ -11008,7 +11008,7 @@
       <c r="J9" s="60" t="inlineStr"/>
       <c r="K9" s="62" t="inlineStr">
         <is>
-          <t>パスワード入力画面になり、「この保護の限界」の説明文が出ている</t>
+          <t>パスワード入力画面になる（保護の限界などの説明文は表示されない）</t>
         </is>
       </c>
       <c r="L9" s="57" t="inlineStr">

--- a/docs/結合試験項目一覧.xlsx
+++ b/docs/結合試験項目一覧.xlsx
@@ -13,7 +13,8 @@
     <sheet name="参加者ビュー" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="名簿・設定" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="共通" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="通シナリオ" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="通知" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="通シナリオ" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -15272,6 +15273,826 @@
     <col width="8.6640625" customWidth="1" style="72" min="1" max="1"/>
     <col width="6.58203125" customWidth="1" style="72" min="2" max="2"/>
     <col width="6.9140625" customWidth="1" style="72" min="3" max="4"/>
+    <col width="9" customWidth="1" style="72" min="5" max="5"/>
+    <col width="16.08203125" bestFit="1" customWidth="1" style="72" min="6" max="6"/>
+    <col width="22.75" bestFit="1" customWidth="1" style="72" min="7" max="7"/>
+    <col width="6.9140625" customWidth="1" style="72" min="8" max="8"/>
+    <col width="78" bestFit="1" customWidth="1" style="72" min="9" max="9"/>
+    <col width="13.83203125" bestFit="1" customWidth="1" style="72" min="10" max="10"/>
+    <col width="90.9140625" customWidth="1" style="72" min="11" max="11"/>
+    <col width="9" customWidth="1" style="72" min="12" max="12"/>
+    <col width="8.6640625" customWidth="1" style="72" min="13" max="14"/>
+    <col width="39" bestFit="1" customWidth="1" style="72" min="15" max="15"/>
+    <col width="7.83203125" bestFit="1" customWidth="1" style="72" min="16" max="16"/>
+    <col width="8.6640625" customWidth="1" style="72" min="17" max="17"/>
+    <col width="8.6640625" customWidth="1" style="72" min="18" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1" s="18">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>●通知（S-11）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="18">
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>目的</t>
+        </is>
+      </c>
+      <c r="C3" s="61" t="inlineStr">
+        <is>
+          <t>通知タブの挙動の確認（主催者・参加者）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="18">
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>前提</t>
+        </is>
+      </c>
+      <c r="C4" s="61" t="inlineStr">
+        <is>
+          <t>デモデータ投入済み。参加者側は abc@example.com ／ abc123 でログイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="18">
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="C5" s="74" t="inlineStr">
+        <is>
+          <t>通知は保存せず各データの時刻から都度組み立てる。既読位置だけを保存する</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="18">
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>テスト内容</t>
+        </is>
+      </c>
+      <c r="C7" s="56" t="n"/>
+      <c r="D7" s="56" t="n"/>
+      <c r="E7" s="56" t="n"/>
+      <c r="F7" s="56" t="n"/>
+      <c r="G7" s="56" t="n"/>
+      <c r="H7" s="56" t="n"/>
+      <c r="I7" s="56" t="n"/>
+      <c r="J7" s="56" t="n"/>
+      <c r="K7" s="58" t="n"/>
+      <c r="L7" s="57" t="inlineStr">
+        <is>
+          <t>テスト実施</t>
+        </is>
+      </c>
+      <c r="M7" s="56" t="n"/>
+      <c r="N7" s="56" t="n"/>
+      <c r="O7" s="56" t="n"/>
+      <c r="P7" s="58" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="18">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>枝番</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>明細</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>大項目</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>中項目</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>小項目</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>観点</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>条件</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>期待動作</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>担当者</t>
+        </is>
+      </c>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="N8" s="12" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>履歴</t>
+        </is>
+      </c>
+      <c r="P8" s="13" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" hidden="1" ht="30.4" customHeight="1" s="18">
+      <c r="B9" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>通知（主催者）</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>一覧</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>並び順</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="I9" s="25" t="inlineStr">
+        <is>
+          <t>主催者ビューで「通知」タブを開く</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>デモデータ投入済み</t>
+        </is>
+      </c>
+      <c r="K9" s="25" t="inlineStr">
+        <is>
+          <t>変更や追加が新しい順に並ぶ。各行に日時・種類・イベント名・内容が出る</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="n"/>
+      <c r="M9" s="20" t="n"/>
+      <c r="N9" s="36" t="n"/>
+      <c r="O9" s="19" t="n"/>
+      <c r="P9" s="51" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30.4" customHeight="1" s="18">
+      <c r="B10" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>通知（主催者）</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>一覧</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>集まる種類</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="I10" s="25" t="inlineStr">
+        <is>
+          <t>一覧の種類バッジを見る</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr"/>
+      <c r="K10" s="25" t="inlineStr">
+        <is>
+          <t>申込・受付・キャンセル・運営スレッド・運営Q&amp;A・運営タスク・マニュアル・ファイル・お知らせ・イベントが出る（告知タブは保存を伴わないため出ない）</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="n"/>
+      <c r="M10" s="20" t="n"/>
+      <c r="N10" s="36" t="n"/>
+      <c r="O10" s="19" t="n"/>
+      <c r="P10" s="51" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30.4" customHeight="1" s="18">
+      <c r="B11" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>通知（主催者）</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>一覧</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>該当タブへ移動</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="I11" s="25" t="inlineStr">
+        <is>
+          <t>「運営タスク」の通知をクリック</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr"/>
+      <c r="K11" s="25" t="inlineStr">
+        <is>
+          <t>そのイベントの詳細が開き、運営タスクのタブが選ばれている</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n"/>
+      <c r="M11" s="20" t="n"/>
+      <c r="N11" s="36" t="n"/>
+      <c r="O11" s="19" t="n"/>
+      <c r="P11" s="51" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" hidden="1" ht="30.4" customHeight="1" s="18">
+      <c r="B12" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>通知（主催者）</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>未読バッジ</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>タブの件数</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="I12" s="25" t="inlineStr">
+        <is>
+          <t>デモデータを投入し、通知タブを見ずに他の画面を開く</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="inlineStr"/>
+      <c r="K12" s="25" t="inlineStr">
+        <is>
+          <t>通知タブに未読の件数が出る（100件を超えると 99+）</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="n"/>
+      <c r="M12" s="20" t="n"/>
+      <c r="N12" s="36" t="n"/>
+      <c r="O12" s="19" t="n"/>
+      <c r="P12" s="51" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30.4" customHeight="1" s="18">
+      <c r="B13" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>通知（主催者）</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>未読バッジ</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>既読化</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="inlineStr">
+        <is>
+          <t>通知タブを開いて別のタブに移る</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="inlineStr"/>
+      <c r="K13" s="25" t="inlineStr">
+        <is>
+          <t>バッジが消える。未読だった行は左に印が付いている</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n"/>
+      <c r="M13" s="20" t="n"/>
+      <c r="N13" s="36" t="n"/>
+      <c r="O13" s="19" t="n"/>
+      <c r="P13" s="51" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30.4" customHeight="1" s="18">
+      <c r="B14" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>通知（主催者）</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>未読バッジ</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>新しい変更</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="I14" s="25" t="inlineStr">
+        <is>
+          <t>お知らせを投稿してから他の画面に移る</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="inlineStr"/>
+      <c r="K14" s="25" t="inlineStr">
+        <is>
+          <t>バッジが 1 になる（自分の操作も変更として数える）</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n"/>
+      <c r="M14" s="20" t="n"/>
+      <c r="N14" s="36" t="n"/>
+      <c r="O14" s="19" t="n"/>
+      <c r="P14" s="51" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" hidden="1" ht="30.4" customHeight="1" s="18">
+      <c r="B15" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>通知（参加者）</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>ログイン</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>未ログイン</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="I15" s="25" t="inlineStr">
+        <is>
+          <t>参加者ビューで「通知」タブを開く</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="inlineStr">
+        <is>
+          <t>ログインしていない</t>
+        </is>
+      </c>
+      <c r="K15" s="25" t="inlineStr">
+        <is>
+          <t>ログインの案内が出て、通知の中身は見えない</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n"/>
+      <c r="M15" s="20" t="n"/>
+      <c r="N15" s="36" t="n"/>
+      <c r="O15" s="19" t="n"/>
+      <c r="P15" s="51" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30.4" customHeight="1" s="18">
+      <c r="B16" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>通知（参加者）</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>一覧</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>自分の分だけ</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
+        <is>
+          <t>ログインして通知タブを開く</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="inlineStr">
+        <is>
+          <t>abc@example.com / abc123</t>
+        </is>
+      </c>
+      <c r="K16" s="25" t="inlineStr">
+        <is>
+          <t>申込んだイベントの通知だけが新しい順に並ぶ（他人のイベントは出ない）</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n"/>
+      <c r="M16" s="20" t="n"/>
+      <c r="N16" s="36" t="n"/>
+      <c r="O16" s="19" t="n"/>
+      <c r="P16" s="51" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" hidden="1" ht="30.4" customHeight="1" s="18">
+      <c r="B17" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>通知（参加者）</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>一覧</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>運営の情報</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
+        <is>
+          <t>一覧の種類を確認する</t>
+        </is>
+      </c>
+      <c r="J17" s="23" t="inlineStr"/>
+      <c r="K17" s="25" t="inlineStr">
+        <is>
+          <t>お知らせ・中止・内容の変更・申込完了・受付完了・キャンセルのみ。運営スレッド・Q&amp;A・タスク・マニュアル・ファイルは出ない</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n"/>
+      <c r="M17" s="20" t="n"/>
+      <c r="N17" s="36" t="n"/>
+      <c r="O17" s="19" t="n"/>
+      <c r="P17" s="51" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" hidden="1" ht="30.4" customHeight="1" s="18">
+      <c r="B18" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>通知（参加者）</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>一覧</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>公開ページへ移動</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="I18" s="25" t="inlineStr">
+        <is>
+          <t>通知をクリック</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="inlineStr"/>
+      <c r="K18" s="25" t="inlineStr">
+        <is>
+          <t>そのイベントの公開ページが開く</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n"/>
+      <c r="M18" s="20" t="n"/>
+      <c r="N18" s="36" t="n"/>
+      <c r="O18" s="19" t="n"/>
+      <c r="P18" s="51" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" hidden="1" ht="18" customHeight="1" s="18">
+      <c r="B19" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>保存の方針</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>都度算出</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>整合</t>
+        </is>
+      </c>
+      <c r="I19" s="25" t="inlineStr">
+        <is>
+          <t>通知を出したあと開発者ツールでデータベースを見る</t>
+        </is>
+      </c>
+      <c r="J19" s="23" t="inlineStr"/>
+      <c r="K19" s="25" t="inlineStr">
+        <is>
+          <t>通知用のストアは作られていない（既読位置だけが readStates に入る）</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n"/>
+      <c r="M19" s="20" t="n"/>
+      <c r="N19" s="36" t="n"/>
+      <c r="O19" s="19" t="n"/>
+      <c r="P19" s="51" t="inlineStr">
+        <is>
+          <t>自動</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" hidden="1" ht="30.4" customHeight="1" s="18">
+      <c r="B20" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>スマホ表示</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>参加者ビュー</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="I20" s="25" t="inlineStr">
+        <is>
+          <t>スマホ幅で参加者の通知タブを開く</t>
+        </is>
+      </c>
+      <c r="J20" s="23" t="inlineStr"/>
+      <c r="K20" s="25" t="inlineStr">
+        <is>
+          <t>日時が上に積まれ、横スクロールが出ない</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n"/>
+      <c r="M20" s="20" t="n"/>
+      <c r="N20" s="36" t="n"/>
+      <c r="O20" s="19" t="n"/>
+      <c r="P20" s="51" t="inlineStr">
+        <is>
+          <t>自動＋手動</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" hidden="1" ht="18" customHeight="1" s="18"/>
+    <row r="22" ht="18" customHeight="1" s="18"/>
+    <row r="23" ht="18" customHeight="1" s="18"/>
+    <row r="24" ht="18" customHeight="1" s="18"/>
+    <row r="25" hidden="1" ht="18" customHeight="1" s="18"/>
+    <row r="26" ht="18" customHeight="1" s="18"/>
+    <row r="27" hidden="1" ht="18" customHeight="1" s="18"/>
+    <row r="28" ht="18" customHeight="1" s="18"/>
+    <row r="29" ht="18" customHeight="1" s="18"/>
+    <row r="30" ht="18" customHeight="1" s="18"/>
+    <row r="31" hidden="1" ht="18" customHeight="1" s="18"/>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="L7:P7"/>
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="C3:K3"/>
+    <mergeCell ref="C4:K4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor theme="5"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <cols>
+    <col width="8.6640625" customWidth="1" style="72" min="1" max="1"/>
+    <col width="6.58203125" customWidth="1" style="72" min="2" max="2"/>
+    <col width="6.9140625" customWidth="1" style="72" min="3" max="4"/>
     <col width="35.1640625" customWidth="1" style="72" min="5" max="5"/>
     <col width="34.58203125" customWidth="1" style="72" min="6" max="6"/>
     <col width="35.4140625" customWidth="1" style="72" min="7" max="7"/>
@@ -15434,7 +16255,7 @@
     </row>
     <row r="9" ht="18" customHeight="1" s="18">
       <c r="B9" s="21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="14" t="n">
         <v>1</v>
@@ -15499,7 +16320,7 @@
     </row>
     <row r="10" ht="18" customHeight="1" s="18">
       <c r="B10" s="21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="14" t="n">
         <v>2</v>
@@ -15564,7 +16385,7 @@
     </row>
     <row r="11" ht="18" customHeight="1" s="18">
       <c r="B11" s="21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" s="14" t="n">
         <v>3</v>
@@ -15625,7 +16446,7 @@
     </row>
     <row r="12" ht="18" customHeight="1" s="18">
       <c r="B12" s="21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" s="14" t="n">
         <v>4</v>
@@ -15686,7 +16507,7 @@
     </row>
     <row r="13" ht="18" customHeight="1" s="18">
       <c r="B13" s="21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" s="14" t="n">
         <v>5</v>
@@ -15747,7 +16568,7 @@
     </row>
     <row r="14" ht="18" customHeight="1" s="18">
       <c r="B14" s="21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" s="14" t="n">
         <v>6</v>
@@ -15808,7 +16629,7 @@
     </row>
     <row r="15" ht="18" customHeight="1" s="18">
       <c r="B15" s="21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" s="14" t="n">
         <v>7</v>
@@ -15869,7 +16690,7 @@
     </row>
     <row r="16" ht="18" customHeight="1" s="18">
       <c r="B16" s="21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C16" s="14" t="n">
         <v>8</v>
@@ -15934,7 +16755,7 @@
     </row>
     <row r="17" ht="18" customHeight="1" s="18">
       <c r="B17" s="21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" s="14" t="n">
         <v>9</v>
@@ -15995,7 +16816,7 @@
     </row>
     <row r="18" ht="18" customHeight="1" s="18">
       <c r="B18" s="21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18" s="14" t="n">
         <v>10</v>
@@ -16056,7 +16877,7 @@
     </row>
     <row r="19" ht="18" customHeight="1" s="18">
       <c r="B19" s="21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" s="14" t="n">
         <v>11</v>
@@ -16121,7 +16942,7 @@
     </row>
     <row r="20" ht="18" customHeight="1" s="18">
       <c r="B20" s="29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C20" s="15" t="n">
         <v>12</v>

--- a/docs/結合試験項目一覧.xlsx
+++ b/docs/結合試験項目一覧.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="606">
   <si>
     <t>●参加者ビュー</t>
   </si>
@@ -1855,6 +1855,10 @@
   </si>
   <si>
     <t>自動</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自動＋手動</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -7729,7 +7733,7 @@
       </c>
       <c r="O13" s="20"/>
       <c r="P13" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7815,7 +7819,7 @@
       </c>
       <c r="O15" s="20"/>
       <c r="P15" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7858,7 +7862,7 @@
       </c>
       <c r="O16" s="20"/>
       <c r="P16" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7944,7 +7948,7 @@
       </c>
       <c r="O18" s="20"/>
       <c r="P18" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
   </sheetData>
@@ -8157,7 +8161,7 @@
       </c>
       <c r="O9" s="20"/>
       <c r="P9" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8202,7 +8206,7 @@
       </c>
       <c r="O10" s="20"/>
       <c r="P10" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8331,7 +8335,7 @@
       </c>
       <c r="O13" s="20"/>
       <c r="P13" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8374,7 +8378,7 @@
       </c>
       <c r="O14" s="20"/>
       <c r="P14" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8419,7 +8423,7 @@
       </c>
       <c r="O15" s="20"/>
       <c r="P15" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8462,7 +8466,7 @@
       </c>
       <c r="O16" s="20"/>
       <c r="P16" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8505,7 +8509,7 @@
       </c>
       <c r="O17" s="20"/>
       <c r="P17" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8548,7 +8552,7 @@
       </c>
       <c r="O18" s="20"/>
       <c r="P18" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="19" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8591,7 +8595,7 @@
       </c>
       <c r="O19" s="20"/>
       <c r="P19" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="20" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8873,7 +8877,7 @@
       </c>
       <c r="O9" s="20"/>
       <c r="P9" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8916,7 +8920,7 @@
       </c>
       <c r="O10" s="20"/>
       <c r="P10" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8959,7 +8963,7 @@
       </c>
       <c r="O11" s="20"/>
       <c r="P11" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9002,7 +9006,7 @@
       </c>
       <c r="O12" s="20"/>
       <c r="P12" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9047,7 +9051,7 @@
       </c>
       <c r="O13" s="20"/>
       <c r="P13" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9133,7 +9137,7 @@
       </c>
       <c r="O15" s="20"/>
       <c r="P15" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9178,7 +9182,7 @@
       </c>
       <c r="O16" s="20"/>
       <c r="P16" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9573,7 +9577,7 @@
       </c>
       <c r="O25" s="20"/>
       <c r="P25" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="26" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9618,7 +9622,7 @@
       </c>
       <c r="O26" s="20"/>
       <c r="P26" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="27" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9661,7 +9665,7 @@
       </c>
       <c r="O27" s="20"/>
       <c r="P27" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="28" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9704,7 +9708,7 @@
       </c>
       <c r="O28" s="20"/>
       <c r="P28" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="29" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9749,7 +9753,7 @@
       </c>
       <c r="O29" s="20"/>
       <c r="P29" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="30" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9792,7 +9796,7 @@
       </c>
       <c r="O30" s="20"/>
       <c r="P30" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="31" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9835,7 +9839,7 @@
       </c>
       <c r="O31" s="20"/>
       <c r="P31" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="32" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9878,7 +9882,7 @@
       </c>
       <c r="O32" s="20"/>
       <c r="P32" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9921,7 +9925,7 @@
       </c>
       <c r="O33" s="20"/>
       <c r="P33" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9964,7 +9968,7 @@
       </c>
       <c r="O34" s="20"/>
       <c r="P34" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10007,7 +10011,7 @@
       </c>
       <c r="O35" s="43"/>
       <c r="P35" s="42" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10050,7 +10054,7 @@
       </c>
       <c r="O36" s="43"/>
       <c r="P36" s="42" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10093,7 +10097,7 @@
       </c>
       <c r="O37" s="43"/>
       <c r="P37" s="42" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10136,7 +10140,7 @@
       </c>
       <c r="O38" s="43"/>
       <c r="P38" s="42" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10179,7 +10183,7 @@
       </c>
       <c r="O39" s="43"/>
       <c r="P39" s="42" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10224,7 +10228,7 @@
       </c>
       <c r="O40" s="43"/>
       <c r="P40" s="42" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10267,7 +10271,7 @@
       </c>
       <c r="O41" s="43"/>
       <c r="P41" s="42" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10353,7 +10357,7 @@
       </c>
       <c r="O43" s="43"/>
       <c r="P43" s="42" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10402,7 +10406,7 @@
       </c>
       <c r="O44" s="43"/>
       <c r="P44" s="42" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10445,7 +10449,7 @@
       </c>
       <c r="O45" s="42"/>
       <c r="P45" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10533,7 +10537,7 @@
       </c>
       <c r="O47" s="42"/>
       <c r="P47" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10576,7 +10580,7 @@
       </c>
       <c r="O48" s="20"/>
       <c r="P48" s="19" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="49" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10750,7 +10754,7 @@
       </c>
       <c r="O52" s="43"/>
       <c r="P52" s="42" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="53" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10793,7 +10797,7 @@
       </c>
       <c r="O53" s="43"/>
       <c r="P53" s="42" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="54" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10969,7 +10973,7 @@
       </c>
       <c r="O57" s="43"/>
       <c r="P57" s="42" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="58" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -11012,7 +11016,7 @@
       </c>
       <c r="O58" s="43"/>
       <c r="P58" s="42" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="59" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -11057,7 +11061,7 @@
       </c>
       <c r="O59" s="43"/>
       <c r="P59" s="42" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="60" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -11102,7 +11106,7 @@
       </c>
       <c r="O60" s="43"/>
       <c r="P60" s="42" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="61" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -11343,7 +11347,7 @@
       </c>
       <c r="O9" s="20"/>
       <c r="P9" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -11431,7 +11435,7 @@
       </c>
       <c r="O11" s="20"/>
       <c r="P11" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -11562,7 +11566,7 @@
       </c>
       <c r="O14" s="20"/>
       <c r="P14" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -11650,7 +11654,7 @@
       </c>
       <c r="O16" s="20"/>
       <c r="P16" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -11779,7 +11783,7 @@
       </c>
       <c r="O19" s="20"/>
       <c r="P19" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="20" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -11824,7 +11828,7 @@
       </c>
       <c r="O20" s="20"/>
       <c r="P20" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="21" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -11869,7 +11873,7 @@
       </c>
       <c r="O21" s="20"/>
       <c r="P21" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="22" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -11914,7 +11918,7 @@
       </c>
       <c r="O22" s="20"/>
       <c r="P22" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="23" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12004,7 +12008,7 @@
       </c>
       <c r="O24" s="43"/>
       <c r="P24" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="25" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12047,7 +12051,7 @@
       </c>
       <c r="O25" s="43"/>
       <c r="P25" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="26" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12133,7 +12137,7 @@
       </c>
       <c r="O27" s="43"/>
       <c r="P27" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="28" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12176,7 +12180,7 @@
       </c>
       <c r="O28" s="43"/>
       <c r="P28" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="29" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12219,7 +12223,7 @@
       </c>
       <c r="O29" s="43"/>
       <c r="P29" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="30" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12262,7 +12266,7 @@
       </c>
       <c r="O30" s="43"/>
       <c r="P30" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="31" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12305,7 +12309,7 @@
       </c>
       <c r="O31" s="43"/>
       <c r="P31" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="32" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12348,7 +12352,7 @@
       </c>
       <c r="O32" s="43"/>
       <c r="P32" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12391,7 +12395,7 @@
       </c>
       <c r="O33" s="43"/>
       <c r="P33" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12436,7 +12440,7 @@
       </c>
       <c r="O34" s="43"/>
       <c r="P34" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12479,7 +12483,7 @@
       </c>
       <c r="O35" s="45"/>
       <c r="P35" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12522,7 +12526,7 @@
       </c>
       <c r="O36" s="59"/>
       <c r="P36" s="40" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
   </sheetData>
@@ -12726,7 +12730,7 @@
       </c>
       <c r="O9" s="20"/>
       <c r="P9" s="52" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12769,7 +12773,7 @@
       </c>
       <c r="O10" s="20"/>
       <c r="P10" s="52" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12812,7 +12816,7 @@
       </c>
       <c r="O11" s="20"/>
       <c r="P11" s="52" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12855,7 +12859,7 @@
       </c>
       <c r="O12" s="20"/>
       <c r="P12" s="52" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12898,7 +12902,7 @@
       </c>
       <c r="O13" s="20"/>
       <c r="P13" s="52" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12941,7 +12945,7 @@
       </c>
       <c r="O14" s="20"/>
       <c r="P14" s="52" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12984,7 +12988,7 @@
       </c>
       <c r="O15" s="20"/>
       <c r="P15" s="52" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13027,7 +13031,7 @@
       </c>
       <c r="O16" s="20"/>
       <c r="P16" s="52" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13070,7 +13074,7 @@
       </c>
       <c r="O17" s="20"/>
       <c r="P17" s="52" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13321,7 +13325,7 @@
       </c>
       <c r="O9" s="20"/>
       <c r="P9" s="51" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13456,7 +13460,7 @@
       </c>
       <c r="O12" s="20"/>
       <c r="P12" s="51" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13591,7 +13595,7 @@
       </c>
       <c r="O15" s="20"/>
       <c r="P15" s="51" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13679,7 +13683,7 @@
       </c>
       <c r="O17" s="20"/>
       <c r="P17" s="51" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13722,7 +13726,7 @@
       </c>
       <c r="O18" s="20"/>
       <c r="P18" s="51" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="19" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13765,7 +13769,7 @@
       </c>
       <c r="O19" s="20"/>
       <c r="P19" s="51" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="20" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13808,7 +13812,7 @@
       </c>
       <c r="O20" s="20"/>
       <c r="P20" s="51" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="21" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13851,7 +13855,7 @@
       </c>
       <c r="O21" s="20"/>
       <c r="P21" s="51" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="22" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14031,7 +14035,7 @@
       </c>
       <c r="O25" s="20"/>
       <c r="P25" s="51" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="26" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14291,7 +14295,7 @@
       </c>
       <c r="O31" s="34"/>
       <c r="P31" s="52" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
   </sheetData>
@@ -14499,7 +14503,7 @@
       </c>
       <c r="O9" s="20"/>
       <c r="P9" s="51" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14587,7 +14591,7 @@
       </c>
       <c r="O11" s="20"/>
       <c r="P11" s="51" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14630,7 +14634,7 @@
       </c>
       <c r="O12" s="20"/>
       <c r="P12" s="51" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14673,7 +14677,7 @@
       </c>
       <c r="O13" s="20"/>
       <c r="P13" s="51" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14716,7 +14720,7 @@
       </c>
       <c r="O14" s="20"/>
       <c r="P14" s="51" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14759,7 +14763,7 @@
       </c>
       <c r="O15" s="20"/>
       <c r="P15" s="51" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14804,7 +14808,7 @@
       </c>
       <c r="O16" s="20"/>
       <c r="P16" s="51" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14847,7 +14851,7 @@
       </c>
       <c r="O17" s="20"/>
       <c r="P17" s="51" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14890,7 +14894,7 @@
       </c>
       <c r="O18" s="20"/>
       <c r="P18" s="51" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
     <row r="19" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14978,7 +14982,7 @@
       </c>
       <c r="O20" s="34"/>
       <c r="P20" s="52" t="s">
-        <v>32</v>
+        <v>605</v>
       </c>
     </row>
   </sheetData>

--- a/docs/結合試験項目一覧.xlsx
+++ b/docs/結合試験項目一覧.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="750">
   <si>
     <t>●参加者ビュー</t>
   </si>
@@ -1860,6 +1860,438 @@
   <si>
     <t>自動＋手動</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>evidence/1-3-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/1-4-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/1-4-2_20260731_01〜04.png（4枚）</t>
+  </si>
+  <si>
+    <t>evidence/1-4-4_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/2-1-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/2-1-2_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/2-3-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/2-3-2_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/2-3-3_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/2-4-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/2-4-2_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/2-4-3_20260731_01〜03.png（3枚）</t>
+  </si>
+  <si>
+    <t>evidence/2-5-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-1-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-1-2_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-2-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-2-2_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-2-3_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-3-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-3-2_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-5-1_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-5-2_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-5-3_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-6-1_20260731_01.png／evidence/3-6-1_20260731_applications_ev_public.csv</t>
+  </si>
+  <si>
+    <t>evidence/3-6-2_20260731_01.png／evidence/3-6-2_20260731_applications_ev_public.csv</t>
+  </si>
+  <si>
+    <t>evidence/3-7-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-8-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-8-2_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-8-3_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-9-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-9-2_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-10-1_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-10-2_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-10-3_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-10-4_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-10-5_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-11-1_20260731_01〜03.png（3枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-11-3_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-11-4_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-11-5_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-11-7_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-12-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-12-5_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-13-1_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-14-3_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-15-1_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-15-2_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-15-3_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/4-1-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/4-1-3_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/4-2-2_20260731_01〜04.png（4枚）</t>
+  </si>
+  <si>
+    <t>evidence/4-2-4_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/4-3-3_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/4-3-4_20260731_01〜03.png（3枚）</t>
+  </si>
+  <si>
+    <t>evidence/4-3-5_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/4-3-6_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/4-3-8_20260731_01〜04.png（4枚）</t>
+  </si>
+  <si>
+    <t>evidence/4-3-9_20260731_01〜03.png（3枚）</t>
+  </si>
+  <si>
+    <t>evidence/4-4-1_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/4-5-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/4-5-2_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/4-5-3_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/4-5-4_20260731_01〜04.png（4枚）</t>
+  </si>
+  <si>
+    <t>evidence/4-5-5_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/4-5-6_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/4-5-7_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/4-5-8_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/4-5-9_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/5-1-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/5-1-2_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/5-1-3_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/5-1-4_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/5-1-5_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/5-1-6_20260731_01.png／evidence/5-1-6_20260731_participants.csv</t>
+  </si>
+  <si>
+    <t>evidence/5-1-7_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/5-2-1_20260731_01〜03.png（3枚）</t>
+  </si>
+  <si>
+    <t>evidence/5-2-2_20260731_01〜03.png（3枚）</t>
+  </si>
+  <si>
+    <t>evidence/6-1-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/6-1-4_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/6-1-7_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/6-2-1_20260731_01〜03.png（3枚）</t>
+  </si>
+  <si>
+    <t>evidence/6-2-2_20260731_01〜03.png（3枚）</t>
+  </si>
+  <si>
+    <t>evidence/6-2-3_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/6-3-1_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/6-3-2_20260731_01〜02.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/6-3-6_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/6-4-4_20260731_01〜03.png（3枚）</t>
+  </si>
+  <si>
+    <t>evidence/7-1-1_20260731_01〜07.png（7枚）／evidence/7-1-1_20260731_applications_4589816a43a82b65.csv</t>
+  </si>
+  <si>
+    <t>evidence/7-3-1_20260731_01〜07.png（7枚）</t>
+  </si>
+  <si>
+    <t>evidence/7-4-1_20260731_01〜04.png（4枚）</t>
+  </si>
+  <si>
+    <t>evidence/7-5-1_20260731_01〜06.png（6枚）</t>
+  </si>
+  <si>
+    <t>evidence/7-6-1_20260731_01〜06.png（6枚）</t>
+  </si>
+  <si>
+    <t>evidence/7-7-1_20260731_01〜06.png（6枚）</t>
+  </si>
+  <si>
+    <t>evidence/7-8-1_20260731_01〜05.png（5枚）</t>
+  </si>
+  <si>
+    <t>evidence/7-9-1_20260731_01〜06.png（6枚）／evidence/7-9-1_20260731_participants.csv</t>
+  </si>
+  <si>
+    <t>evidence/7-10-1_20260731_01〜08.png（8枚）</t>
+  </si>
+  <si>
+    <t>evidence/7-12-1_20260731_01〜05.png（5枚）</t>
+  </si>
+  <si>
+    <t>evidence/1-4-2_20260731_*.png（4枚）</t>
+  </si>
+  <si>
+    <t>evidence/2-3-3_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/2-4-3_20260731_*.png（3枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-1-2_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-5-1_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-5-3_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-8-2_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-8-3_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-9-2_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-10-1_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-10-2_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-10-3_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-10-5_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-11-1_20260731_*.png（3枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-12-5_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-13-1_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-15-1_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-15-2_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-15-3_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/4-2-2_20260731_*.png（4枚）</t>
+  </si>
+  <si>
+    <t>evidence/4-3-4_20260731_*.png（3枚）</t>
+  </si>
+  <si>
+    <t>evidence/4-3-5_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/4-3-8_20260731_*.png（4枚）</t>
+  </si>
+  <si>
+    <t>evidence/4-3-9_20260731_*.png（3枚）</t>
+  </si>
+  <si>
+    <t>evidence/4-4-1_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/4-5-4_20260731_*.png（4枚）</t>
+  </si>
+  <si>
+    <t>evidence/4-5-8_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/5-1-5_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/5-1-7_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/5-2-1_20260731_*.png（3枚）</t>
+  </si>
+  <si>
+    <t>evidence/5-2-2_20260731_*.png（3枚）</t>
+  </si>
+  <si>
+    <t>evidence/6-1-4_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/6-2-1_20260731_*.png（3枚）</t>
+  </si>
+  <si>
+    <t>evidence/6-2-2_20260731_*.png（3枚）</t>
+  </si>
+  <si>
+    <t>evidence/6-3-1_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/6-3-2_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/6-4-4_20260731_*.png（3枚）</t>
+  </si>
+  <si>
+    <t>evidence/7-1-1_20260731_*.png（7枚）／evidence/7-1-1_20260731_applications_4589816a43a82b65.csv</t>
+  </si>
+  <si>
+    <t>evidence/7-3-1_20260731_*.png（7枚）</t>
+  </si>
+  <si>
+    <t>evidence/7-4-1_20260731_*.png（4枚）</t>
+  </si>
+  <si>
+    <t>evidence/7-5-1_20260731_*.png（6枚）</t>
+  </si>
+  <si>
+    <t>evidence/7-6-1_20260731_*.png（6枚）</t>
+  </si>
+  <si>
+    <t>evidence/7-7-1_20260731_*.png（6枚）</t>
+  </si>
+  <si>
+    <t>evidence/7-8-1_20260731_*.png（5枚）</t>
+  </si>
+  <si>
+    <t>evidence/7-9-1_20260731_*.png（6枚）／evidence/7-9-1_20260731_participants.csv</t>
+  </si>
+  <si>
+    <t>evidence/7-10-1_20260731_*.png（8枚）</t>
+  </si>
+  <si>
+    <t>evidence/7-12-1_20260731_*.png（5枚）</t>
   </si>
 </sst>
 </file>
@@ -7731,7 +8163,9 @@
       <c r="N13" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O13" s="20"/>
+      <c r="O13" s="20" t="s">
+        <v>606</v>
+      </c>
       <c r="P13" s="40" t="s">
         <v>605</v>
       </c>
@@ -7817,7 +8251,9 @@
       <c r="N15" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O15" s="20"/>
+      <c r="O15" s="20" t="s">
+        <v>607</v>
+      </c>
       <c r="P15" s="40" t="s">
         <v>605</v>
       </c>
@@ -7860,7 +8296,9 @@
       <c r="N16" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O16" s="20"/>
+      <c r="O16" s="20" t="s">
+        <v>703</v>
+      </c>
       <c r="P16" s="40" t="s">
         <v>605</v>
       </c>
@@ -7946,7 +8384,9 @@
       <c r="N18" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O18" s="20"/>
+      <c r="O18" s="20" t="s">
+        <v>609</v>
+      </c>
       <c r="P18" s="40" t="s">
         <v>605</v>
       </c>
@@ -8159,7 +8599,9 @@
       <c r="N9" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O9" s="20"/>
+      <c r="O9" s="20" t="s">
+        <v>610</v>
+      </c>
       <c r="P9" s="40" t="s">
         <v>605</v>
       </c>
@@ -8204,7 +8646,9 @@
       <c r="N10" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O10" s="20"/>
+      <c r="O10" s="20" t="s">
+        <v>611</v>
+      </c>
       <c r="P10" s="40" t="s">
         <v>605</v>
       </c>
@@ -8333,7 +8777,9 @@
       <c r="N13" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O13" s="20"/>
+      <c r="O13" s="20" t="s">
+        <v>612</v>
+      </c>
       <c r="P13" s="40" t="s">
         <v>605</v>
       </c>
@@ -8376,7 +8822,9 @@
       <c r="N14" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O14" s="20"/>
+      <c r="O14" s="20" t="s">
+        <v>613</v>
+      </c>
       <c r="P14" s="40" t="s">
         <v>605</v>
       </c>
@@ -8421,7 +8869,9 @@
       <c r="N15" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O15" s="20"/>
+      <c r="O15" s="20" t="s">
+        <v>704</v>
+      </c>
       <c r="P15" s="40" t="s">
         <v>605</v>
       </c>
@@ -8464,7 +8914,9 @@
       <c r="N16" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O16" s="20"/>
+      <c r="O16" s="20" t="s">
+        <v>615</v>
+      </c>
       <c r="P16" s="40" t="s">
         <v>605</v>
       </c>
@@ -8507,7 +8959,9 @@
       <c r="N17" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O17" s="20"/>
+      <c r="O17" s="20" t="s">
+        <v>616</v>
+      </c>
       <c r="P17" s="40" t="s">
         <v>605</v>
       </c>
@@ -8550,7 +9004,9 @@
       <c r="N18" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O18" s="20"/>
+      <c r="O18" s="20" t="s">
+        <v>705</v>
+      </c>
       <c r="P18" s="40" t="s">
         <v>605</v>
       </c>
@@ -8593,7 +9049,9 @@
       <c r="N19" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O19" s="20"/>
+      <c r="O19" s="20" t="s">
+        <v>618</v>
+      </c>
       <c r="P19" s="40" t="s">
         <v>605</v>
       </c>
@@ -8875,7 +9333,9 @@
       <c r="N9" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O9" s="20"/>
+      <c r="O9" s="20" t="s">
+        <v>619</v>
+      </c>
       <c r="P9" s="40" t="s">
         <v>605</v>
       </c>
@@ -8918,7 +9378,9 @@
       <c r="N10" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O10" s="20"/>
+      <c r="O10" s="20" t="s">
+        <v>706</v>
+      </c>
       <c r="P10" s="40" t="s">
         <v>605</v>
       </c>
@@ -8961,7 +9423,9 @@
       <c r="N11" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O11" s="20"/>
+      <c r="O11" s="20" t="s">
+        <v>621</v>
+      </c>
       <c r="P11" s="40" t="s">
         <v>605</v>
       </c>
@@ -9004,7 +9468,9 @@
       <c r="N12" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O12" s="20"/>
+      <c r="O12" s="20" t="s">
+        <v>622</v>
+      </c>
       <c r="P12" s="40" t="s">
         <v>605</v>
       </c>
@@ -9049,7 +9515,9 @@
       <c r="N13" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O13" s="20"/>
+      <c r="O13" s="20" t="s">
+        <v>623</v>
+      </c>
       <c r="P13" s="40" t="s">
         <v>605</v>
       </c>
@@ -9135,7 +9603,9 @@
       <c r="N15" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O15" s="20"/>
+      <c r="O15" s="20" t="s">
+        <v>624</v>
+      </c>
       <c r="P15" s="40" t="s">
         <v>605</v>
       </c>
@@ -9180,7 +9650,9 @@
       <c r="N16" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O16" s="20"/>
+      <c r="O16" s="20" t="s">
+        <v>625</v>
+      </c>
       <c r="P16" s="40" t="s">
         <v>605</v>
       </c>
@@ -9575,7 +10047,9 @@
       <c r="N25" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O25" s="20"/>
+      <c r="O25" s="20" t="s">
+        <v>707</v>
+      </c>
       <c r="P25" s="40" t="s">
         <v>605</v>
       </c>
@@ -9620,7 +10094,9 @@
       <c r="N26" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O26" s="20"/>
+      <c r="O26" s="20" t="s">
+        <v>627</v>
+      </c>
       <c r="P26" s="40" t="s">
         <v>605</v>
       </c>
@@ -9663,7 +10139,9 @@
       <c r="N27" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O27" s="20"/>
+      <c r="O27" s="20" t="s">
+        <v>708</v>
+      </c>
       <c r="P27" s="40" t="s">
         <v>605</v>
       </c>
@@ -9706,7 +10184,9 @@
       <c r="N28" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O28" s="20"/>
+      <c r="O28" s="20" t="s">
+        <v>629</v>
+      </c>
       <c r="P28" s="40" t="s">
         <v>605</v>
       </c>
@@ -9751,7 +10231,9 @@
       <c r="N29" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O29" s="20"/>
+      <c r="O29" s="20" t="s">
+        <v>630</v>
+      </c>
       <c r="P29" s="40" t="s">
         <v>605</v>
       </c>
@@ -9794,7 +10276,9 @@
       <c r="N30" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O30" s="20"/>
+      <c r="O30" s="20" t="s">
+        <v>631</v>
+      </c>
       <c r="P30" s="40" t="s">
         <v>605</v>
       </c>
@@ -9837,7 +10321,9 @@
       <c r="N31" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O31" s="20"/>
+      <c r="O31" s="20" t="s">
+        <v>632</v>
+      </c>
       <c r="P31" s="40" t="s">
         <v>605</v>
       </c>
@@ -9880,7 +10366,9 @@
       <c r="N32" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O32" s="20"/>
+      <c r="O32" s="20" t="s">
+        <v>709</v>
+      </c>
       <c r="P32" s="40" t="s">
         <v>605</v>
       </c>
@@ -9923,7 +10411,9 @@
       <c r="N33" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O33" s="20"/>
+      <c r="O33" s="20" t="s">
+        <v>710</v>
+      </c>
       <c r="P33" s="40" t="s">
         <v>605</v>
       </c>
@@ -9966,7 +10456,9 @@
       <c r="N34" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O34" s="20"/>
+      <c r="O34" s="20" t="s">
+        <v>635</v>
+      </c>
       <c r="P34" s="40" t="s">
         <v>605</v>
       </c>
@@ -10009,7 +10501,9 @@
       <c r="N35" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O35" s="43"/>
+      <c r="O35" s="43" t="s">
+        <v>711</v>
+      </c>
       <c r="P35" s="42" t="s">
         <v>605</v>
       </c>
@@ -10052,7 +10546,9 @@
       <c r="N36" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O36" s="43"/>
+      <c r="O36" s="43" t="s">
+        <v>712</v>
+      </c>
       <c r="P36" s="42" t="s">
         <v>605</v>
       </c>
@@ -10095,7 +10591,9 @@
       <c r="N37" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O37" s="43"/>
+      <c r="O37" s="43" t="s">
+        <v>713</v>
+      </c>
       <c r="P37" s="42" t="s">
         <v>605</v>
       </c>
@@ -10138,7 +10636,9 @@
       <c r="N38" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O38" s="43"/>
+      <c r="O38" s="43" t="s">
+        <v>714</v>
+      </c>
       <c r="P38" s="42" t="s">
         <v>605</v>
       </c>
@@ -10181,7 +10681,9 @@
       <c r="N39" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O39" s="43"/>
+      <c r="O39" s="43" t="s">
+        <v>640</v>
+      </c>
       <c r="P39" s="42" t="s">
         <v>605</v>
       </c>
@@ -10226,7 +10728,9 @@
       <c r="N40" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O40" s="43"/>
+      <c r="O40" s="43" t="s">
+        <v>715</v>
+      </c>
       <c r="P40" s="42" t="s">
         <v>605</v>
       </c>
@@ -10269,7 +10773,9 @@
       <c r="N41" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O41" s="43"/>
+      <c r="O41" s="43" t="s">
+        <v>716</v>
+      </c>
       <c r="P41" s="42" t="s">
         <v>605</v>
       </c>
@@ -10355,7 +10861,9 @@
       <c r="N43" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O43" s="43"/>
+      <c r="O43" s="43" t="s">
+        <v>643</v>
+      </c>
       <c r="P43" s="42" t="s">
         <v>605</v>
       </c>
@@ -10404,7 +10912,9 @@
       <c r="N44" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O44" s="43"/>
+      <c r="O44" s="43" t="s">
+        <v>644</v>
+      </c>
       <c r="P44" s="42" t="s">
         <v>605</v>
       </c>
@@ -10447,7 +10957,9 @@
       <c r="N45" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O45" s="42"/>
+      <c r="O45" s="42" t="s">
+        <v>645</v>
+      </c>
       <c r="P45" s="40" t="s">
         <v>605</v>
       </c>
@@ -10535,7 +11047,9 @@
       <c r="N47" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O47" s="42"/>
+      <c r="O47" s="42" t="s">
+        <v>646</v>
+      </c>
       <c r="P47" s="40" t="s">
         <v>605</v>
       </c>
@@ -10578,7 +11092,9 @@
       <c r="N48" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O48" s="20"/>
+      <c r="O48" s="20" t="s">
+        <v>647</v>
+      </c>
       <c r="P48" s="19" t="s">
         <v>605</v>
       </c>
@@ -10752,7 +11268,9 @@
       <c r="N52" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O52" s="43"/>
+      <c r="O52" s="43" t="s">
+        <v>717</v>
+      </c>
       <c r="P52" s="42" t="s">
         <v>605</v>
       </c>
@@ -10795,7 +11313,9 @@
       <c r="N53" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O53" s="43"/>
+      <c r="O53" s="43" t="s">
+        <v>718</v>
+      </c>
       <c r="P53" s="42" t="s">
         <v>605</v>
       </c>
@@ -10971,7 +11491,9 @@
       <c r="N57" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O57" s="43"/>
+      <c r="O57" s="43" t="s">
+        <v>650</v>
+      </c>
       <c r="P57" s="42" t="s">
         <v>605</v>
       </c>
@@ -11014,7 +11536,9 @@
       <c r="N58" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O58" s="43"/>
+      <c r="O58" s="43" t="s">
+        <v>719</v>
+      </c>
       <c r="P58" s="42" t="s">
         <v>605</v>
       </c>
@@ -11059,7 +11583,9 @@
       <c r="N59" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O59" s="43"/>
+      <c r="O59" s="43" t="s">
+        <v>720</v>
+      </c>
       <c r="P59" s="42" t="s">
         <v>605</v>
       </c>
@@ -11104,7 +11630,9 @@
       <c r="N60" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O60" s="43"/>
+      <c r="O60" s="43" t="s">
+        <v>721</v>
+      </c>
       <c r="P60" s="42" t="s">
         <v>605</v>
       </c>
@@ -11345,7 +11873,9 @@
       <c r="N9" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O9" s="20"/>
+      <c r="O9" s="20" t="s">
+        <v>654</v>
+      </c>
       <c r="P9" s="40" t="s">
         <v>605</v>
       </c>
@@ -11433,7 +11963,9 @@
       <c r="N11" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O11" s="20"/>
+      <c r="O11" s="20" t="s">
+        <v>655</v>
+      </c>
       <c r="P11" s="40" t="s">
         <v>605</v>
       </c>
@@ -11564,7 +12096,9 @@
       <c r="N14" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O14" s="20"/>
+      <c r="O14" s="20" t="s">
+        <v>722</v>
+      </c>
       <c r="P14" s="40" t="s">
         <v>605</v>
       </c>
@@ -11652,7 +12186,9 @@
       <c r="N16" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O16" s="20"/>
+      <c r="O16" s="20" t="s">
+        <v>657</v>
+      </c>
       <c r="P16" s="40" t="s">
         <v>605</v>
       </c>
@@ -11781,7 +12317,9 @@
       <c r="N19" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O19" s="20"/>
+      <c r="O19" s="20" t="s">
+        <v>658</v>
+      </c>
       <c r="P19" s="40" t="s">
         <v>605</v>
       </c>
@@ -11826,7 +12364,9 @@
       <c r="N20" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O20" s="20"/>
+      <c r="O20" s="20" t="s">
+        <v>723</v>
+      </c>
       <c r="P20" s="40" t="s">
         <v>605</v>
       </c>
@@ -11871,7 +12411,9 @@
       <c r="N21" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O21" s="20"/>
+      <c r="O21" s="20" t="s">
+        <v>724</v>
+      </c>
       <c r="P21" s="40" t="s">
         <v>605</v>
       </c>
@@ -11916,7 +12458,9 @@
       <c r="N22" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O22" s="20"/>
+      <c r="O22" s="20" t="s">
+        <v>661</v>
+      </c>
       <c r="P22" s="40" t="s">
         <v>605</v>
       </c>
@@ -12006,7 +12550,9 @@
       <c r="N24" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O24" s="43"/>
+      <c r="O24" s="43" t="s">
+        <v>725</v>
+      </c>
       <c r="P24" s="40" t="s">
         <v>605</v>
       </c>
@@ -12049,7 +12595,9 @@
       <c r="N25" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O25" s="43"/>
+      <c r="O25" s="43" t="s">
+        <v>726</v>
+      </c>
       <c r="P25" s="40" t="s">
         <v>605</v>
       </c>
@@ -12135,7 +12683,9 @@
       <c r="N27" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O27" s="43"/>
+      <c r="O27" s="43" t="s">
+        <v>727</v>
+      </c>
       <c r="P27" s="40" t="s">
         <v>605</v>
       </c>
@@ -12178,7 +12728,9 @@
       <c r="N28" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O28" s="43"/>
+      <c r="O28" s="43" t="s">
+        <v>665</v>
+      </c>
       <c r="P28" s="40" t="s">
         <v>605</v>
       </c>
@@ -12221,7 +12773,9 @@
       <c r="N29" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O29" s="43"/>
+      <c r="O29" s="43" t="s">
+        <v>666</v>
+      </c>
       <c r="P29" s="40" t="s">
         <v>605</v>
       </c>
@@ -12264,7 +12818,9 @@
       <c r="N30" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O30" s="43"/>
+      <c r="O30" s="43" t="s">
+        <v>667</v>
+      </c>
       <c r="P30" s="40" t="s">
         <v>605</v>
       </c>
@@ -12307,7 +12863,9 @@
       <c r="N31" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O31" s="43"/>
+      <c r="O31" s="43" t="s">
+        <v>728</v>
+      </c>
       <c r="P31" s="40" t="s">
         <v>605</v>
       </c>
@@ -12350,7 +12908,9 @@
       <c r="N32" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O32" s="43"/>
+      <c r="O32" s="43" t="s">
+        <v>669</v>
+      </c>
       <c r="P32" s="40" t="s">
         <v>605</v>
       </c>
@@ -12393,7 +12953,9 @@
       <c r="N33" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O33" s="43"/>
+      <c r="O33" s="43" t="s">
+        <v>670</v>
+      </c>
       <c r="P33" s="40" t="s">
         <v>605</v>
       </c>
@@ -12438,7 +13000,9 @@
       <c r="N34" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O34" s="43"/>
+      <c r="O34" s="43" t="s">
+        <v>671</v>
+      </c>
       <c r="P34" s="40" t="s">
         <v>605</v>
       </c>
@@ -12481,7 +13045,9 @@
       <c r="N35" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O35" s="45"/>
+      <c r="O35" s="45" t="s">
+        <v>729</v>
+      </c>
       <c r="P35" s="40" t="s">
         <v>605</v>
       </c>
@@ -12524,7 +13090,9 @@
       <c r="N36" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O36" s="59"/>
+      <c r="O36" s="59" t="s">
+        <v>673</v>
+      </c>
       <c r="P36" s="40" t="s">
         <v>605</v>
       </c>
@@ -12728,7 +13296,9 @@
       <c r="N9" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O9" s="20"/>
+      <c r="O9" s="20" t="s">
+        <v>674</v>
+      </c>
       <c r="P9" s="52" t="s">
         <v>605</v>
       </c>
@@ -12771,7 +13341,9 @@
       <c r="N10" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O10" s="20"/>
+      <c r="O10" s="20" t="s">
+        <v>675</v>
+      </c>
       <c r="P10" s="52" t="s">
         <v>605</v>
       </c>
@@ -12814,7 +13386,9 @@
       <c r="N11" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O11" s="20"/>
+      <c r="O11" s="20" t="s">
+        <v>676</v>
+      </c>
       <c r="P11" s="52" t="s">
         <v>605</v>
       </c>
@@ -12857,7 +13431,9 @@
       <c r="N12" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O12" s="20"/>
+      <c r="O12" s="20" t="s">
+        <v>677</v>
+      </c>
       <c r="P12" s="52" t="s">
         <v>605</v>
       </c>
@@ -12900,7 +13476,9 @@
       <c r="N13" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O13" s="20"/>
+      <c r="O13" s="20" t="s">
+        <v>730</v>
+      </c>
       <c r="P13" s="52" t="s">
         <v>605</v>
       </c>
@@ -12943,7 +13521,9 @@
       <c r="N14" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O14" s="20"/>
+      <c r="O14" s="20" t="s">
+        <v>679</v>
+      </c>
       <c r="P14" s="52" t="s">
         <v>605</v>
       </c>
@@ -12986,7 +13566,9 @@
       <c r="N15" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O15" s="20"/>
+      <c r="O15" s="20" t="s">
+        <v>731</v>
+      </c>
       <c r="P15" s="52" t="s">
         <v>605</v>
       </c>
@@ -13029,7 +13611,9 @@
       <c r="N16" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O16" s="20"/>
+      <c r="O16" s="20" t="s">
+        <v>732</v>
+      </c>
       <c r="P16" s="52" t="s">
         <v>605</v>
       </c>
@@ -13072,7 +13656,9 @@
       <c r="N17" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O17" s="20"/>
+      <c r="O17" s="20" t="s">
+        <v>733</v>
+      </c>
       <c r="P17" s="52" t="s">
         <v>605</v>
       </c>
@@ -13323,7 +13909,9 @@
       <c r="N9" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O9" s="20"/>
+      <c r="O9" s="20" t="s">
+        <v>683</v>
+      </c>
       <c r="P9" s="51" t="s">
         <v>605</v>
       </c>
@@ -13458,7 +14046,9 @@
       <c r="N12" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O12" s="20"/>
+      <c r="O12" s="20" t="s">
+        <v>734</v>
+      </c>
       <c r="P12" s="51" t="s">
         <v>605</v>
       </c>
@@ -13593,7 +14183,9 @@
       <c r="N15" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O15" s="20"/>
+      <c r="O15" s="20" t="s">
+        <v>685</v>
+      </c>
       <c r="P15" s="51" t="s">
         <v>605</v>
       </c>
@@ -13681,7 +14273,9 @@
       <c r="N17" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O17" s="20"/>
+      <c r="O17" s="20" t="s">
+        <v>735</v>
+      </c>
       <c r="P17" s="51" t="s">
         <v>605</v>
       </c>
@@ -13724,7 +14318,9 @@
       <c r="N18" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O18" s="20"/>
+      <c r="O18" s="20" t="s">
+        <v>736</v>
+      </c>
       <c r="P18" s="51" t="s">
         <v>605</v>
       </c>
@@ -13767,7 +14363,9 @@
       <c r="N19" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O19" s="20"/>
+      <c r="O19" s="20" t="s">
+        <v>688</v>
+      </c>
       <c r="P19" s="51" t="s">
         <v>605</v>
       </c>
@@ -13810,7 +14408,9 @@
       <c r="N20" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O20" s="20"/>
+      <c r="O20" s="20" t="s">
+        <v>737</v>
+      </c>
       <c r="P20" s="51" t="s">
         <v>605</v>
       </c>
@@ -13853,7 +14453,9 @@
       <c r="N21" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O21" s="20"/>
+      <c r="O21" s="20" t="s">
+        <v>738</v>
+      </c>
       <c r="P21" s="51" t="s">
         <v>605</v>
       </c>
@@ -14033,7 +14635,9 @@
       <c r="N25" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O25" s="20"/>
+      <c r="O25" s="20" t="s">
+        <v>691</v>
+      </c>
       <c r="P25" s="51" t="s">
         <v>605</v>
       </c>
@@ -14293,7 +14897,9 @@
       <c r="N31" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O31" s="34"/>
+      <c r="O31" s="34" t="s">
+        <v>739</v>
+      </c>
       <c r="P31" s="52" t="s">
         <v>605</v>
       </c>
@@ -14501,7 +15107,9 @@
       <c r="N9" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O9" s="20"/>
+      <c r="O9" s="20" t="s">
+        <v>740</v>
+      </c>
       <c r="P9" s="51" t="s">
         <v>605</v>
       </c>
@@ -14589,7 +15197,9 @@
       <c r="N11" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O11" s="20"/>
+      <c r="O11" s="20" t="s">
+        <v>741</v>
+      </c>
       <c r="P11" s="51" t="s">
         <v>605</v>
       </c>
@@ -14632,7 +15242,9 @@
       <c r="N12" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O12" s="20"/>
+      <c r="O12" s="20" t="s">
+        <v>742</v>
+      </c>
       <c r="P12" s="51" t="s">
         <v>605</v>
       </c>
@@ -14675,7 +15287,9 @@
       <c r="N13" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O13" s="20"/>
+      <c r="O13" s="20" t="s">
+        <v>743</v>
+      </c>
       <c r="P13" s="51" t="s">
         <v>605</v>
       </c>
@@ -14718,7 +15332,9 @@
       <c r="N14" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O14" s="20"/>
+      <c r="O14" s="20" t="s">
+        <v>744</v>
+      </c>
       <c r="P14" s="51" t="s">
         <v>605</v>
       </c>
@@ -14761,7 +15377,9 @@
       <c r="N15" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O15" s="20"/>
+      <c r="O15" s="20" t="s">
+        <v>745</v>
+      </c>
       <c r="P15" s="51" t="s">
         <v>605</v>
       </c>
@@ -14806,7 +15424,9 @@
       <c r="N16" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O16" s="20"/>
+      <c r="O16" s="20" t="s">
+        <v>746</v>
+      </c>
       <c r="P16" s="51" t="s">
         <v>605</v>
       </c>
@@ -14849,7 +15469,9 @@
       <c r="N17" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O17" s="20"/>
+      <c r="O17" s="20" t="s">
+        <v>747</v>
+      </c>
       <c r="P17" s="51" t="s">
         <v>605</v>
       </c>
@@ -14892,7 +15514,9 @@
       <c r="N18" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O18" s="20"/>
+      <c r="O18" s="20" t="s">
+        <v>748</v>
+      </c>
       <c r="P18" s="51" t="s">
         <v>605</v>
       </c>
@@ -14980,7 +15604,9 @@
       <c r="N20" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="O20" s="34"/>
+      <c r="O20" s="34" t="s">
+        <v>749</v>
+      </c>
       <c r="P20" s="52" t="s">
         <v>605</v>
       </c>

--- a/docs/結合試験項目一覧.xlsx
+++ b/docs/結合試験項目一覧.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1694" uniqueCount="797">
   <si>
     <t>●参加者ビュー</t>
   </si>
@@ -2292,6 +2292,147 @@
   </si>
   <si>
     <t>evidence/7-12-1_20260731_*.png（5枚）</t>
+  </si>
+  <si>
+    <t>evidence/1-1-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/1-2-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/1-2-2_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/1-2-3_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/1-3-2_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/1-4-3_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/2-1-3_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/2-2-1_20260731_*.png（3枚）</t>
+  </si>
+  <si>
+    <t>evidence/2-6-1_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/2-6-2_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-2-4_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-3-3_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-4-5_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-4-6_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-4-7_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-11-2_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-11-6_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-12-2_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-12-3_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-12-4_20260731_01.png／evidence/3-12-4_20260731_登壇者一覧.txt</t>
+  </si>
+  <si>
+    <t>evidence/3-13-2_20260731_*.png（4枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-14-1_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/3-14-2_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-15-4_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/4-1-2_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/4-1-4_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/4-2-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/4-2-3_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/4-3-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/4-3-2_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/4-3-7_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/4-3-10_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/6-1-2_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/6-1-3_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/6-1-5_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/6-1-6_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/6-1-8_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/6-3-3_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/6-3-4_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/6-3-5_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/6-3-7_20260731_*.png（4枚）</t>
+  </si>
+  <si>
+    <t>evidence/6-3-8_20260731_ci.log</t>
+  </si>
+  <si>
+    <t>evidence/6-4-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/6-4-2_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/6-4-3_20260731_*.png（2枚）</t>
+  </si>
+  <si>
+    <t>evidence/7-2-1_20260731_*.png（4枚）</t>
+  </si>
+  <si>
+    <t>evidence/7-11-1_20260731_*.png（6枚）</t>
   </si>
 </sst>
 </file>
@@ -7987,7 +8128,9 @@
       <c r="N9" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O9" s="20"/>
+      <c r="O9" s="20" t="s">
+        <v>750</v>
+      </c>
       <c r="P9" s="19" t="s">
         <v>37</v>
       </c>
@@ -8032,7 +8175,9 @@
       <c r="N10" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O10" s="20"/>
+      <c r="O10" s="20" t="s">
+        <v>751</v>
+      </c>
       <c r="P10" s="19" t="s">
         <v>37</v>
       </c>
@@ -8077,7 +8222,9 @@
       <c r="N11" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O11" s="20"/>
+      <c r="O11" s="20" t="s">
+        <v>752</v>
+      </c>
       <c r="P11" s="19" t="s">
         <v>37</v>
       </c>
@@ -8120,7 +8267,9 @@
       <c r="N12" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O12" s="20"/>
+      <c r="O12" s="20" t="s">
+        <v>753</v>
+      </c>
       <c r="P12" s="19" t="s">
         <v>37</v>
       </c>
@@ -8208,7 +8357,9 @@
       <c r="N14" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O14" s="20"/>
+      <c r="O14" s="20" t="s">
+        <v>754</v>
+      </c>
       <c r="P14" s="19" t="s">
         <v>32</v>
       </c>
@@ -8341,7 +8492,9 @@
       <c r="N17" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O17" s="20"/>
+      <c r="O17" s="20" t="s">
+        <v>755</v>
+      </c>
       <c r="P17" s="19" t="s">
         <v>37</v>
       </c>
@@ -8691,7 +8844,9 @@
       <c r="N11" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="O11" s="20"/>
+      <c r="O11" s="20" t="s">
+        <v>756</v>
+      </c>
       <c r="P11" s="19" t="s">
         <v>37</v>
       </c>
@@ -8734,7 +8889,9 @@
       <c r="N12" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="O12" s="20"/>
+      <c r="O12" s="20" t="s">
+        <v>757</v>
+      </c>
       <c r="P12" s="19" t="s">
         <v>37</v>
       </c>
@@ -9096,7 +9253,9 @@
       <c r="N20" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="O20" s="20"/>
+      <c r="O20" s="20" t="s">
+        <v>758</v>
+      </c>
       <c r="P20" s="19" t="s">
         <v>37</v>
       </c>
@@ -9141,7 +9300,9 @@
       <c r="N21" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="O21" s="20"/>
+      <c r="O21" s="20" t="s">
+        <v>759</v>
+      </c>
       <c r="P21" s="19" t="s">
         <v>37</v>
       </c>
@@ -9560,7 +9721,9 @@
       <c r="N14" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O14" s="20"/>
+      <c r="O14" s="20" t="s">
+        <v>760</v>
+      </c>
       <c r="P14" s="19" t="s">
         <v>37</v>
       </c>
@@ -9695,7 +9858,9 @@
       <c r="N17" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O17" s="20"/>
+      <c r="O17" s="20" t="s">
+        <v>761</v>
+      </c>
       <c r="P17" s="19" t="s">
         <v>37</v>
       </c>
@@ -9914,7 +10079,9 @@
       <c r="N22" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O22" s="20"/>
+      <c r="O22" s="20" t="s">
+        <v>762</v>
+      </c>
       <c r="P22" s="19" t="s">
         <v>37</v>
       </c>
@@ -9959,7 +10126,9 @@
       <c r="N23" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O23" s="20"/>
+      <c r="O23" s="20" t="s">
+        <v>763</v>
+      </c>
       <c r="P23" s="19" t="s">
         <v>37</v>
       </c>
@@ -10003,7 +10172,7 @@
       </c>
       <c r="N24" s="36"/>
       <c r="O24" s="43" t="s">
-        <v>266</v>
+        <v>764</v>
       </c>
       <c r="P24" s="19" t="s">
         <v>37</v>
@@ -10818,7 +10987,9 @@
       <c r="N42" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O42" s="43"/>
+      <c r="O42" s="43" t="s">
+        <v>765</v>
+      </c>
       <c r="P42" s="42" t="s">
         <v>37</v>
       </c>
@@ -11002,7 +11173,9 @@
       <c r="N46" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O46" s="42"/>
+      <c r="O46" s="42" t="s">
+        <v>766</v>
+      </c>
       <c r="P46" s="42" t="s">
         <v>32</v>
       </c>
@@ -11137,7 +11310,9 @@
       <c r="N49" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O49" s="20"/>
+      <c r="O49" s="20" t="s">
+        <v>767</v>
+      </c>
       <c r="P49" s="19" t="s">
         <v>37</v>
       </c>
@@ -11182,7 +11357,9 @@
       <c r="N50" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O50" s="20"/>
+      <c r="O50" s="20" t="s">
+        <v>768</v>
+      </c>
       <c r="P50" s="55" t="s">
         <v>32</v>
       </c>
@@ -11225,7 +11402,9 @@
       <c r="N51" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O51" s="43"/>
+      <c r="O51" s="43" t="s">
+        <v>769</v>
+      </c>
       <c r="P51" s="42" t="s">
         <v>37</v>
       </c>
@@ -11358,7 +11537,9 @@
       <c r="N54" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O54" s="43"/>
+      <c r="O54" s="43" t="s">
+        <v>770</v>
+      </c>
       <c r="P54" s="42" t="s">
         <v>37</v>
       </c>
@@ -11401,7 +11582,9 @@
       <c r="N55" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O55" s="43"/>
+      <c r="O55" s="43" t="s">
+        <v>771</v>
+      </c>
       <c r="P55" s="42" t="s">
         <v>37</v>
       </c>
@@ -11447,7 +11630,7 @@
         <v>31</v>
       </c>
       <c r="O56" s="38" t="s">
-        <v>411</v>
+        <v>772</v>
       </c>
       <c r="P56" s="55" t="s">
         <v>32</v>
@@ -11675,7 +11858,9 @@
       <c r="N61" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O61" s="43"/>
+      <c r="O61" s="43" t="s">
+        <v>773</v>
+      </c>
       <c r="P61" s="42" t="s">
         <v>37</v>
       </c>
@@ -11918,7 +12103,9 @@
       <c r="N10" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O10" s="20"/>
+      <c r="O10" s="20" t="s">
+        <v>774</v>
+      </c>
       <c r="P10" s="19" t="s">
         <v>37</v>
       </c>
@@ -12008,7 +12195,9 @@
       <c r="N12" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O12" s="20"/>
+      <c r="O12" s="20" t="s">
+        <v>775</v>
+      </c>
       <c r="P12" s="19" t="s">
         <v>37</v>
       </c>
@@ -12051,7 +12240,9 @@
       <c r="N13" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O13" s="20"/>
+      <c r="O13" s="20" t="s">
+        <v>776</v>
+      </c>
       <c r="P13" s="19" t="s">
         <v>37</v>
       </c>
@@ -12143,7 +12334,9 @@
       <c r="N15" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O15" s="20"/>
+      <c r="O15" s="20" t="s">
+        <v>777</v>
+      </c>
       <c r="P15" s="19" t="s">
         <v>37</v>
       </c>
@@ -12231,7 +12424,9 @@
       <c r="N17" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O17" s="20"/>
+      <c r="O17" s="20" t="s">
+        <v>778</v>
+      </c>
       <c r="P17" s="19" t="s">
         <v>37</v>
       </c>
@@ -12274,7 +12469,9 @@
       <c r="N18" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O18" s="20"/>
+      <c r="O18" s="20" t="s">
+        <v>779</v>
+      </c>
       <c r="P18" s="19" t="s">
         <v>37</v>
       </c>
@@ -12505,7 +12702,9 @@
       <c r="N23" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O23" s="43"/>
+      <c r="O23" s="43" t="s">
+        <v>780</v>
+      </c>
       <c r="P23" s="42" t="s">
         <v>37</v>
       </c>
@@ -12640,7 +12839,9 @@
       <c r="N26" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O26" s="43"/>
+      <c r="O26" s="43" t="s">
+        <v>781</v>
+      </c>
       <c r="P26" s="42" t="s">
         <v>37</v>
       </c>
@@ -13957,7 +14158,7 @@
         <v>31</v>
       </c>
       <c r="O10" s="43" t="s">
-        <v>475</v>
+        <v>782</v>
       </c>
       <c r="P10" s="75" t="s">
         <v>604</v>
@@ -14002,7 +14203,7 @@
         <v>31</v>
       </c>
       <c r="O11" s="43" t="s">
-        <v>475</v>
+        <v>783</v>
       </c>
       <c r="P11" s="75" t="s">
         <v>604</v>
@@ -14094,7 +14295,7 @@
         <v>31</v>
       </c>
       <c r="O13" s="43" t="s">
-        <v>475</v>
+        <v>784</v>
       </c>
       <c r="P13" s="75" t="s">
         <v>604</v>
@@ -14139,7 +14340,7 @@
         <v>31</v>
       </c>
       <c r="O14" s="43" t="s">
-        <v>475</v>
+        <v>785</v>
       </c>
       <c r="P14" s="75" t="s">
         <v>604</v>
@@ -14229,7 +14430,7 @@
         <v>31</v>
       </c>
       <c r="O16" s="43" t="s">
-        <v>475</v>
+        <v>786</v>
       </c>
       <c r="P16" s="75" t="s">
         <v>604</v>
@@ -14500,7 +14701,9 @@
       <c r="N22" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O22" s="20"/>
+      <c r="O22" s="20" t="s">
+        <v>787</v>
+      </c>
       <c r="P22" s="22" t="s">
         <v>37</v>
       </c>
@@ -14545,7 +14748,9 @@
       <c r="N23" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O23" s="20"/>
+      <c r="O23" s="20" t="s">
+        <v>788</v>
+      </c>
       <c r="P23" s="22" t="s">
         <v>37</v>
       </c>
@@ -14590,7 +14795,9 @@
       <c r="N24" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O24" s="20"/>
+      <c r="O24" s="20" t="s">
+        <v>789</v>
+      </c>
       <c r="P24" s="22" t="s">
         <v>37</v>
       </c>
@@ -14682,7 +14889,9 @@
       <c r="N26" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O26" s="20"/>
+      <c r="O26" s="20" t="s">
+        <v>790</v>
+      </c>
       <c r="P26" s="22" t="s">
         <v>37</v>
       </c>
@@ -14725,7 +14934,9 @@
       <c r="N27" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O27" s="20"/>
+      <c r="O27" s="20" t="s">
+        <v>791</v>
+      </c>
       <c r="P27" s="51" t="s">
         <v>32</v>
       </c>
@@ -14768,7 +14979,9 @@
       <c r="N28" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O28" s="20"/>
+      <c r="O28" s="20" t="s">
+        <v>792</v>
+      </c>
       <c r="P28" s="22" t="s">
         <v>37</v>
       </c>
@@ -14811,7 +15024,9 @@
       <c r="N29" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O29" s="20"/>
+      <c r="O29" s="20" t="s">
+        <v>793</v>
+      </c>
       <c r="P29" s="22" t="s">
         <v>37</v>
       </c>
@@ -14854,7 +15069,9 @@
       <c r="N30" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O30" s="20"/>
+      <c r="O30" s="20" t="s">
+        <v>794</v>
+      </c>
       <c r="P30" s="22" t="s">
         <v>37</v>
       </c>
@@ -15153,7 +15370,7 @@
       </c>
       <c r="N10" s="36"/>
       <c r="O10" s="43" t="s">
-        <v>555</v>
+        <v>795</v>
       </c>
       <c r="P10" s="22" t="s">
         <v>37</v>
@@ -15560,7 +15777,7 @@
       </c>
       <c r="N19" s="36"/>
       <c r="O19" s="43" t="s">
-        <v>555</v>
+        <v>796</v>
       </c>
       <c r="P19" s="22" t="s">
         <v>37</v>

--- a/docs/結合試験項目一覧.xlsx
+++ b/docs/結合試験項目一覧.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1694" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="797">
   <si>
     <t>●参加者ビュー</t>
   </si>
@@ -8122,12 +8122,8 @@
       <c r="L9" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N9" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M9" s="37"/>
+      <c r="N9" s="36"/>
       <c r="O9" s="20" t="s">
         <v>750</v>
       </c>
@@ -8169,12 +8165,8 @@
       <c r="L10" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M10" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N10" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M10" s="37"/>
+      <c r="N10" s="36"/>
       <c r="O10" s="20" t="s">
         <v>751</v>
       </c>
@@ -8216,12 +8208,8 @@
       <c r="L11" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M11" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N11" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M11" s="37"/>
+      <c r="N11" s="36"/>
       <c r="O11" s="20" t="s">
         <v>752</v>
       </c>
@@ -8261,12 +8249,8 @@
       <c r="L12" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M12" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N12" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M12" s="37"/>
+      <c r="N12" s="36"/>
       <c r="O12" s="20" t="s">
         <v>753</v>
       </c>
@@ -8304,14 +8288,10 @@
         <v>160</v>
       </c>
       <c r="L13" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M13" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N13" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M13" s="37"/>
+      <c r="N13" s="36"/>
       <c r="O13" s="20" t="s">
         <v>606</v>
       </c>
@@ -8349,14 +8329,10 @@
         <v>163</v>
       </c>
       <c r="L14" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M14" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N14" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M14" s="37"/>
+      <c r="N14" s="36"/>
       <c r="O14" s="20" t="s">
         <v>754</v>
       </c>
@@ -8394,14 +8370,10 @@
         <v>166</v>
       </c>
       <c r="L15" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M15" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N15" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M15" s="37"/>
+      <c r="N15" s="36"/>
       <c r="O15" s="20" t="s">
         <v>607</v>
       </c>
@@ -8439,14 +8411,10 @@
         <v>169</v>
       </c>
       <c r="L16" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M16" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N16" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M16" s="37"/>
+      <c r="N16" s="36"/>
       <c r="O16" s="20" t="s">
         <v>703</v>
       </c>
@@ -8486,12 +8454,8 @@
       <c r="L17" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M17" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N17" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M17" s="37"/>
+      <c r="N17" s="36"/>
       <c r="O17" s="20" t="s">
         <v>755</v>
       </c>
@@ -8529,14 +8493,10 @@
         <v>174</v>
       </c>
       <c r="L18" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M18" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N18" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M18" s="37"/>
+      <c r="N18" s="36"/>
       <c r="O18" s="20" t="s">
         <v>609</v>
       </c>
@@ -8744,14 +8704,10 @@
         <v>181</v>
       </c>
       <c r="L9" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N9" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M9" s="37"/>
+      <c r="N9" s="36"/>
       <c r="O9" s="20" t="s">
         <v>610</v>
       </c>
@@ -8791,14 +8747,10 @@
         <v>184</v>
       </c>
       <c r="L10" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M10" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N10" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M10" s="37"/>
+      <c r="N10" s="36"/>
       <c r="O10" s="20" t="s">
         <v>611</v>
       </c>
@@ -8838,12 +8790,8 @@
       <c r="L11" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="M11" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N11" s="39" t="s">
-        <v>31</v>
-      </c>
+      <c r="M11" s="37"/>
+      <c r="N11" s="39"/>
       <c r="O11" s="20" t="s">
         <v>756</v>
       </c>
@@ -8883,12 +8831,8 @@
       <c r="L12" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="M12" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N12" s="39" t="s">
-        <v>31</v>
-      </c>
+      <c r="M12" s="37"/>
+      <c r="N12" s="39"/>
       <c r="O12" s="20" t="s">
         <v>757</v>
       </c>
@@ -8926,14 +8870,10 @@
         <v>195</v>
       </c>
       <c r="L13" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M13" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N13" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M13" s="37"/>
+      <c r="N13" s="36"/>
       <c r="O13" s="20" t="s">
         <v>612</v>
       </c>
@@ -8971,14 +8911,10 @@
         <v>197</v>
       </c>
       <c r="L14" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M14" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N14" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M14" s="37"/>
+      <c r="N14" s="36"/>
       <c r="O14" s="20" t="s">
         <v>613</v>
       </c>
@@ -9018,14 +8954,10 @@
         <v>201</v>
       </c>
       <c r="L15" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M15" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N15" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M15" s="37"/>
+      <c r="N15" s="36"/>
       <c r="O15" s="20" t="s">
         <v>704</v>
       </c>
@@ -9063,14 +8995,10 @@
         <v>205</v>
       </c>
       <c r="L16" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M16" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N16" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M16" s="37"/>
+      <c r="N16" s="36"/>
       <c r="O16" s="20" t="s">
         <v>615</v>
       </c>
@@ -9108,14 +9036,10 @@
         <v>208</v>
       </c>
       <c r="L17" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M17" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N17" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M17" s="37"/>
+      <c r="N17" s="36"/>
       <c r="O17" s="20" t="s">
         <v>616</v>
       </c>
@@ -9153,14 +9077,10 @@
         <v>211</v>
       </c>
       <c r="L18" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M18" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N18" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M18" s="37"/>
+      <c r="N18" s="36"/>
       <c r="O18" s="20" t="s">
         <v>705</v>
       </c>
@@ -9198,14 +9118,10 @@
         <v>215</v>
       </c>
       <c r="L19" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M19" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N19" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M19" s="37"/>
+      <c r="N19" s="36"/>
       <c r="O19" s="20" t="s">
         <v>618</v>
       </c>
@@ -9247,12 +9163,8 @@
       <c r="L20" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="M20" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N20" s="39" t="s">
-        <v>31</v>
-      </c>
+      <c r="M20" s="37"/>
+      <c r="N20" s="39"/>
       <c r="O20" s="20" t="s">
         <v>758</v>
       </c>
@@ -9294,12 +9206,8 @@
       <c r="L21" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="M21" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N21" s="39" t="s">
-        <v>31</v>
-      </c>
+      <c r="M21" s="37"/>
+      <c r="N21" s="39"/>
       <c r="O21" s="20" t="s">
         <v>759</v>
       </c>
@@ -9486,14 +9394,10 @@
         <v>231</v>
       </c>
       <c r="L9" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N9" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M9" s="37"/>
+      <c r="N9" s="36"/>
       <c r="O9" s="20" t="s">
         <v>619</v>
       </c>
@@ -9531,14 +9435,10 @@
         <v>234</v>
       </c>
       <c r="L10" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M10" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N10" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M10" s="37"/>
+      <c r="N10" s="36"/>
       <c r="O10" s="20" t="s">
         <v>706</v>
       </c>
@@ -9576,14 +9476,10 @@
         <v>239</v>
       </c>
       <c r="L11" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M11" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N11" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M11" s="37"/>
+      <c r="N11" s="36"/>
       <c r="O11" s="20" t="s">
         <v>621</v>
       </c>
@@ -9621,14 +9517,10 @@
         <v>243</v>
       </c>
       <c r="L12" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M12" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N12" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M12" s="37"/>
+      <c r="N12" s="36"/>
       <c r="O12" s="20" t="s">
         <v>622</v>
       </c>
@@ -9668,14 +9560,10 @@
         <v>247</v>
       </c>
       <c r="L13" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M13" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N13" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M13" s="37"/>
+      <c r="N13" s="36"/>
       <c r="O13" s="20" t="s">
         <v>623</v>
       </c>
@@ -9715,12 +9603,8 @@
       <c r="L14" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M14" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N14" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M14" s="37"/>
+      <c r="N14" s="36"/>
       <c r="O14" s="20" t="s">
         <v>760</v>
       </c>
@@ -9758,14 +9642,10 @@
         <v>254</v>
       </c>
       <c r="L15" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M15" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N15" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M15" s="37"/>
+      <c r="N15" s="36"/>
       <c r="O15" s="20" t="s">
         <v>624</v>
       </c>
@@ -9805,14 +9685,10 @@
         <v>257</v>
       </c>
       <c r="L16" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M16" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N16" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M16" s="37"/>
+      <c r="N16" s="36"/>
       <c r="O16" s="20" t="s">
         <v>625</v>
       </c>
@@ -9852,12 +9728,8 @@
       <c r="L17" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M17" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N17" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M17" s="37"/>
+      <c r="N17" s="36"/>
       <c r="O17" s="20" t="s">
         <v>761</v>
       </c>
@@ -9899,9 +9771,7 @@
       <c r="L18" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M18" s="37">
-        <v>46233</v>
-      </c>
+      <c r="M18" s="37"/>
       <c r="N18" s="36"/>
       <c r="O18" s="43" t="s">
         <v>266</v>
@@ -9942,9 +9812,7 @@
       <c r="L19" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M19" s="37">
-        <v>46233</v>
-      </c>
+      <c r="M19" s="37"/>
       <c r="N19" s="36"/>
       <c r="O19" s="43" t="s">
         <v>266</v>
@@ -9985,9 +9853,7 @@
       <c r="L20" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M20" s="37">
-        <v>46233</v>
-      </c>
+      <c r="M20" s="37"/>
       <c r="N20" s="36"/>
       <c r="O20" s="43" t="s">
         <v>266</v>
@@ -10028,9 +9894,7 @@
       <c r="L21" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M21" s="37">
-        <v>46233</v>
-      </c>
+      <c r="M21" s="37"/>
       <c r="N21" s="36"/>
       <c r="O21" s="43" t="s">
         <v>266</v>
@@ -10073,12 +9937,8 @@
       <c r="L22" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M22" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N22" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M22" s="37"/>
+      <c r="N22" s="36"/>
       <c r="O22" s="20" t="s">
         <v>762</v>
       </c>
@@ -10120,12 +9980,8 @@
       <c r="L23" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M23" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N23" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M23" s="37"/>
+      <c r="N23" s="36"/>
       <c r="O23" s="20" t="s">
         <v>763</v>
       </c>
@@ -10167,9 +10023,7 @@
       <c r="L24" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M24" s="37">
-        <v>46233</v>
-      </c>
+      <c r="M24" s="37"/>
       <c r="N24" s="36"/>
       <c r="O24" s="43" t="s">
         <v>764</v>
@@ -10208,14 +10062,10 @@
         <v>290</v>
       </c>
       <c r="L25" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M25" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N25" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M25" s="37"/>
+      <c r="N25" s="36"/>
       <c r="O25" s="20" t="s">
         <v>707</v>
       </c>
@@ -10255,14 +10105,10 @@
         <v>293</v>
       </c>
       <c r="L26" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M26" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N26" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M26" s="37"/>
+      <c r="N26" s="36"/>
       <c r="O26" s="20" t="s">
         <v>627</v>
       </c>
@@ -10300,14 +10146,10 @@
         <v>295</v>
       </c>
       <c r="L27" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M27" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N27" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M27" s="37"/>
+      <c r="N27" s="36"/>
       <c r="O27" s="20" t="s">
         <v>708</v>
       </c>
@@ -10345,14 +10187,10 @@
         <v>299</v>
       </c>
       <c r="L28" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M28" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N28" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M28" s="37"/>
+      <c r="N28" s="36"/>
       <c r="O28" s="20" t="s">
         <v>629</v>
       </c>
@@ -10392,14 +10230,10 @@
         <v>302</v>
       </c>
       <c r="L29" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M29" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N29" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M29" s="37"/>
+      <c r="N29" s="36"/>
       <c r="O29" s="20" t="s">
         <v>630</v>
       </c>
@@ -10437,14 +10271,10 @@
         <v>306</v>
       </c>
       <c r="L30" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M30" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N30" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M30" s="37"/>
+      <c r="N30" s="36"/>
       <c r="O30" s="20" t="s">
         <v>631</v>
       </c>
@@ -10482,14 +10312,10 @@
         <v>311</v>
       </c>
       <c r="L31" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M31" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N31" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M31" s="37"/>
+      <c r="N31" s="36"/>
       <c r="O31" s="20" t="s">
         <v>632</v>
       </c>
@@ -10527,14 +10353,10 @@
         <v>315</v>
       </c>
       <c r="L32" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M32" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N32" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M32" s="37"/>
+      <c r="N32" s="36"/>
       <c r="O32" s="20" t="s">
         <v>709</v>
       </c>
@@ -10572,14 +10394,10 @@
         <v>318</v>
       </c>
       <c r="L33" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M33" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N33" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M33" s="37"/>
+      <c r="N33" s="36"/>
       <c r="O33" s="20" t="s">
         <v>710</v>
       </c>
@@ -10617,14 +10435,10 @@
         <v>323</v>
       </c>
       <c r="L34" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M34" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N34" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M34" s="37"/>
+      <c r="N34" s="36"/>
       <c r="O34" s="20" t="s">
         <v>635</v>
       </c>
@@ -10662,14 +10476,10 @@
         <v>327</v>
       </c>
       <c r="L35" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M35" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N35" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M35" s="37"/>
+      <c r="N35" s="36"/>
       <c r="O35" s="43" t="s">
         <v>711</v>
       </c>
@@ -10707,14 +10517,10 @@
         <v>332</v>
       </c>
       <c r="L36" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M36" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N36" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M36" s="37"/>
+      <c r="N36" s="36"/>
       <c r="O36" s="43" t="s">
         <v>712</v>
       </c>
@@ -10752,14 +10558,10 @@
         <v>336</v>
       </c>
       <c r="L37" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M37" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N37" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M37" s="37"/>
+      <c r="N37" s="36"/>
       <c r="O37" s="43" t="s">
         <v>713</v>
       </c>
@@ -10797,14 +10599,10 @@
         <v>339</v>
       </c>
       <c r="L38" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M38" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N38" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M38" s="37"/>
+      <c r="N38" s="36"/>
       <c r="O38" s="43" t="s">
         <v>714</v>
       </c>
@@ -10842,14 +10640,10 @@
         <v>343</v>
       </c>
       <c r="L39" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M39" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N39" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M39" s="37"/>
+      <c r="N39" s="36"/>
       <c r="O39" s="43" t="s">
         <v>640</v>
       </c>
@@ -10889,14 +10683,10 @@
         <v>348</v>
       </c>
       <c r="L40" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M40" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N40" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M40" s="37"/>
+      <c r="N40" s="36"/>
       <c r="O40" s="43" t="s">
         <v>715</v>
       </c>
@@ -10934,14 +10724,10 @@
         <v>353</v>
       </c>
       <c r="L41" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M41" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N41" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M41" s="37"/>
+      <c r="N41" s="36"/>
       <c r="O41" s="43" t="s">
         <v>716</v>
       </c>
@@ -10981,12 +10767,8 @@
       <c r="L42" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M42" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N42" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M42" s="37"/>
+      <c r="N42" s="36"/>
       <c r="O42" s="43" t="s">
         <v>765</v>
       </c>
@@ -11024,14 +10806,10 @@
         <v>361</v>
       </c>
       <c r="L43" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M43" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N43" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M43" s="37"/>
+      <c r="N43" s="36"/>
       <c r="O43" s="43" t="s">
         <v>643</v>
       </c>
@@ -11075,14 +10853,10 @@
         <v>365</v>
       </c>
       <c r="L44" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M44" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N44" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M44" s="37"/>
+      <c r="N44" s="36"/>
       <c r="O44" s="43" t="s">
         <v>644</v>
       </c>
@@ -11120,14 +10894,10 @@
         <v>369</v>
       </c>
       <c r="L45" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M45" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N45" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M45" s="37"/>
+      <c r="N45" s="36"/>
       <c r="O45" s="42" t="s">
         <v>645</v>
       </c>
@@ -11165,14 +10935,10 @@
         <v>372</v>
       </c>
       <c r="L46" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M46" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N46" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M46" s="37"/>
+      <c r="N46" s="36"/>
       <c r="O46" s="42" t="s">
         <v>766</v>
       </c>
@@ -11212,14 +10978,10 @@
         <v>376</v>
       </c>
       <c r="L47" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M47" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N47" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M47" s="37"/>
+      <c r="N47" s="36"/>
       <c r="O47" s="42" t="s">
         <v>646</v>
       </c>
@@ -11257,14 +11019,10 @@
         <v>380</v>
       </c>
       <c r="L48" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="M48" s="20">
-        <v>46232</v>
-      </c>
-      <c r="N48" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M48" s="20"/>
+      <c r="N48" s="36"/>
       <c r="O48" s="20" t="s">
         <v>647</v>
       </c>
@@ -11304,12 +11062,8 @@
       <c r="L49" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="M49" s="20">
-        <v>46233</v>
-      </c>
-      <c r="N49" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M49" s="20"/>
+      <c r="N49" s="36"/>
       <c r="O49" s="20" t="s">
         <v>767</v>
       </c>
@@ -11349,14 +11103,10 @@
         <v>386</v>
       </c>
       <c r="L50" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M50" s="20">
-        <v>46233</v>
-      </c>
-      <c r="N50" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M50" s="20"/>
+      <c r="N50" s="36"/>
       <c r="O50" s="20" t="s">
         <v>768</v>
       </c>
@@ -11396,12 +11146,8 @@
       <c r="L51" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M51" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N51" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M51" s="37"/>
+      <c r="N51" s="36"/>
       <c r="O51" s="43" t="s">
         <v>769</v>
       </c>
@@ -11439,14 +11185,10 @@
         <v>393</v>
       </c>
       <c r="L52" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M52" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N52" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M52" s="37"/>
+      <c r="N52" s="36"/>
       <c r="O52" s="43" t="s">
         <v>717</v>
       </c>
@@ -11484,14 +11226,10 @@
         <v>398</v>
       </c>
       <c r="L53" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M53" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N53" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M53" s="37"/>
+      <c r="N53" s="36"/>
       <c r="O53" s="43" t="s">
         <v>718</v>
       </c>
@@ -11531,12 +11269,8 @@
       <c r="L54" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M54" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N54" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M54" s="37"/>
+      <c r="N54" s="36"/>
       <c r="O54" s="43" t="s">
         <v>770</v>
       </c>
@@ -11576,12 +11310,8 @@
       <c r="L55" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M55" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N55" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M55" s="37"/>
+      <c r="N55" s="36"/>
       <c r="O55" s="43" t="s">
         <v>771</v>
       </c>
@@ -11623,12 +11353,8 @@
       <c r="L56" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M56" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N56" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M56" s="37"/>
+      <c r="N56" s="36"/>
       <c r="O56" s="38" t="s">
         <v>772</v>
       </c>
@@ -11666,14 +11392,10 @@
         <v>414</v>
       </c>
       <c r="L57" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M57" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N57" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M57" s="37"/>
+      <c r="N57" s="36"/>
       <c r="O57" s="43" t="s">
         <v>650</v>
       </c>
@@ -11711,14 +11433,10 @@
         <v>419</v>
       </c>
       <c r="L58" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M58" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N58" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M58" s="37"/>
+      <c r="N58" s="36"/>
       <c r="O58" s="43" t="s">
         <v>719</v>
       </c>
@@ -11758,14 +11476,10 @@
         <v>421</v>
       </c>
       <c r="L59" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M59" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N59" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M59" s="37"/>
+      <c r="N59" s="36"/>
       <c r="O59" s="43" t="s">
         <v>720</v>
       </c>
@@ -11805,14 +11519,10 @@
         <v>424</v>
       </c>
       <c r="L60" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="M60" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N60" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M60" s="37"/>
+      <c r="N60" s="36"/>
       <c r="O60" s="43" t="s">
         <v>721</v>
       </c>
@@ -11852,12 +11562,8 @@
       <c r="L61" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M61" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N61" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M61" s="37"/>
+      <c r="N61" s="36"/>
       <c r="O61" s="43" t="s">
         <v>773</v>
       </c>
@@ -12050,14 +11756,10 @@
         <v>29</v>
       </c>
       <c r="L9" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N9" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M9" s="37"/>
+      <c r="N9" s="36"/>
       <c r="O9" s="20" t="s">
         <v>654</v>
       </c>
@@ -12097,12 +11799,8 @@
       <c r="L10" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M10" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N10" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M10" s="37"/>
+      <c r="N10" s="36"/>
       <c r="O10" s="20" t="s">
         <v>774</v>
       </c>
@@ -12142,14 +11840,10 @@
         <v>41</v>
       </c>
       <c r="L11" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M11" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N11" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M11" s="37"/>
+      <c r="N11" s="36"/>
       <c r="O11" s="20" t="s">
         <v>655</v>
       </c>
@@ -12189,12 +11883,8 @@
       <c r="L12" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M12" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N12" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M12" s="37"/>
+      <c r="N12" s="36"/>
       <c r="O12" s="20" t="s">
         <v>775</v>
       </c>
@@ -12234,12 +11924,8 @@
       <c r="L13" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M13" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N13" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M13" s="37"/>
+      <c r="N13" s="36"/>
       <c r="O13" s="20" t="s">
         <v>776</v>
       </c>
@@ -12279,14 +11965,10 @@
         <v>53</v>
       </c>
       <c r="L14" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M14" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N14" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M14" s="37"/>
+      <c r="N14" s="36"/>
       <c r="O14" s="20" t="s">
         <v>722</v>
       </c>
@@ -12328,12 +12010,8 @@
       <c r="L15" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M15" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N15" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M15" s="37"/>
+      <c r="N15" s="36"/>
       <c r="O15" s="20" t="s">
         <v>777</v>
       </c>
@@ -12371,14 +12049,10 @@
         <v>63</v>
       </c>
       <c r="L16" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M16" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N16" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M16" s="37"/>
+      <c r="N16" s="36"/>
       <c r="O16" s="20" t="s">
         <v>657</v>
       </c>
@@ -12418,12 +12092,8 @@
       <c r="L17" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M17" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N17" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M17" s="37"/>
+      <c r="N17" s="36"/>
       <c r="O17" s="20" t="s">
         <v>778</v>
       </c>
@@ -12463,12 +12133,8 @@
       <c r="L18" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M18" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N18" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M18" s="37"/>
+      <c r="N18" s="36"/>
       <c r="O18" s="20" t="s">
         <v>779</v>
       </c>
@@ -12506,14 +12172,10 @@
         <v>74</v>
       </c>
       <c r="L19" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M19" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N19" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M19" s="37"/>
+      <c r="N19" s="36"/>
       <c r="O19" s="20" t="s">
         <v>658</v>
       </c>
@@ -12553,14 +12215,10 @@
         <v>79</v>
       </c>
       <c r="L20" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M20" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N20" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M20" s="37"/>
+      <c r="N20" s="36"/>
       <c r="O20" s="20" t="s">
         <v>723</v>
       </c>
@@ -12600,14 +12258,10 @@
         <v>84</v>
       </c>
       <c r="L21" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M21" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N21" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M21" s="37"/>
+      <c r="N21" s="36"/>
       <c r="O21" s="20" t="s">
         <v>724</v>
       </c>
@@ -12647,14 +12301,10 @@
         <v>88</v>
       </c>
       <c r="L22" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M22" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N22" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M22" s="37"/>
+      <c r="N22" s="36"/>
       <c r="O22" s="20" t="s">
         <v>661</v>
       </c>
@@ -12696,12 +12346,8 @@
       <c r="L23" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M23" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N23" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M23" s="37"/>
+      <c r="N23" s="36"/>
       <c r="O23" s="43" t="s">
         <v>780</v>
       </c>
@@ -12741,14 +12387,10 @@
         <v>94</v>
       </c>
       <c r="L24" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M24" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N24" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M24" s="37"/>
+      <c r="N24" s="36"/>
       <c r="O24" s="43" t="s">
         <v>725</v>
       </c>
@@ -12786,14 +12428,10 @@
         <v>98</v>
       </c>
       <c r="L25" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M25" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N25" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M25" s="37"/>
+      <c r="N25" s="36"/>
       <c r="O25" s="43" t="s">
         <v>726</v>
       </c>
@@ -12833,12 +12471,8 @@
       <c r="L26" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M26" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N26" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M26" s="37"/>
+      <c r="N26" s="36"/>
       <c r="O26" s="43" t="s">
         <v>781</v>
       </c>
@@ -12876,14 +12510,10 @@
         <v>106</v>
       </c>
       <c r="L27" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M27" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N27" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M27" s="37"/>
+      <c r="N27" s="36"/>
       <c r="O27" s="43" t="s">
         <v>727</v>
       </c>
@@ -12921,14 +12551,10 @@
         <v>111</v>
       </c>
       <c r="L28" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M28" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N28" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M28" s="37"/>
+      <c r="N28" s="36"/>
       <c r="O28" s="43" t="s">
         <v>665</v>
       </c>
@@ -12966,14 +12592,10 @@
         <v>114</v>
       </c>
       <c r="L29" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M29" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N29" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M29" s="37"/>
+      <c r="N29" s="36"/>
       <c r="O29" s="43" t="s">
         <v>666</v>
       </c>
@@ -13011,14 +12633,10 @@
         <v>117</v>
       </c>
       <c r="L30" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M30" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N30" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M30" s="37"/>
+      <c r="N30" s="36"/>
       <c r="O30" s="43" t="s">
         <v>667</v>
       </c>
@@ -13056,14 +12674,10 @@
         <v>120</v>
       </c>
       <c r="L31" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M31" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N31" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M31" s="37"/>
+      <c r="N31" s="36"/>
       <c r="O31" s="43" t="s">
         <v>728</v>
       </c>
@@ -13101,14 +12715,10 @@
         <v>123</v>
       </c>
       <c r="L32" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M32" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N32" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M32" s="37"/>
+      <c r="N32" s="36"/>
       <c r="O32" s="43" t="s">
         <v>669</v>
       </c>
@@ -13146,14 +12756,10 @@
         <v>125</v>
       </c>
       <c r="L33" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M33" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N33" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M33" s="37"/>
+      <c r="N33" s="36"/>
       <c r="O33" s="43" t="s">
         <v>670</v>
       </c>
@@ -13193,14 +12799,10 @@
         <v>129</v>
       </c>
       <c r="L34" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M34" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N34" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M34" s="37"/>
+      <c r="N34" s="36"/>
       <c r="O34" s="43" t="s">
         <v>671</v>
       </c>
@@ -13238,14 +12840,10 @@
         <v>132</v>
       </c>
       <c r="L35" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M35" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N35" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M35" s="37"/>
+      <c r="N35" s="36"/>
       <c r="O35" s="45" t="s">
         <v>729</v>
       </c>
@@ -13283,14 +12881,10 @@
         <v>135</v>
       </c>
       <c r="L36" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M36" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N36" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M36" s="37"/>
+      <c r="N36" s="36"/>
       <c r="O36" s="59" t="s">
         <v>673</v>
       </c>
@@ -13489,14 +13083,10 @@
         <v>435</v>
       </c>
       <c r="L9" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N9" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M9" s="37"/>
+      <c r="N9" s="36"/>
       <c r="O9" s="20" t="s">
         <v>674</v>
       </c>
@@ -13534,14 +13124,10 @@
         <v>438</v>
       </c>
       <c r="L10" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M10" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N10" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M10" s="37"/>
+      <c r="N10" s="36"/>
       <c r="O10" s="20" t="s">
         <v>675</v>
       </c>
@@ -13579,14 +13165,10 @@
         <v>441</v>
       </c>
       <c r="L11" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M11" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N11" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M11" s="37"/>
+      <c r="N11" s="36"/>
       <c r="O11" s="20" t="s">
         <v>676</v>
       </c>
@@ -13624,14 +13206,10 @@
         <v>442</v>
       </c>
       <c r="L12" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M12" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N12" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M12" s="37"/>
+      <c r="N12" s="36"/>
       <c r="O12" s="20" t="s">
         <v>677</v>
       </c>
@@ -13669,14 +13247,10 @@
         <v>444</v>
       </c>
       <c r="L13" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M13" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N13" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M13" s="37"/>
+      <c r="N13" s="36"/>
       <c r="O13" s="20" t="s">
         <v>730</v>
       </c>
@@ -13714,14 +13288,10 @@
         <v>446</v>
       </c>
       <c r="L14" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M14" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N14" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M14" s="37"/>
+      <c r="N14" s="36"/>
       <c r="O14" s="20" t="s">
         <v>679</v>
       </c>
@@ -13759,14 +13329,10 @@
         <v>449</v>
       </c>
       <c r="L15" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M15" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N15" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M15" s="37"/>
+      <c r="N15" s="36"/>
       <c r="O15" s="20" t="s">
         <v>731</v>
       </c>
@@ -13804,14 +13370,10 @@
         <v>454</v>
       </c>
       <c r="L16" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M16" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N16" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M16" s="37"/>
+      <c r="N16" s="36"/>
       <c r="O16" s="20" t="s">
         <v>732</v>
       </c>
@@ -13849,14 +13411,10 @@
         <v>458</v>
       </c>
       <c r="L17" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M17" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N17" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M17" s="37"/>
+      <c r="N17" s="36"/>
       <c r="O17" s="20" t="s">
         <v>733</v>
       </c>
@@ -13894,14 +13452,10 @@
         <v>462</v>
       </c>
       <c r="L18" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M18" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N18" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M18" s="37"/>
+      <c r="N18" s="36"/>
       <c r="O18" s="34"/>
       <c r="P18" s="52" t="s">
         <v>32</v>
@@ -14102,14 +13656,10 @@
         <v>471</v>
       </c>
       <c r="L9" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N9" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M9" s="37"/>
+      <c r="N9" s="36"/>
       <c r="O9" s="20" t="s">
         <v>683</v>
       </c>
@@ -14149,14 +13699,10 @@
         <v>474</v>
       </c>
       <c r="L10" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="M10" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N10" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M10" s="37"/>
+      <c r="N10" s="36"/>
       <c r="O10" s="43" t="s">
         <v>782</v>
       </c>
@@ -14194,14 +13740,10 @@
         <v>478</v>
       </c>
       <c r="L11" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="M11" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N11" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M11" s="37"/>
+      <c r="N11" s="36"/>
       <c r="O11" s="43" t="s">
         <v>783</v>
       </c>
@@ -14239,14 +13781,10 @@
         <v>481</v>
       </c>
       <c r="L12" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M12" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N12" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M12" s="37"/>
+      <c r="N12" s="36"/>
       <c r="O12" s="20" t="s">
         <v>734</v>
       </c>
@@ -14286,14 +13824,10 @@
         <v>484</v>
       </c>
       <c r="L13" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="M13" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N13" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M13" s="37"/>
+      <c r="N13" s="36"/>
       <c r="O13" s="43" t="s">
         <v>784</v>
       </c>
@@ -14331,14 +13865,10 @@
         <v>486</v>
       </c>
       <c r="L14" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="M14" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N14" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M14" s="37"/>
+      <c r="N14" s="36"/>
       <c r="O14" s="43" t="s">
         <v>785</v>
       </c>
@@ -14376,14 +13906,10 @@
         <v>489</v>
       </c>
       <c r="L15" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M15" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N15" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M15" s="37"/>
+      <c r="N15" s="36"/>
       <c r="O15" s="20" t="s">
         <v>685</v>
       </c>
@@ -14421,14 +13947,10 @@
         <v>491</v>
       </c>
       <c r="L16" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="M16" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N16" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M16" s="37"/>
+      <c r="N16" s="36"/>
       <c r="O16" s="43" t="s">
         <v>786</v>
       </c>
@@ -14466,14 +13988,10 @@
         <v>495</v>
       </c>
       <c r="L17" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M17" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N17" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M17" s="37"/>
+      <c r="N17" s="36"/>
       <c r="O17" s="20" t="s">
         <v>735</v>
       </c>
@@ -14511,14 +14029,10 @@
         <v>498</v>
       </c>
       <c r="L18" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M18" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N18" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M18" s="37"/>
+      <c r="N18" s="36"/>
       <c r="O18" s="20" t="s">
         <v>736</v>
       </c>
@@ -14556,14 +14070,10 @@
         <v>501</v>
       </c>
       <c r="L19" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M19" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N19" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M19" s="37"/>
+      <c r="N19" s="36"/>
       <c r="O19" s="20" t="s">
         <v>688</v>
       </c>
@@ -14601,14 +14111,10 @@
         <v>505</v>
       </c>
       <c r="L20" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M20" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N20" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M20" s="37"/>
+      <c r="N20" s="36"/>
       <c r="O20" s="20" t="s">
         <v>737</v>
       </c>
@@ -14646,14 +14152,10 @@
         <v>507</v>
       </c>
       <c r="L21" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M21" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N21" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M21" s="37"/>
+      <c r="N21" s="36"/>
       <c r="O21" s="20" t="s">
         <v>738</v>
       </c>
@@ -14695,12 +14197,8 @@
       <c r="L22" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M22" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N22" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M22" s="37"/>
+      <c r="N22" s="36"/>
       <c r="O22" s="20" t="s">
         <v>787</v>
       </c>
@@ -14742,12 +14240,8 @@
       <c r="L23" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M23" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N23" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M23" s="37"/>
+      <c r="N23" s="36"/>
       <c r="O23" s="20" t="s">
         <v>788</v>
       </c>
@@ -14789,12 +14283,8 @@
       <c r="L24" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M24" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N24" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M24" s="37"/>
+      <c r="N24" s="36"/>
       <c r="O24" s="20" t="s">
         <v>789</v>
       </c>
@@ -14834,14 +14324,10 @@
         <v>519</v>
       </c>
       <c r="L25" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M25" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N25" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M25" s="37"/>
+      <c r="N25" s="36"/>
       <c r="O25" s="20" t="s">
         <v>691</v>
       </c>
@@ -14883,12 +14369,8 @@
       <c r="L26" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M26" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N26" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M26" s="37"/>
+      <c r="N26" s="36"/>
       <c r="O26" s="20" t="s">
         <v>790</v>
       </c>
@@ -14926,14 +14408,10 @@
         <v>526</v>
       </c>
       <c r="L27" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M27" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N27" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M27" s="37"/>
+      <c r="N27" s="36"/>
       <c r="O27" s="20" t="s">
         <v>791</v>
       </c>
@@ -14973,12 +14451,8 @@
       <c r="L28" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M28" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N28" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M28" s="37"/>
+      <c r="N28" s="36"/>
       <c r="O28" s="20" t="s">
         <v>792</v>
       </c>
@@ -15018,12 +14492,8 @@
       <c r="L29" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M29" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N29" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M29" s="37"/>
+      <c r="N29" s="36"/>
       <c r="O29" s="20" t="s">
         <v>793</v>
       </c>
@@ -15063,12 +14533,8 @@
       <c r="L30" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M30" s="37">
-        <v>46233</v>
-      </c>
-      <c r="N30" s="36" t="s">
-        <v>31</v>
-      </c>
+      <c r="M30" s="37"/>
+      <c r="N30" s="36"/>
       <c r="O30" s="20" t="s">
         <v>794</v>
       </c>
@@ -15106,14 +14572,10 @@
         <v>539</v>
       </c>
       <c r="L31" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M31" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N31" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M31" s="37"/>
+      <c r="N31" s="36"/>
       <c r="O31" s="34" t="s">
         <v>739</v>
       </c>
@@ -15316,14 +14778,10 @@
         <v>549</v>
       </c>
       <c r="L9" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N9" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M9" s="37"/>
+      <c r="N9" s="36"/>
       <c r="O9" s="20" t="s">
         <v>740</v>
       </c>
@@ -15365,9 +14823,7 @@
       <c r="L10" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="M10" s="37">
-        <v>46233</v>
-      </c>
+      <c r="M10" s="37"/>
       <c r="N10" s="36"/>
       <c r="O10" s="43" t="s">
         <v>795</v>
@@ -15406,14 +14862,10 @@
         <v>560</v>
       </c>
       <c r="L11" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M11" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N11" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M11" s="37"/>
+      <c r="N11" s="36"/>
       <c r="O11" s="20" t="s">
         <v>741</v>
       </c>
@@ -15451,14 +14903,10 @@
         <v>564</v>
       </c>
       <c r="L12" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M12" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N12" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M12" s="37"/>
+      <c r="N12" s="36"/>
       <c r="O12" s="20" t="s">
         <v>742</v>
       </c>
@@ -15496,14 +14944,10 @@
         <v>569</v>
       </c>
       <c r="L13" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M13" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N13" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M13" s="37"/>
+      <c r="N13" s="36"/>
       <c r="O13" s="20" t="s">
         <v>743</v>
       </c>
@@ -15541,14 +14985,10 @@
         <v>574</v>
       </c>
       <c r="L14" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M14" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N14" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M14" s="37"/>
+      <c r="N14" s="36"/>
       <c r="O14" s="20" t="s">
         <v>744</v>
       </c>
@@ -15586,14 +15026,10 @@
         <v>579</v>
       </c>
       <c r="L15" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M15" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N15" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M15" s="37"/>
+      <c r="N15" s="36"/>
       <c r="O15" s="20" t="s">
         <v>745</v>
       </c>
@@ -15633,14 +15069,10 @@
         <v>584</v>
       </c>
       <c r="L16" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M16" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N16" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M16" s="37"/>
+      <c r="N16" s="36"/>
       <c r="O16" s="20" t="s">
         <v>746</v>
       </c>
@@ -15678,14 +15110,10 @@
         <v>588</v>
       </c>
       <c r="L17" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M17" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N17" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M17" s="37"/>
+      <c r="N17" s="36"/>
       <c r="O17" s="20" t="s">
         <v>747</v>
       </c>
@@ -15723,14 +15151,10 @@
         <v>593</v>
       </c>
       <c r="L18" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M18" s="37">
-        <v>46232</v>
-      </c>
-      <c r="N18" s="36" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M18" s="37"/>
+      <c r="N18" s="36"/>
       <c r="O18" s="20" t="s">
         <v>748</v>
       </c>
@@ -15772,9 +15196,7 @@
       <c r="L19" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="M19" s="37">
-        <v>46233</v>
-      </c>
+      <c r="M19" s="37"/>
       <c r="N19" s="36"/>
       <c r="O19" s="43" t="s">
         <v>796</v>
@@ -15813,14 +15235,10 @@
         <v>603</v>
       </c>
       <c r="L20" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="M20" s="53">
-        <v>46232</v>
-      </c>
-      <c r="N20" s="54" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="M20" s="53"/>
+      <c r="N20" s="54"/>
       <c r="O20" s="34" t="s">
         <v>749</v>
       </c>

--- a/docs/結合試験項目一覧.xlsx
+++ b/docs/結合試験項目一覧.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\neo-oi\neo_event_tool\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE4CB37-09A5-4F50-9551-D37C7659055E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A7808F-DD32-43F1-B962-60E500C988D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="759">
   <si>
     <t>●参加者ビュー</t>
   </si>
@@ -840,9 +840,6 @@
     <t>「〇〇さんを受付しました」と出て、一覧がチェックイン済みになる</t>
   </si>
   <si>
-    <t>QR確認できず</t>
-  </si>
-  <si>
     <t>受付済みのQR</t>
   </si>
   <si>
@@ -1275,9 +1272,6 @@
     <t>「コピーできませんでした」と出る（成功と偽らない）</t>
   </si>
   <si>
-    <t>拒否していてもコピーできてしまう</t>
-  </si>
-  <si>
     <t>共有</t>
   </si>
   <si>
@@ -1467,9 +1461,6 @@
     <t>「対応する申込が見つかりません」と出て通常画面へ。他人の情報は出ない</t>
   </si>
   <si>
-    <t>URLが変わらず確認不可のため自動に変更</t>
-  </si>
-  <si>
     <t>キャンセル済み</t>
   </si>
   <si>
@@ -1705,9 +1696,6 @@
   </si>
   <si>
     <t>受付できるのは未受付だけ。各パターンで正しいメッセージが出て、検索とQRの結果が同じ</t>
-  </si>
-  <si>
-    <t>QRの未確認不可</t>
   </si>
   <si>
     <t>URLから開く全パターン</t>
@@ -1868,9 +1856,6 @@
     <t>evidence/1-4-1_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/1-4-2_20260731_01〜04.png（4枚）</t>
-  </si>
-  <si>
     <t>evidence/1-4-4_20260731_01.png</t>
   </si>
   <si>
@@ -1886,27 +1871,18 @@
     <t>evidence/2-3-2_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/2-3-3_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
     <t>evidence/2-4-1_20260731_01.png</t>
   </si>
   <si>
     <t>evidence/2-4-2_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/2-4-3_20260731_01〜03.png（3枚）</t>
-  </si>
-  <si>
     <t>evidence/2-5-1_20260731_01.png</t>
   </si>
   <si>
     <t>evidence/3-1-1_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/3-1-2_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
     <t>evidence/3-2-1_20260731_01.png</t>
   </si>
   <si>
@@ -1922,15 +1898,9 @@
     <t>evidence/3-3-2_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/3-5-1_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
     <t>evidence/3-5-2_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/3-5-3_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
     <t>evidence/3-6-1_20260731_01.png／evidence/3-6-1_20260731_applications_ev_public.csv</t>
   </si>
   <si>
@@ -1943,36 +1913,12 @@
     <t>evidence/3-8-1_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/3-8-2_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
-    <t>evidence/3-8-3_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
     <t>evidence/3-9-1_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/3-9-2_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
-    <t>evidence/3-10-1_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
-    <t>evidence/3-10-2_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
-    <t>evidence/3-10-3_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
     <t>evidence/3-10-4_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/3-10-5_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
-    <t>evidence/3-11-1_20260731_01〜03.png（3枚）</t>
-  </si>
-  <si>
     <t>evidence/3-11-3_20260731_01.png</t>
   </si>
   <si>
@@ -1988,57 +1934,24 @@
     <t>evidence/3-12-1_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/3-12-5_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
-    <t>evidence/3-13-1_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
     <t>evidence/3-14-3_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/3-15-1_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
-    <t>evidence/3-15-2_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
-    <t>evidence/3-15-3_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
     <t>evidence/4-1-1_20260731_01.png</t>
   </si>
   <si>
     <t>evidence/4-1-3_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/4-2-2_20260731_01〜04.png（4枚）</t>
-  </si>
-  <si>
     <t>evidence/4-2-4_20260731_01.png</t>
   </si>
   <si>
     <t>evidence/4-3-3_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/4-3-4_20260731_01〜03.png（3枚）</t>
-  </si>
-  <si>
-    <t>evidence/4-3-5_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
     <t>evidence/4-3-6_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/4-3-8_20260731_01〜04.png（4枚）</t>
-  </si>
-  <si>
-    <t>evidence/4-3-9_20260731_01〜03.png（3枚）</t>
-  </si>
-  <si>
-    <t>evidence/4-4-1_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
     <t>evidence/4-5-1_20260731_01.png</t>
   </si>
   <si>
@@ -2048,9 +1961,6 @@
     <t>evidence/4-5-3_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/4-5-4_20260731_01〜04.png（4枚）</t>
-  </si>
-  <si>
     <t>evidence/4-5-5_20260731_01.png</t>
   </si>
   <si>
@@ -2060,9 +1970,6 @@
     <t>evidence/4-5-7_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/4-5-8_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
     <t>evidence/4-5-9_20260731_01.png</t>
   </si>
   <si>
@@ -2078,81 +1985,21 @@
     <t>evidence/5-1-4_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/5-1-5_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
     <t>evidence/5-1-6_20260731_01.png／evidence/5-1-6_20260731_participants.csv</t>
   </si>
   <si>
-    <t>evidence/5-1-7_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
-    <t>evidence/5-2-1_20260731_01〜03.png（3枚）</t>
-  </si>
-  <si>
-    <t>evidence/5-2-2_20260731_01〜03.png（3枚）</t>
-  </si>
-  <si>
     <t>evidence/6-1-1_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/6-1-4_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
     <t>evidence/6-1-7_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/6-2-1_20260731_01〜03.png（3枚）</t>
-  </si>
-  <si>
-    <t>evidence/6-2-2_20260731_01〜03.png（3枚）</t>
-  </si>
-  <si>
     <t>evidence/6-2-3_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/6-3-1_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
-    <t>evidence/6-3-2_20260731_01〜02.png（2枚）</t>
-  </si>
-  <si>
     <t>evidence/6-3-6_20260731_01.png</t>
   </si>
   <si>
-    <t>evidence/6-4-4_20260731_01〜03.png（3枚）</t>
-  </si>
-  <si>
-    <t>evidence/7-1-1_20260731_01〜07.png（7枚）／evidence/7-1-1_20260731_applications_4589816a43a82b65.csv</t>
-  </si>
-  <si>
-    <t>evidence/7-3-1_20260731_01〜07.png（7枚）</t>
-  </si>
-  <si>
-    <t>evidence/7-4-1_20260731_01〜04.png（4枚）</t>
-  </si>
-  <si>
-    <t>evidence/7-5-1_20260731_01〜06.png（6枚）</t>
-  </si>
-  <si>
-    <t>evidence/7-6-1_20260731_01〜06.png（6枚）</t>
-  </si>
-  <si>
-    <t>evidence/7-7-1_20260731_01〜06.png（6枚）</t>
-  </si>
-  <si>
-    <t>evidence/7-8-1_20260731_01〜05.png（5枚）</t>
-  </si>
-  <si>
-    <t>evidence/7-9-1_20260731_01〜06.png（6枚）／evidence/7-9-1_20260731_participants.csv</t>
-  </si>
-  <si>
-    <t>evidence/7-10-1_20260731_01〜08.png（8枚）</t>
-  </si>
-  <si>
-    <t>evidence/7-12-1_20260731_01〜05.png（5枚）</t>
-  </si>
-  <si>
     <t>evidence/1-4-2_20260731_*.png（4枚）</t>
   </si>
   <si>
@@ -2433,13 +2280,75 @@
   </si>
   <si>
     <t>evidence/7-11-1_20260731_*.png（6枚）</t>
+  </si>
+  <si>
+    <t>tore</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>列1</t>
+    <rPh sb="1" eb="2">
+      <t>ケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>１件１＋１になっていておかしい</t>
+    </r>
+    <rPh sb="1" eb="2">
+      <t>ケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>evidence/3-4-4_2026_07_31.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>evidence/3-4-3_2026_07_31.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>evidence/3-4-2_2026_07_31.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>evidence/3-4-1_2026_07_31.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>evidence/3-4-1_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-4-2_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-4-3_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-4-4_20260731_01.png</t>
+  </si>
+  <si>
+    <t>evidence/3-6-2_20260731_*.png（2枚）／evidence/3-6-2_20260731_applications_ev_public.csv</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2587,6 +2496,11 @@
       <color theme="1"/>
       <name val="Segoe UI Symbol"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="7">
@@ -2775,7 +2689,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2957,12 +2871,16 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2971,13 +2889,6 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2990,18 +2901,67 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="137">
+  <dxfs count="138">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color theme="1"/>
@@ -4871,6 +4831,673 @@
         <family val="2"/>
       </font>
       <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="47" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
         <patternFill>
           <fgColor indexed="64"/>
           <bgColor theme="0"/>
@@ -6737,673 +7364,6 @@
         </horizontal>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="47" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="left" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -7418,168 +7378,175 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="テーブル3" displayName="テーブル3" ref="B8:P18" totalsRowShown="0" headerRowDxfId="117" dataDxfId="115" headerRowBorderDxfId="116" tableBorderDxfId="114">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="テーブル3" displayName="テーブル3" ref="B8:P18" totalsRowShown="0" headerRowDxfId="137" dataDxfId="135" headerRowBorderDxfId="136" tableBorderDxfId="134">
   <autoFilter ref="B8:P18" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="No." dataDxfId="113"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="枝番" dataDxfId="112"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="明細" dataDxfId="111"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="大項目" dataDxfId="110"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="中項目" dataDxfId="109"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="小項目" dataDxfId="108"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="観点" dataDxfId="107"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="手順" dataDxfId="106"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="条件" dataDxfId="105"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="期待動作" dataDxfId="104"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="担当者" dataDxfId="103"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="日付" dataDxfId="102"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="結果" dataDxfId="101"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="履歴　" dataDxfId="100"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="備考" dataDxfId="99"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="No." dataDxfId="133"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="枝番" dataDxfId="132"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="明細" dataDxfId="131"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="大項目" dataDxfId="130"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="中項目" dataDxfId="129"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="小項目" dataDxfId="128"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="観点" dataDxfId="127"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="手順" dataDxfId="126"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="条件" dataDxfId="125"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="期待動作" dataDxfId="124"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="担当者" dataDxfId="123"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="日付" dataDxfId="122"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="結果" dataDxfId="121"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="履歴　" dataDxfId="120"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="備考" dataDxfId="119"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="テーブル1" displayName="テーブル1" ref="B8:P21" totalsRowShown="0" headerRowDxfId="98" dataDxfId="96" headerRowBorderDxfId="97" tableBorderDxfId="95" totalsRowBorderDxfId="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="テーブル1" displayName="テーブル1" ref="B8:P21" totalsRowShown="0" headerRowDxfId="118" dataDxfId="116" headerRowBorderDxfId="117" tableBorderDxfId="115" totalsRowBorderDxfId="114">
   <autoFilter ref="B8:P21" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="No." dataDxfId="93"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="枝番" dataDxfId="92"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="明細" dataDxfId="91"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="大項目" dataDxfId="90"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="中項目" dataDxfId="89"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="小項目" dataDxfId="88"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="観点" dataDxfId="87"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="手順" dataDxfId="86"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="条件" dataDxfId="85"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="期待動作" dataDxfId="84"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="担当者" dataDxfId="83"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="日付" dataDxfId="82"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="結果" dataDxfId="81"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="履歴" dataDxfId="80"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="備考" dataDxfId="79"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="No." dataDxfId="113"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="枝番" dataDxfId="112"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="明細" dataDxfId="111"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="大項目" dataDxfId="110"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="中項目" dataDxfId="109"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="小項目" dataDxfId="108"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="観点" dataDxfId="107"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="手順" dataDxfId="106"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="条件" dataDxfId="105"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="期待動作" dataDxfId="104"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="担当者" dataDxfId="103"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="日付" dataDxfId="102"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="結果" dataDxfId="101"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="履歴" dataDxfId="100"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="備考" dataDxfId="99"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="テーブル2" displayName="テーブル2" ref="B8:P61" totalsRowShown="0" headerRowDxfId="78" dataDxfId="76" headerRowBorderDxfId="77" tableBorderDxfId="75" totalsRowBorderDxfId="74">
-  <autoFilter ref="B8:P61" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
-  <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="No." dataDxfId="73"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="枝番" dataDxfId="72"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="明細" dataDxfId="71"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="大項目" dataDxfId="70"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="中項目" dataDxfId="69"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="小項目" dataDxfId="68"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="観点" dataDxfId="67"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="手順" dataDxfId="66"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="条件" dataDxfId="65"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="期待動作" dataDxfId="64"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="担当者" dataDxfId="63"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="日付" dataDxfId="62"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="結果" dataDxfId="61"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="履歴" dataDxfId="60"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="備考" dataDxfId="59"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="テーブル2" displayName="テーブル2" ref="B8:Q61" totalsRowShown="0" headerRowDxfId="98" dataDxfId="96" headerRowBorderDxfId="97" tableBorderDxfId="95" totalsRowBorderDxfId="94">
+  <autoFilter ref="B8:Q61" xr:uid="{00000000-0009-0000-0100-000003000000}">
+    <filterColumn colId="13">
+      <filters>
+        <filter val="QR確認できず"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="No." dataDxfId="93"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="枝番" dataDxfId="92"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="明細" dataDxfId="91"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="大項目" dataDxfId="90"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="中項目" dataDxfId="89"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="小項目" dataDxfId="88"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="観点" dataDxfId="87"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="手順" dataDxfId="86"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="条件" dataDxfId="85"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="期待動作" dataDxfId="84"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="担当者" dataDxfId="83"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="日付" dataDxfId="82"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="結果" dataDxfId="81"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="履歴" dataDxfId="80"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="備考" dataDxfId="79"/>
+    <tableColumn id="11" xr3:uid="{BDE2CAFA-CDEE-4A16-8EBC-BE4AB88CE6E5}" name="列1" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="テーブル4" displayName="テーブル4" ref="B8:P36" totalsRowShown="0" headerRowDxfId="136" headerRowBorderDxfId="135" tableBorderDxfId="134" totalsRowBorderDxfId="133">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="テーブル4" displayName="テーブル4" ref="B8:P36" totalsRowShown="0" headerRowDxfId="78" headerRowBorderDxfId="77" tableBorderDxfId="76" totalsRowBorderDxfId="75">
   <autoFilter ref="B8:P36" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="No." dataDxfId="132"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="枝番" dataDxfId="131"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="明細" dataDxfId="130"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="大項目" dataDxfId="129"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="中項目" dataDxfId="128"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="小項目" dataDxfId="127"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="観点" dataDxfId="126"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="手順" dataDxfId="125"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="条件" dataDxfId="124"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="期待動作" dataDxfId="123"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="担当者" dataDxfId="122"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="日付" dataDxfId="121"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="結果" dataDxfId="120"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="履歴" dataDxfId="119"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="備考" dataDxfId="118"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="No." dataDxfId="74"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="枝番" dataDxfId="73"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="明細" dataDxfId="72"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="大項目" dataDxfId="71"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="中項目" dataDxfId="70"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="小項目" dataDxfId="69"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="観点" dataDxfId="68"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="手順" dataDxfId="67"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="条件" dataDxfId="66"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="期待動作" dataDxfId="65"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="担当者" dataDxfId="64"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="日付" dataDxfId="63"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="結果" dataDxfId="62"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="履歴" dataDxfId="61"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="備考" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="テーブル6" displayName="テーブル6" ref="B8:P18" totalsRowShown="0" headerRowDxfId="58" headerRowBorderDxfId="57" tableBorderDxfId="56" totalsRowBorderDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="テーブル6" displayName="テーブル6" ref="B8:P18" totalsRowShown="0" headerRowDxfId="59" headerRowBorderDxfId="58" tableBorderDxfId="57" totalsRowBorderDxfId="56">
   <autoFilter ref="B8:P18" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="No." dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="枝番" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="明細" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="大項目" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="中項目" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="小項目" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="観点" dataDxfId="48"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="手順" dataDxfId="47"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="条件" dataDxfId="46"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="期待動作" dataDxfId="45"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="担当者" dataDxfId="44"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="日付" dataDxfId="43"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" name="結果" dataDxfId="42"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0400-00000E000000}" name="履歴" dataDxfId="41"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0400-00000F000000}" name="備考" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="No." dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="枝番" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="明細" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="大項目" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="中項目" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="小項目" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="観点" dataDxfId="49"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="手順" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="条件" dataDxfId="47"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="期待動作" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="担当者" dataDxfId="45"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="日付" dataDxfId="44"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" name="結果" dataDxfId="43"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0400-00000E000000}" name="履歴" dataDxfId="42"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0400-00000F000000}" name="備考" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="テーブル5" displayName="テーブル5" ref="B8:P31" totalsRowShown="0" headerRowDxfId="39" headerRowBorderDxfId="38" tableBorderDxfId="37" totalsRowBorderDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="テーブル5" displayName="テーブル5" ref="B8:P31" totalsRowShown="0" headerRowDxfId="40" headerRowBorderDxfId="39" tableBorderDxfId="38" totalsRowBorderDxfId="37">
   <autoFilter ref="B8:P31" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="No." dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="枝番" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="明細" dataDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="大項目" dataDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="中項目" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="小項目" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="観点" dataDxfId="29"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="手順" dataDxfId="28"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="条件" dataDxfId="27"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="期待動作" dataDxfId="26"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="担当者" dataDxfId="25"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="日付" dataDxfId="24"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="結果" dataDxfId="23"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0500-00000E000000}" name="履歴" dataDxfId="22"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0500-00000F000000}" name="備考" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="No." dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="枝番" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="明細" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="大項目" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="中項目" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="小項目" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="観点" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="手順" dataDxfId="29"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="条件" dataDxfId="28"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="期待動作" dataDxfId="27"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="担当者" dataDxfId="26"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="日付" dataDxfId="25"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="結果" dataDxfId="24"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0500-00000E000000}" name="履歴" dataDxfId="23"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0500-00000F000000}" name="備考" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="テーブル7" displayName="テーブル7" ref="B8:P20" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="19" tableBorderDxfId="18" totalsRowBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="テーブル7" displayName="テーブル7" ref="B8:P20" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
   <autoFilter ref="B8:P20" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="No." dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="枝番" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="明細" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="大項目" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="中項目" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="小項目" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="観点" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="手順" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="条件" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="期待動作" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" name="担当者" dataDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" name="日付" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" name="結果" dataDxfId="4"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" name="履歴" dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" name="備考" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="No." dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="枝番" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="明細" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="大項目" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="中項目" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="小項目" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="観点" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="手順" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="条件" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="期待動作" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" name="担当者" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" name="日付" dataDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" name="結果" dataDxfId="5"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" name="履歴" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" name="tore" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7965,8 +7932,8 @@
     <col min="11" max="11" width="75.9140625" style="4" customWidth="1"/>
     <col min="12" max="12" width="11.75" style="4" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="8.58203125" style="4" customWidth="1"/>
-    <col min="15" max="15" width="9.25" style="4" customWidth="1"/>
-    <col min="16" max="16" width="30.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="37.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.58203125" style="4" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="8.58203125" style="4" customWidth="1"/>
     <col min="19" max="16384" width="8.58203125" style="4"/>
   </cols>
@@ -7980,68 +7947,68 @@
       <c r="B3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="69" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63"/>
     </row>
     <row r="5" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="65"/>
-      <c r="L7" s="63" t="s">
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="65"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="66"/>
+      <c r="O7" s="66"/>
+      <c r="P7" s="67"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
@@ -8125,7 +8092,7 @@
       <c r="M9" s="37"/>
       <c r="N9" s="36"/>
       <c r="O9" s="20" t="s">
-        <v>750</v>
+        <v>699</v>
       </c>
       <c r="P9" s="19" t="s">
         <v>37</v>
@@ -8168,7 +8135,7 @@
       <c r="M10" s="37"/>
       <c r="N10" s="36"/>
       <c r="O10" s="20" t="s">
-        <v>751</v>
+        <v>700</v>
       </c>
       <c r="P10" s="19" t="s">
         <v>37</v>
@@ -8211,7 +8178,7 @@
       <c r="M11" s="37"/>
       <c r="N11" s="36"/>
       <c r="O11" s="20" t="s">
-        <v>752</v>
+        <v>701</v>
       </c>
       <c r="P11" s="19" t="s">
         <v>37</v>
@@ -8252,7 +8219,7 @@
       <c r="M12" s="37"/>
       <c r="N12" s="36"/>
       <c r="O12" s="20" t="s">
-        <v>753</v>
+        <v>702</v>
       </c>
       <c r="P12" s="19" t="s">
         <v>37</v>
@@ -8293,10 +8260,10 @@
       <c r="M13" s="37"/>
       <c r="N13" s="36"/>
       <c r="O13" s="20" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="P13" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8334,7 +8301,7 @@
       <c r="M14" s="37"/>
       <c r="N14" s="36"/>
       <c r="O14" s="20" t="s">
-        <v>754</v>
+        <v>703</v>
       </c>
       <c r="P14" s="19" t="s">
         <v>32</v>
@@ -8375,10 +8342,10 @@
       <c r="M15" s="37"/>
       <c r="N15" s="36"/>
       <c r="O15" s="20" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="P15" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8416,10 +8383,10 @@
       <c r="M16" s="37"/>
       <c r="N16" s="36"/>
       <c r="O16" s="20" t="s">
-        <v>703</v>
+        <v>652</v>
       </c>
       <c r="P16" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8457,7 +8424,7 @@
       <c r="M17" s="37"/>
       <c r="N17" s="36"/>
       <c r="O17" s="20" t="s">
-        <v>755</v>
+        <v>704</v>
       </c>
       <c r="P17" s="19" t="s">
         <v>37</v>
@@ -8498,10 +8465,10 @@
       <c r="M18" s="37"/>
       <c r="N18" s="36"/>
       <c r="O18" s="20" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="P18" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
   </sheetData>
@@ -8514,12 +8481,12 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="B8:K8">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="2">
+    <cfRule type="notContainsBlanks" dxfId="2" priority="2">
       <formula>LEN(TRIM(B8))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L8:P8">
-    <cfRule type="notContainsBlanks" dxfId="0" priority="1">
+    <cfRule type="notContainsBlanks" dxfId="1" priority="1">
       <formula>LEN(TRIM(L8))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8549,8 +8516,9 @@
     <col min="11" max="11" width="78.25" style="4" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10" style="4" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="8.6640625" style="4" customWidth="1"/>
-    <col min="16" max="16" width="7.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.6640625" style="4" customWidth="1"/>
+    <col min="15" max="15" width="37.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.58203125" style="4" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="8.6640625" style="4" customWidth="1"/>
     <col min="19" max="16384" width="8.6640625" style="4"/>
   </cols>
@@ -8564,68 +8532,68 @@
       <c r="B3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="69" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63"/>
     </row>
     <row r="5" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="72"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="65"/>
-      <c r="L7" s="63" t="s">
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="65"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="66"/>
+      <c r="O7" s="66"/>
+      <c r="P7" s="67"/>
     </row>
     <row r="8" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="27" t="s">
@@ -8709,10 +8677,10 @@
       <c r="M9" s="37"/>
       <c r="N9" s="36"/>
       <c r="O9" s="20" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="P9" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8752,10 +8720,10 @@
       <c r="M10" s="37"/>
       <c r="N10" s="36"/>
       <c r="O10" s="20" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="P10" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8793,7 +8761,7 @@
       <c r="M11" s="37"/>
       <c r="N11" s="39"/>
       <c r="O11" s="20" t="s">
-        <v>756</v>
+        <v>705</v>
       </c>
       <c r="P11" s="19" t="s">
         <v>37</v>
@@ -8834,7 +8802,7 @@
       <c r="M12" s="37"/>
       <c r="N12" s="39"/>
       <c r="O12" s="20" t="s">
-        <v>757</v>
+        <v>706</v>
       </c>
       <c r="P12" s="19" t="s">
         <v>37</v>
@@ -8875,10 +8843,10 @@
       <c r="M13" s="37"/>
       <c r="N13" s="36"/>
       <c r="O13" s="20" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="P13" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8916,10 +8884,10 @@
       <c r="M14" s="37"/>
       <c r="N14" s="36"/>
       <c r="O14" s="20" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="P14" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8959,10 +8927,10 @@
       <c r="M15" s="37"/>
       <c r="N15" s="36"/>
       <c r="O15" s="20" t="s">
-        <v>704</v>
+        <v>653</v>
       </c>
       <c r="P15" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9000,10 +8968,10 @@
       <c r="M16" s="37"/>
       <c r="N16" s="36"/>
       <c r="O16" s="20" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="P16" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9041,10 +9009,10 @@
       <c r="M17" s="37"/>
       <c r="N17" s="36"/>
       <c r="O17" s="20" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="P17" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9082,10 +9050,10 @@
       <c r="M18" s="37"/>
       <c r="N18" s="36"/>
       <c r="O18" s="20" t="s">
-        <v>705</v>
+        <v>654</v>
       </c>
       <c r="P18" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="19" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9123,10 +9091,10 @@
       <c r="M19" s="37"/>
       <c r="N19" s="36"/>
       <c r="O19" s="20" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="P19" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="20" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9166,7 +9134,7 @@
       <c r="M20" s="37"/>
       <c r="N20" s="39"/>
       <c r="O20" s="20" t="s">
-        <v>758</v>
+        <v>707</v>
       </c>
       <c r="P20" s="19" t="s">
         <v>37</v>
@@ -9209,7 +9177,7 @@
       <c r="M21" s="37"/>
       <c r="N21" s="39"/>
       <c r="O21" s="20" t="s">
-        <v>759</v>
+        <v>708</v>
       </c>
       <c r="P21" s="19" t="s">
         <v>37</v>
@@ -9236,7 +9204,7 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:P61"/>
+  <dimension ref="A1:Q61"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="8.6640625" style="4" customWidth="1"/>
@@ -9250,29 +9218,29 @@
     <col min="12" max="12" width="10" style="4" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8.6640625" style="4" customWidth="1"/>
-    <col min="15" max="15" width="29.58203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="81.58203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.58203125" style="4" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="8.6640625" style="4" customWidth="1"/>
     <col min="19" max="16384" width="8.6640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="69" t="s">
         <v>225</v>
       </c>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-    </row>
-    <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+    </row>
+    <row r="4" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
         <v>3</v>
       </c>
@@ -9280,44 +9248,44 @@
         <v>226</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="73" t="s">
+      <c r="C5" s="72" t="s">
         <v>227</v>
       </c>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
-    </row>
-    <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="66" t="s">
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+    </row>
+    <row r="7" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="65"/>
-      <c r="L7" s="63" t="s">
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="65"/>
-    </row>
-    <row r="8" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M7" s="66"/>
+      <c r="N7" s="66"/>
+      <c r="O7" s="66"/>
+      <c r="P7" s="67"/>
+    </row>
+    <row r="8" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="10" t="s">
         <v>9</v>
       </c>
@@ -9363,8 +9331,11 @@
       <c r="P8" s="13" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q8" s="12" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="14">
         <v>3</v>
       </c>
@@ -9399,13 +9370,14 @@
       <c r="M9" s="37"/>
       <c r="N9" s="36"/>
       <c r="O9" s="20" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="P9" s="40" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q9" s="77"/>
+    </row>
+    <row r="10" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="14">
         <v>3</v>
       </c>
@@ -9440,13 +9412,14 @@
       <c r="M10" s="37"/>
       <c r="N10" s="36"/>
       <c r="O10" s="20" t="s">
-        <v>706</v>
+        <v>655</v>
       </c>
       <c r="P10" s="40" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q10" s="43"/>
+    </row>
+    <row r="11" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="14">
         <v>3</v>
       </c>
@@ -9481,13 +9454,14 @@
       <c r="M11" s="37"/>
       <c r="N11" s="36"/>
       <c r="O11" s="20" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="P11" s="40" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q11" s="43"/>
+    </row>
+    <row r="12" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="14">
         <v>3</v>
       </c>
@@ -9522,13 +9496,14 @@
       <c r="M12" s="37"/>
       <c r="N12" s="36"/>
       <c r="O12" s="20" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="P12" s="40" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q12" s="43"/>
+    </row>
+    <row r="13" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="14">
         <v>3</v>
       </c>
@@ -9565,13 +9540,14 @@
       <c r="M13" s="37"/>
       <c r="N13" s="36"/>
       <c r="O13" s="20" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="P13" s="40" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q13" s="43"/>
+    </row>
+    <row r="14" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="14">
         <v>3</v>
       </c>
@@ -9606,13 +9582,14 @@
       <c r="M14" s="37"/>
       <c r="N14" s="36"/>
       <c r="O14" s="20" t="s">
-        <v>760</v>
+        <v>709</v>
       </c>
       <c r="P14" s="19" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q14" s="43"/>
+    </row>
+    <row r="15" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="14">
         <v>3</v>
       </c>
@@ -9647,13 +9624,14 @@
       <c r="M15" s="37"/>
       <c r="N15" s="36"/>
       <c r="O15" s="20" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="P15" s="40" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q15" s="43"/>
+    </row>
+    <row r="16" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="14">
         <v>3</v>
       </c>
@@ -9690,13 +9668,14 @@
       <c r="M16" s="37"/>
       <c r="N16" s="36"/>
       <c r="O16" s="20" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="P16" s="40" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="17" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q16" s="43"/>
+    </row>
+    <row r="17" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="14">
         <v>3</v>
       </c>
@@ -9731,13 +9710,14 @@
       <c r="M17" s="37"/>
       <c r="N17" s="36"/>
       <c r="O17" s="20" t="s">
-        <v>761</v>
+        <v>710</v>
       </c>
       <c r="P17" s="19" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="18" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q17" s="43"/>
+    </row>
+    <row r="18" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="14">
         <v>3</v>
       </c>
@@ -9771,16 +9751,21 @@
       <c r="L18" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M18" s="37"/>
-      <c r="N18" s="36"/>
+      <c r="M18" s="37">
+        <v>46233</v>
+      </c>
+      <c r="N18" s="39" t="s">
+        <v>31</v>
+      </c>
       <c r="O18" s="43" t="s">
-        <v>266</v>
+        <v>754</v>
       </c>
       <c r="P18" s="19" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="19" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q18" s="43"/>
+    </row>
+    <row r="19" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="14">
         <v>3</v>
       </c>
@@ -9797,31 +9782,36 @@
         <v>261</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H19" s="20" t="s">
         <v>26</v>
       </c>
       <c r="I19" s="19" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J19" s="19"/>
       <c r="K19" s="19" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L19" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M19" s="37"/>
-      <c r="N19" s="36"/>
+      <c r="M19" s="37">
+        <v>46233</v>
+      </c>
+      <c r="N19" s="39" t="s">
+        <v>31</v>
+      </c>
       <c r="O19" s="43" t="s">
-        <v>266</v>
+        <v>755</v>
       </c>
       <c r="P19" s="19" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="20" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q19" s="43"/>
+    </row>
+    <row r="20" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="14">
         <v>3</v>
       </c>
@@ -9838,31 +9828,36 @@
         <v>261</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H20" s="20" t="s">
         <v>26</v>
       </c>
       <c r="I20" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J20" s="19"/>
       <c r="K20" s="19" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L20" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M20" s="37"/>
-      <c r="N20" s="36"/>
+      <c r="M20" s="37">
+        <v>46233</v>
+      </c>
+      <c r="N20" s="39" t="s">
+        <v>31</v>
+      </c>
       <c r="O20" s="43" t="s">
-        <v>266</v>
+        <v>756</v>
       </c>
       <c r="P20" s="19" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="21" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q20" s="43"/>
+    </row>
+    <row r="21" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="14">
         <v>3</v>
       </c>
@@ -9879,31 +9874,36 @@
         <v>261</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H21" s="20" t="s">
         <v>26</v>
       </c>
       <c r="I21" s="19" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J21" s="19"/>
       <c r="K21" s="19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L21" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M21" s="37"/>
-      <c r="N21" s="36"/>
+      <c r="M21" s="37">
+        <v>46233</v>
+      </c>
+      <c r="N21" s="39" t="s">
+        <v>31</v>
+      </c>
       <c r="O21" s="43" t="s">
-        <v>266</v>
+        <v>757</v>
       </c>
       <c r="P21" s="19" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="22" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q21" s="43"/>
+    </row>
+    <row r="22" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="14">
         <v>3</v>
       </c>
@@ -9920,19 +9920,19 @@
         <v>261</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H22" s="20" t="s">
         <v>86</v>
       </c>
       <c r="I22" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="J22" s="19" t="s">
         <v>277</v>
       </c>
-      <c r="J22" s="19" t="s">
+      <c r="K22" s="19" t="s">
         <v>278</v>
-      </c>
-      <c r="K22" s="19" t="s">
-        <v>279</v>
       </c>
       <c r="L22" s="35" t="s">
         <v>36</v>
@@ -9940,13 +9940,14 @@
       <c r="M22" s="37"/>
       <c r="N22" s="36"/>
       <c r="O22" s="20" t="s">
-        <v>762</v>
+        <v>711</v>
       </c>
       <c r="P22" s="19" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="23" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q22" s="43"/>
+    </row>
+    <row r="23" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="14">
         <v>3</v>
       </c>
@@ -9963,19 +9964,19 @@
         <v>261</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H23" s="20" t="s">
         <v>86</v>
       </c>
       <c r="I23" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="J23" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="K23" s="19" t="s">
         <v>281</v>
-      </c>
-      <c r="J23" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="K23" s="19" t="s">
-        <v>282</v>
       </c>
       <c r="L23" s="35" t="s">
         <v>36</v>
@@ -9983,13 +9984,14 @@
       <c r="M23" s="37"/>
       <c r="N23" s="36"/>
       <c r="O23" s="20" t="s">
-        <v>763</v>
+        <v>712</v>
       </c>
       <c r="P23" s="19" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="24" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q23" s="43"/>
+    </row>
+    <row r="24" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="14">
         <v>3</v>
       </c>
@@ -10006,19 +10008,19 @@
         <v>261</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H24" s="20" t="s">
         <v>86</v>
       </c>
       <c r="I24" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="J24" s="19" t="s">
         <v>284</v>
       </c>
-      <c r="J24" s="19" t="s">
+      <c r="K24" s="19" t="s">
         <v>285</v>
-      </c>
-      <c r="K24" s="19" t="s">
-        <v>286</v>
       </c>
       <c r="L24" s="35" t="s">
         <v>36</v>
@@ -10026,13 +10028,14 @@
       <c r="M24" s="37"/>
       <c r="N24" s="36"/>
       <c r="O24" s="43" t="s">
-        <v>764</v>
+        <v>713</v>
       </c>
       <c r="P24" s="19" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="25" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q24" s="43"/>
+    </row>
+    <row r="25" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="14">
         <v>3</v>
       </c>
@@ -10046,20 +10049,20 @@
         <v>235</v>
       </c>
       <c r="F25" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="G25" s="19" t="s">
         <v>287</v>
-      </c>
-      <c r="G25" s="19" t="s">
-        <v>288</v>
       </c>
       <c r="H25" s="20" t="s">
         <v>56</v>
       </c>
       <c r="I25" s="19" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J25" s="19"/>
       <c r="K25" s="19" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L25" s="43" t="s">
         <v>36</v>
@@ -10067,13 +10070,14 @@
       <c r="M25" s="37"/>
       <c r="N25" s="36"/>
       <c r="O25" s="20" t="s">
-        <v>707</v>
+        <v>656</v>
       </c>
       <c r="P25" s="40" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="26" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q25" s="43"/>
+    </row>
+    <row r="26" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="14">
         <v>3</v>
       </c>
@@ -10087,22 +10091,22 @@
         <v>235</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H26" s="20" t="s">
         <v>86</v>
       </c>
       <c r="I26" s="19" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>83</v>
       </c>
       <c r="K26" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L26" s="43" t="s">
         <v>36</v>
@@ -10110,13 +10114,14 @@
       <c r="M26" s="37"/>
       <c r="N26" s="36"/>
       <c r="O26" s="20" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="P26" s="40" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="27" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q26" s="43"/>
+    </row>
+    <row r="27" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="14">
         <v>3</v>
       </c>
@@ -10133,7 +10138,7 @@
         <v>130</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H27" s="20" t="s">
         <v>56</v>
@@ -10143,7 +10148,7 @@
       </c>
       <c r="J27" s="19"/>
       <c r="K27" s="19" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L27" s="43" t="s">
         <v>36</v>
@@ -10151,13 +10156,14 @@
       <c r="M27" s="37"/>
       <c r="N27" s="36"/>
       <c r="O27" s="20" t="s">
-        <v>708</v>
+        <v>657</v>
       </c>
       <c r="P27" s="40" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="28" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q27" s="43"/>
+    </row>
+    <row r="28" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="14">
         <v>3</v>
       </c>
@@ -10171,20 +10177,20 @@
         <v>235</v>
       </c>
       <c r="F28" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="G28" s="19" t="s">
         <v>296</v>
-      </c>
-      <c r="G28" s="19" t="s">
-        <v>297</v>
       </c>
       <c r="H28" s="20" t="s">
         <v>56</v>
       </c>
       <c r="I28" s="19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J28" s="19"/>
       <c r="K28" s="19" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L28" s="43" t="s">
         <v>36</v>
@@ -10192,13 +10198,14 @@
       <c r="M28" s="37"/>
       <c r="N28" s="36"/>
       <c r="O28" s="20" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="P28" s="40" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="29" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q28" s="43"/>
+    </row>
+    <row r="29" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="14">
         <v>3</v>
       </c>
@@ -10212,22 +10219,22 @@
         <v>235</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H29" s="20" t="s">
         <v>86</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J29" s="19" t="s">
         <v>83</v>
       </c>
       <c r="K29" s="19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L29" s="43" t="s">
         <v>36</v>
@@ -10235,13 +10242,16 @@
       <c r="M29" s="37"/>
       <c r="N29" s="36"/>
       <c r="O29" s="20" t="s">
-        <v>630</v>
+        <v>758</v>
       </c>
       <c r="P29" s="40" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="30" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q29" s="43" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="14">
         <v>3</v>
       </c>
@@ -10255,20 +10265,20 @@
         <v>235</v>
       </c>
       <c r="F30" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="G30" s="19" t="s">
         <v>303</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>304</v>
       </c>
       <c r="H30" s="20" t="s">
         <v>26</v>
       </c>
       <c r="I30" s="19" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J30" s="19"/>
       <c r="K30" s="19" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L30" s="43" t="s">
         <v>36</v>
@@ -10276,13 +10286,14 @@
       <c r="M30" s="37"/>
       <c r="N30" s="36"/>
       <c r="O30" s="20" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="P30" s="40" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="31" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q30" s="43"/>
+    </row>
+    <row r="31" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="14">
         <v>3</v>
       </c>
@@ -10293,23 +10304,23 @@
         <v>1</v>
       </c>
       <c r="E31" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="F31" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="F31" s="19" t="s">
+      <c r="G31" s="19" t="s">
         <v>308</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>309</v>
       </c>
       <c r="H31" s="20" t="s">
         <v>56</v>
       </c>
       <c r="I31" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J31" s="19"/>
       <c r="K31" s="19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L31" s="43" t="s">
         <v>36</v>
@@ -10317,13 +10328,14 @@
       <c r="M31" s="37"/>
       <c r="N31" s="36"/>
       <c r="O31" s="20" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="P31" s="40" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="32" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q31" s="43"/>
+    </row>
+    <row r="32" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="14">
         <v>3</v>
       </c>
@@ -10334,23 +10346,23 @@
         <v>2</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F32" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="G32" s="19" t="s">
         <v>312</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>313</v>
       </c>
       <c r="H32" s="20" t="s">
         <v>26</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J32" s="19"/>
       <c r="K32" s="19" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L32" s="43" t="s">
         <v>36</v>
@@ -10358,13 +10370,14 @@
       <c r="M32" s="37"/>
       <c r="N32" s="36"/>
       <c r="O32" s="20" t="s">
-        <v>709</v>
+        <v>658</v>
       </c>
       <c r="P32" s="40" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q32" s="43"/>
+    </row>
+    <row r="33" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="14">
         <v>3</v>
       </c>
@@ -10375,23 +10388,23 @@
         <v>3</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G33" s="19" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H33" s="20" t="s">
         <v>56</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J33" s="19"/>
       <c r="K33" s="19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L33" s="43" t="s">
         <v>36</v>
@@ -10399,13 +10412,14 @@
       <c r="M33" s="37"/>
       <c r="N33" s="36"/>
       <c r="O33" s="20" t="s">
-        <v>710</v>
+        <v>659</v>
       </c>
       <c r="P33" s="40" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q33" s="43"/>
+    </row>
+    <row r="34" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="14">
         <v>3</v>
       </c>
@@ -10416,23 +10430,23 @@
         <v>1</v>
       </c>
       <c r="E34" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="F34" s="19" t="s">
         <v>319</v>
       </c>
-      <c r="F34" s="19" t="s">
+      <c r="G34" s="19" t="s">
         <v>320</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>321</v>
       </c>
       <c r="H34" s="20" t="s">
         <v>56</v>
       </c>
       <c r="I34" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J34" s="19"/>
       <c r="K34" s="19" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L34" s="43" t="s">
         <v>36</v>
@@ -10440,13 +10454,14 @@
       <c r="M34" s="37"/>
       <c r="N34" s="36"/>
       <c r="O34" s="20" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="P34" s="40" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q34" s="43"/>
+    </row>
+    <row r="35" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="41">
         <v>3</v>
       </c>
@@ -10457,23 +10472,23 @@
         <v>2</v>
       </c>
       <c r="E35" s="42" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F35" s="42" t="s">
+        <v>323</v>
+      </c>
+      <c r="G35" s="42" t="s">
         <v>324</v>
-      </c>
-      <c r="G35" s="42" t="s">
-        <v>325</v>
       </c>
       <c r="H35" s="43" t="s">
         <v>56</v>
       </c>
       <c r="I35" s="42" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J35" s="42"/>
       <c r="K35" s="42" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L35" s="43" t="s">
         <v>36</v>
@@ -10481,13 +10496,14 @@
       <c r="M35" s="37"/>
       <c r="N35" s="36"/>
       <c r="O35" s="43" t="s">
-        <v>711</v>
+        <v>660</v>
       </c>
       <c r="P35" s="42" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q35" s="43"/>
+    </row>
+    <row r="36" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="41">
         <v>3</v>
       </c>
@@ -10498,23 +10514,23 @@
         <v>1</v>
       </c>
       <c r="E36" s="42" t="s">
+        <v>327</v>
+      </c>
+      <c r="F36" s="42" t="s">
         <v>328</v>
       </c>
-      <c r="F36" s="42" t="s">
+      <c r="G36" s="42" t="s">
         <v>329</v>
-      </c>
-      <c r="G36" s="42" t="s">
-        <v>330</v>
       </c>
       <c r="H36" s="43" t="s">
         <v>56</v>
       </c>
       <c r="I36" s="42" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J36" s="42"/>
       <c r="K36" s="42" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L36" s="43" t="s">
         <v>36</v>
@@ -10522,13 +10538,14 @@
       <c r="M36" s="37"/>
       <c r="N36" s="36"/>
       <c r="O36" s="43" t="s">
-        <v>712</v>
+        <v>661</v>
       </c>
       <c r="P36" s="42" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q36" s="43"/>
+    </row>
+    <row r="37" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="41">
         <v>3</v>
       </c>
@@ -10539,23 +10556,23 @@
         <v>2</v>
       </c>
       <c r="E37" s="42" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F37" s="42" t="s">
+        <v>332</v>
+      </c>
+      <c r="G37" s="42" t="s">
         <v>333</v>
-      </c>
-      <c r="G37" s="42" t="s">
-        <v>334</v>
       </c>
       <c r="H37" s="43" t="s">
         <v>56</v>
       </c>
       <c r="I37" s="42" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J37" s="42"/>
       <c r="K37" s="42" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="L37" s="43" t="s">
         <v>36</v>
@@ -10563,13 +10580,14 @@
       <c r="M37" s="37"/>
       <c r="N37" s="36"/>
       <c r="O37" s="43" t="s">
-        <v>713</v>
+        <v>662</v>
       </c>
       <c r="P37" s="42" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q37" s="43"/>
+    </row>
+    <row r="38" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="41">
         <v>3</v>
       </c>
@@ -10580,23 +10598,23 @@
         <v>3</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F38" s="42" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G38" s="42" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H38" s="43" t="s">
         <v>26</v>
       </c>
       <c r="I38" s="42" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J38" s="42"/>
       <c r="K38" s="42" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="L38" s="43" t="s">
         <v>36</v>
@@ -10604,13 +10622,14 @@
       <c r="M38" s="37"/>
       <c r="N38" s="36"/>
       <c r="O38" s="43" t="s">
-        <v>714</v>
+        <v>663</v>
       </c>
       <c r="P38" s="42" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q38" s="43"/>
+    </row>
+    <row r="39" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="41">
         <v>3</v>
       </c>
@@ -10621,23 +10640,23 @@
         <v>4</v>
       </c>
       <c r="E39" s="42" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F39" s="42" t="s">
+        <v>339</v>
+      </c>
+      <c r="G39" s="42" t="s">
         <v>340</v>
-      </c>
-      <c r="G39" s="42" t="s">
-        <v>341</v>
       </c>
       <c r="H39" s="43" t="s">
         <v>26</v>
       </c>
       <c r="I39" s="42" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J39" s="42"/>
       <c r="K39" s="42" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L39" s="43" t="s">
         <v>36</v>
@@ -10645,13 +10664,14 @@
       <c r="M39" s="37"/>
       <c r="N39" s="36"/>
       <c r="O39" s="43" t="s">
-        <v>640</v>
+        <v>624</v>
       </c>
       <c r="P39" s="42" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q39" s="43"/>
+    </row>
+    <row r="40" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="41">
         <v>3</v>
       </c>
@@ -10662,25 +10682,25 @@
         <v>5</v>
       </c>
       <c r="E40" s="42" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F40" s="42" t="s">
+        <v>343</v>
+      </c>
+      <c r="G40" s="42" t="s">
         <v>344</v>
-      </c>
-      <c r="G40" s="42" t="s">
-        <v>345</v>
       </c>
       <c r="H40" s="43" t="s">
         <v>26</v>
       </c>
       <c r="I40" s="42" t="s">
+        <v>345</v>
+      </c>
+      <c r="J40" s="42" t="s">
         <v>346</v>
       </c>
-      <c r="J40" s="42" t="s">
+      <c r="K40" s="42" t="s">
         <v>347</v>
-      </c>
-      <c r="K40" s="42" t="s">
-        <v>348</v>
       </c>
       <c r="L40" s="43" t="s">
         <v>36</v>
@@ -10688,13 +10708,14 @@
       <c r="M40" s="37"/>
       <c r="N40" s="36"/>
       <c r="O40" s="43" t="s">
-        <v>715</v>
+        <v>664</v>
       </c>
       <c r="P40" s="42" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q40" s="43"/>
+    </row>
+    <row r="41" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="41">
         <v>3</v>
       </c>
@@ -10705,23 +10726,23 @@
         <v>1</v>
       </c>
       <c r="E41" s="42" t="s">
+        <v>348</v>
+      </c>
+      <c r="F41" s="42" t="s">
         <v>349</v>
       </c>
-      <c r="F41" s="42" t="s">
+      <c r="G41" s="42" t="s">
         <v>350</v>
-      </c>
-      <c r="G41" s="42" t="s">
-        <v>351</v>
       </c>
       <c r="H41" s="43" t="s">
         <v>26</v>
       </c>
       <c r="I41" s="42" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J41" s="42"/>
       <c r="K41" s="42" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L41" s="43" t="s">
         <v>36</v>
@@ -10729,13 +10750,14 @@
       <c r="M41" s="37"/>
       <c r="N41" s="36"/>
       <c r="O41" s="43" t="s">
-        <v>716</v>
+        <v>665</v>
       </c>
       <c r="P41" s="42" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q41" s="43"/>
+    </row>
+    <row r="42" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="41">
         <v>3</v>
       </c>
@@ -10746,23 +10768,23 @@
         <v>2</v>
       </c>
       <c r="E42" s="42" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F42" s="42" t="s">
+        <v>353</v>
+      </c>
+      <c r="G42" s="42" t="s">
         <v>354</v>
-      </c>
-      <c r="G42" s="42" t="s">
-        <v>355</v>
       </c>
       <c r="H42" s="43" t="s">
         <v>56</v>
       </c>
       <c r="I42" s="42" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J42" s="42"/>
       <c r="K42" s="42" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L42" s="35" t="s">
         <v>36</v>
@@ -10770,13 +10792,14 @@
       <c r="M42" s="37"/>
       <c r="N42" s="36"/>
       <c r="O42" s="43" t="s">
-        <v>765</v>
+        <v>714</v>
       </c>
       <c r="P42" s="42" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q42" s="43"/>
+    </row>
+    <row r="43" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="41">
         <v>3</v>
       </c>
@@ -10787,23 +10810,23 @@
         <v>3</v>
       </c>
       <c r="E43" s="42" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F43" s="42" t="s">
+        <v>357</v>
+      </c>
+      <c r="G43" s="42" t="s">
         <v>358</v>
-      </c>
-      <c r="G43" s="42" t="s">
-        <v>359</v>
       </c>
       <c r="H43" s="43" t="s">
         <v>26</v>
       </c>
       <c r="I43" s="42" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J43" s="42"/>
       <c r="K43" s="42" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="L43" s="43" t="s">
         <v>36</v>
@@ -10811,13 +10834,14 @@
       <c r="M43" s="37"/>
       <c r="N43" s="36"/>
       <c r="O43" s="43" t="s">
-        <v>643</v>
+        <v>625</v>
       </c>
       <c r="P43" s="42" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q43" s="43"/>
+    </row>
+    <row r="44" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="str">
         <f t="array" aca="1" ref="A44" ca="1">44:50</f>
         <v/>
@@ -10832,25 +10856,25 @@
         <v>4</v>
       </c>
       <c r="E44" s="42" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F44" s="42" t="s">
+        <v>361</v>
+      </c>
+      <c r="G44" s="42" t="s">
         <v>362</v>
-      </c>
-      <c r="G44" s="42" t="s">
-        <v>363</v>
       </c>
       <c r="H44" s="43" t="s">
         <v>86</v>
       </c>
       <c r="I44" s="42" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J44" s="42" t="s">
         <v>83</v>
       </c>
       <c r="K44" s="42" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="L44" s="43" t="s">
         <v>36</v>
@@ -10858,13 +10882,14 @@
       <c r="M44" s="37"/>
       <c r="N44" s="36"/>
       <c r="O44" s="43" t="s">
-        <v>644</v>
+        <v>626</v>
       </c>
       <c r="P44" s="42" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q44" s="43"/>
+    </row>
+    <row r="45" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="57">
         <v>3</v>
       </c>
@@ -10875,23 +10900,23 @@
         <v>5</v>
       </c>
       <c r="E45" s="42" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F45" s="42" t="s">
+        <v>365</v>
+      </c>
+      <c r="G45" s="42" t="s">
         <v>366</v>
-      </c>
-      <c r="G45" s="42" t="s">
-        <v>367</v>
       </c>
       <c r="H45" s="42" t="s">
         <v>56</v>
       </c>
       <c r="I45" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="J45" s="42"/>
       <c r="K45" s="42" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="L45" s="43" t="s">
         <v>36</v>
@@ -10899,13 +10924,14 @@
       <c r="M45" s="37"/>
       <c r="N45" s="36"/>
       <c r="O45" s="42" t="s">
-        <v>645</v>
+        <v>627</v>
       </c>
       <c r="P45" s="40" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q45" s="43"/>
+    </row>
+    <row r="46" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="57">
         <v>3</v>
       </c>
@@ -10916,23 +10942,23 @@
         <v>6</v>
       </c>
       <c r="E46" s="42" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F46" s="42" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G46" s="42" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H46" s="42" t="s">
         <v>56</v>
       </c>
       <c r="I46" s="42" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="J46" s="42"/>
       <c r="K46" s="42" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L46" s="43" t="s">
         <v>36</v>
@@ -10940,13 +10966,14 @@
       <c r="M46" s="37"/>
       <c r="N46" s="36"/>
       <c r="O46" s="42" t="s">
-        <v>766</v>
+        <v>715</v>
       </c>
       <c r="P46" s="42" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q46" s="43"/>
+    </row>
+    <row r="47" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="57">
         <v>3</v>
       </c>
@@ -10957,25 +10984,25 @@
         <v>7</v>
       </c>
       <c r="E47" s="42" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F47" s="42" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G47" s="42" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H47" s="42" t="s">
         <v>56</v>
       </c>
       <c r="I47" s="42" t="s">
+        <v>373</v>
+      </c>
+      <c r="J47" s="42" t="s">
         <v>374</v>
       </c>
-      <c r="J47" s="42" t="s">
+      <c r="K47" s="42" t="s">
         <v>375</v>
-      </c>
-      <c r="K47" s="42" t="s">
-        <v>376</v>
       </c>
       <c r="L47" s="43" t="s">
         <v>36</v>
@@ -10983,13 +11010,14 @@
       <c r="M47" s="37"/>
       <c r="N47" s="36"/>
       <c r="O47" s="42" t="s">
-        <v>646</v>
+        <v>628</v>
       </c>
       <c r="P47" s="40" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q47" s="43"/>
+    </row>
+    <row r="48" spans="1:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="14">
         <v>3</v>
       </c>
@@ -11000,23 +11028,23 @@
         <v>1</v>
       </c>
       <c r="E48" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="G48" s="19" t="s">
         <v>377</v>
-      </c>
-      <c r="F48" s="19" t="s">
-        <v>329</v>
-      </c>
-      <c r="G48" s="19" t="s">
-        <v>378</v>
       </c>
       <c r="H48" s="20" t="s">
         <v>56</v>
       </c>
       <c r="I48" s="19" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="J48" s="19"/>
       <c r="K48" s="19" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="L48" s="20" t="s">
         <v>36</v>
@@ -11024,13 +11052,14 @@
       <c r="M48" s="20"/>
       <c r="N48" s="36"/>
       <c r="O48" s="20" t="s">
-        <v>647</v>
+        <v>629</v>
       </c>
       <c r="P48" s="19" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="49" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q48" s="43"/>
+    </row>
+    <row r="49" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="14">
         <v>3</v>
       </c>
@@ -11041,23 +11070,23 @@
         <v>2</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H49" s="20" t="s">
         <v>56</v>
       </c>
       <c r="I49" s="19" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J49" s="19"/>
       <c r="K49" s="19" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="L49" s="26" t="s">
         <v>36</v>
@@ -11065,13 +11094,14 @@
       <c r="M49" s="20"/>
       <c r="N49" s="36"/>
       <c r="O49" s="20" t="s">
-        <v>767</v>
+        <v>716</v>
       </c>
       <c r="P49" s="19" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="50" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q49" s="43"/>
+    </row>
+    <row r="50" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="14">
         <v>3</v>
       </c>
@@ -11082,25 +11112,25 @@
         <v>3</v>
       </c>
       <c r="E50" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H50" s="20" t="s">
         <v>81</v>
       </c>
       <c r="I50" s="19" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J50" s="19" t="s">
         <v>83</v>
       </c>
       <c r="K50" s="60" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L50" s="26" t="s">
         <v>36</v>
@@ -11108,13 +11138,14 @@
       <c r="M50" s="20"/>
       <c r="N50" s="36"/>
       <c r="O50" s="20" t="s">
-        <v>768</v>
+        <v>717</v>
       </c>
       <c r="P50" s="55" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="51" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q50" s="43"/>
+    </row>
+    <row r="51" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="41">
         <v>3</v>
       </c>
@@ -11125,23 +11156,23 @@
         <v>4</v>
       </c>
       <c r="E51" s="42" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F51" s="42" t="s">
+        <v>386</v>
+      </c>
+      <c r="G51" s="42" t="s">
         <v>387</v>
-      </c>
-      <c r="G51" s="42" t="s">
-        <v>388</v>
       </c>
       <c r="H51" s="43" t="s">
         <v>56</v>
       </c>
       <c r="I51" s="42" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="J51" s="42"/>
       <c r="K51" s="42" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L51" s="35" t="s">
         <v>36</v>
@@ -11149,13 +11180,14 @@
       <c r="M51" s="37"/>
       <c r="N51" s="36"/>
       <c r="O51" s="43" t="s">
-        <v>769</v>
+        <v>718</v>
       </c>
       <c r="P51" s="42" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="52" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q51" s="43"/>
+    </row>
+    <row r="52" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="41">
         <v>3</v>
       </c>
@@ -11166,13 +11198,13 @@
         <v>5</v>
       </c>
       <c r="E52" s="42" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F52" s="42" t="s">
+        <v>390</v>
+      </c>
+      <c r="G52" s="42" t="s">
         <v>391</v>
-      </c>
-      <c r="G52" s="42" t="s">
-        <v>392</v>
       </c>
       <c r="H52" s="43" t="s">
         <v>56</v>
@@ -11182,7 +11214,7 @@
       </c>
       <c r="J52" s="42"/>
       <c r="K52" s="42" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L52" s="43" t="s">
         <v>36</v>
@@ -11190,13 +11222,14 @@
       <c r="M52" s="37"/>
       <c r="N52" s="36"/>
       <c r="O52" s="43" t="s">
-        <v>717</v>
+        <v>666</v>
       </c>
       <c r="P52" s="42" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="53" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q52" s="43"/>
+    </row>
+    <row r="53" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="41">
         <v>3</v>
       </c>
@@ -11207,23 +11240,23 @@
         <v>1</v>
       </c>
       <c r="E53" s="42" t="s">
+        <v>393</v>
+      </c>
+      <c r="F53" s="42" t="s">
         <v>394</v>
       </c>
-      <c r="F53" s="42" t="s">
+      <c r="G53" s="42" t="s">
         <v>395</v>
-      </c>
-      <c r="G53" s="42" t="s">
-        <v>396</v>
       </c>
       <c r="H53" s="43" t="s">
         <v>56</v>
       </c>
       <c r="I53" s="42" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J53" s="42"/>
       <c r="K53" s="42" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L53" s="43" t="s">
         <v>36</v>
@@ -11231,13 +11264,14 @@
       <c r="M53" s="37"/>
       <c r="N53" s="36"/>
       <c r="O53" s="43" t="s">
-        <v>718</v>
+        <v>667</v>
       </c>
       <c r="P53" s="42" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="54" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q53" s="43"/>
+    </row>
+    <row r="54" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="41">
         <v>3</v>
       </c>
@@ -11248,23 +11282,23 @@
         <v>2</v>
       </c>
       <c r="E54" s="42" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F54" s="42" t="s">
+        <v>398</v>
+      </c>
+      <c r="G54" s="42" t="s">
         <v>399</v>
-      </c>
-      <c r="G54" s="42" t="s">
-        <v>400</v>
       </c>
       <c r="H54" s="43" t="s">
         <v>56</v>
       </c>
       <c r="I54" s="42" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="J54" s="42"/>
       <c r="K54" s="42" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="L54" s="35" t="s">
         <v>36</v>
@@ -11272,13 +11306,14 @@
       <c r="M54" s="37"/>
       <c r="N54" s="36"/>
       <c r="O54" s="43" t="s">
-        <v>770</v>
+        <v>719</v>
       </c>
       <c r="P54" s="42" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="55" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q54" s="43"/>
+    </row>
+    <row r="55" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="41">
         <v>3</v>
       </c>
@@ -11289,23 +11324,23 @@
         <v>1</v>
       </c>
       <c r="E55" s="42" t="s">
+        <v>402</v>
+      </c>
+      <c r="F55" s="42" t="s">
         <v>403</v>
       </c>
-      <c r="F55" s="42" t="s">
+      <c r="G55" s="42" t="s">
         <v>404</v>
-      </c>
-      <c r="G55" s="42" t="s">
-        <v>405</v>
       </c>
       <c r="H55" s="43" t="s">
         <v>56</v>
       </c>
       <c r="I55" s="42" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J55" s="42"/>
       <c r="K55" s="42" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="L55" s="35" t="s">
         <v>36</v>
@@ -11313,13 +11348,14 @@
       <c r="M55" s="37"/>
       <c r="N55" s="36"/>
       <c r="O55" s="43" t="s">
-        <v>771</v>
+        <v>720</v>
       </c>
       <c r="P55" s="42" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="56" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q55" s="43"/>
+    </row>
+    <row r="56" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="41">
         <v>3</v>
       </c>
@@ -11330,25 +11366,25 @@
         <v>2</v>
       </c>
       <c r="E56" s="42" t="s">
+        <v>402</v>
+      </c>
+      <c r="F56" s="42" t="s">
         <v>403</v>
       </c>
-      <c r="F56" s="42" t="s">
-        <v>404</v>
-      </c>
       <c r="G56" s="42" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H56" s="43" t="s">
         <v>86</v>
       </c>
       <c r="I56" s="42" t="s">
+        <v>408</v>
+      </c>
+      <c r="J56" s="42" t="s">
+        <v>277</v>
+      </c>
+      <c r="K56" s="42" t="s">
         <v>409</v>
-      </c>
-      <c r="J56" s="42" t="s">
-        <v>278</v>
-      </c>
-      <c r="K56" s="42" t="s">
-        <v>410</v>
       </c>
       <c r="L56" s="35" t="s">
         <v>36</v>
@@ -11356,13 +11392,14 @@
       <c r="M56" s="37"/>
       <c r="N56" s="36"/>
       <c r="O56" s="38" t="s">
-        <v>772</v>
+        <v>721</v>
       </c>
       <c r="P56" s="55" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="57" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q56" s="43"/>
+    </row>
+    <row r="57" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="41">
         <v>3</v>
       </c>
@@ -11373,13 +11410,13 @@
         <v>3</v>
       </c>
       <c r="E57" s="42" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F57" s="42" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="G57" s="42" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H57" s="43" t="s">
         <v>56</v>
@@ -11389,7 +11426,7 @@
       </c>
       <c r="J57" s="42"/>
       <c r="K57" s="42" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="L57" s="43" t="s">
         <v>36</v>
@@ -11397,13 +11434,14 @@
       <c r="M57" s="37"/>
       <c r="N57" s="36"/>
       <c r="O57" s="43" t="s">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="P57" s="42" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="58" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q57" s="43"/>
+    </row>
+    <row r="58" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="41">
         <v>3</v>
       </c>
@@ -11414,23 +11452,23 @@
         <v>1</v>
       </c>
       <c r="E58" s="42" t="s">
+        <v>413</v>
+      </c>
+      <c r="F58" s="42" t="s">
+        <v>414</v>
+      </c>
+      <c r="G58" s="42" t="s">
         <v>415</v>
-      </c>
-      <c r="F58" s="42" t="s">
-        <v>416</v>
-      </c>
-      <c r="G58" s="42" t="s">
-        <v>417</v>
       </c>
       <c r="H58" s="43" t="s">
         <v>56</v>
       </c>
       <c r="I58" s="42" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="J58" s="42"/>
       <c r="K58" s="42" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="L58" s="43" t="s">
         <v>36</v>
@@ -11438,13 +11476,14 @@
       <c r="M58" s="37"/>
       <c r="N58" s="36"/>
       <c r="O58" s="43" t="s">
-        <v>719</v>
+        <v>668</v>
       </c>
       <c r="P58" s="42" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="59" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q58" s="43"/>
+    </row>
+    <row r="59" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="41">
         <v>3</v>
       </c>
@@ -11455,10 +11494,10 @@
         <v>2</v>
       </c>
       <c r="E59" s="42" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F59" s="42" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="G59" s="42" t="s">
         <v>209</v>
@@ -11473,7 +11512,7 @@
         <v>222</v>
       </c>
       <c r="K59" s="42" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L59" s="43" t="s">
         <v>36</v>
@@ -11481,13 +11520,14 @@
       <c r="M59" s="37"/>
       <c r="N59" s="36"/>
       <c r="O59" s="43" t="s">
-        <v>720</v>
+        <v>669</v>
       </c>
       <c r="P59" s="42" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="60" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q59" s="43"/>
+    </row>
+    <row r="60" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="41">
         <v>3</v>
       </c>
@@ -11498,13 +11538,13 @@
         <v>3</v>
       </c>
       <c r="E60" s="42" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F60" s="42" t="s">
+        <v>418</v>
+      </c>
+      <c r="G60" s="42" t="s">
         <v>420</v>
-      </c>
-      <c r="G60" s="42" t="s">
-        <v>422</v>
       </c>
       <c r="H60" s="43" t="s">
         <v>56</v>
@@ -11513,10 +11553,10 @@
         <v>253</v>
       </c>
       <c r="J60" s="42" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="K60" s="42" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L60" s="43" t="s">
         <v>36</v>
@@ -11524,13 +11564,14 @@
       <c r="M60" s="37"/>
       <c r="N60" s="36"/>
       <c r="O60" s="43" t="s">
-        <v>721</v>
+        <v>670</v>
       </c>
       <c r="P60" s="42" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="61" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="Q60" s="43"/>
+    </row>
+    <row r="61" spans="2:17" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="41">
         <v>3</v>
       </c>
@@ -11541,23 +11582,23 @@
         <v>4</v>
       </c>
       <c r="E61" s="42" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F61" s="42" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="G61" s="42" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H61" s="43" t="s">
         <v>26</v>
       </c>
       <c r="I61" s="42" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="J61" s="42"/>
       <c r="K61" s="42" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="L61" s="35" t="s">
         <v>36</v>
@@ -11565,11 +11606,12 @@
       <c r="M61" s="37"/>
       <c r="N61" s="36"/>
       <c r="O61" s="43" t="s">
-        <v>773</v>
+        <v>722</v>
       </c>
       <c r="P61" s="42" t="s">
         <v>37</v>
       </c>
+      <c r="Q61" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -11605,8 +11647,9 @@
     <col min="10" max="10" width="42.75" style="4" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="123.75" style="4" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="8.6640625" style="4" customWidth="1"/>
-    <col min="16" max="16" width="7.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.6640625" style="4" customWidth="1"/>
+    <col min="15" max="15" width="38.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.58203125" style="4" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="8.6640625" style="4" customWidth="1"/>
     <col min="19" max="16384" width="8.6640625" style="4"/>
   </cols>
@@ -11620,17 +11663,17 @@
       <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
@@ -11644,38 +11687,38 @@
       <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="61" t="s">
+      <c r="C5" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="65"/>
-      <c r="L7" s="63" t="s">
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="65"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="66"/>
+      <c r="O7" s="66"/>
+      <c r="P7" s="67"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B8" s="10" t="s">
@@ -11761,10 +11804,10 @@
       <c r="M9" s="37"/>
       <c r="N9" s="36"/>
       <c r="O9" s="20" t="s">
-        <v>654</v>
+        <v>631</v>
       </c>
       <c r="P9" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -11802,7 +11845,7 @@
       <c r="M10" s="37"/>
       <c r="N10" s="36"/>
       <c r="O10" s="20" t="s">
-        <v>774</v>
+        <v>723</v>
       </c>
       <c r="P10" s="19" t="s">
         <v>37</v>
@@ -11845,10 +11888,10 @@
       <c r="M11" s="37"/>
       <c r="N11" s="36"/>
       <c r="O11" s="20" t="s">
-        <v>655</v>
+        <v>632</v>
       </c>
       <c r="P11" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -11886,7 +11929,7 @@
       <c r="M12" s="37"/>
       <c r="N12" s="36"/>
       <c r="O12" s="20" t="s">
-        <v>775</v>
+        <v>724</v>
       </c>
       <c r="P12" s="19" t="s">
         <v>37</v>
@@ -11927,7 +11970,7 @@
       <c r="M13" s="37"/>
       <c r="N13" s="36"/>
       <c r="O13" s="20" t="s">
-        <v>776</v>
+        <v>725</v>
       </c>
       <c r="P13" s="19" t="s">
         <v>37</v>
@@ -11970,10 +12013,10 @@
       <c r="M14" s="37"/>
       <c r="N14" s="36"/>
       <c r="O14" s="20" t="s">
-        <v>722</v>
+        <v>671</v>
       </c>
       <c r="P14" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12013,7 +12056,7 @@
       <c r="M15" s="37"/>
       <c r="N15" s="36"/>
       <c r="O15" s="20" t="s">
-        <v>777</v>
+        <v>726</v>
       </c>
       <c r="P15" s="19" t="s">
         <v>37</v>
@@ -12054,10 +12097,10 @@
       <c r="M16" s="37"/>
       <c r="N16" s="36"/>
       <c r="O16" s="20" t="s">
-        <v>657</v>
+        <v>633</v>
       </c>
       <c r="P16" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12095,7 +12138,7 @@
       <c r="M17" s="37"/>
       <c r="N17" s="36"/>
       <c r="O17" s="20" t="s">
-        <v>778</v>
+        <v>727</v>
       </c>
       <c r="P17" s="19" t="s">
         <v>37</v>
@@ -12136,7 +12179,7 @@
       <c r="M18" s="37"/>
       <c r="N18" s="36"/>
       <c r="O18" s="20" t="s">
-        <v>779</v>
+        <v>728</v>
       </c>
       <c r="P18" s="19" t="s">
         <v>37</v>
@@ -12177,10 +12220,10 @@
       <c r="M19" s="37"/>
       <c r="N19" s="36"/>
       <c r="O19" s="20" t="s">
-        <v>658</v>
+        <v>634</v>
       </c>
       <c r="P19" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="20" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12220,10 +12263,10 @@
       <c r="M20" s="37"/>
       <c r="N20" s="36"/>
       <c r="O20" s="20" t="s">
-        <v>723</v>
+        <v>672</v>
       </c>
       <c r="P20" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="21" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12263,10 +12306,10 @@
       <c r="M21" s="37"/>
       <c r="N21" s="36"/>
       <c r="O21" s="20" t="s">
-        <v>724</v>
+        <v>673</v>
       </c>
       <c r="P21" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="22" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12306,10 +12349,10 @@
       <c r="M22" s="37"/>
       <c r="N22" s="36"/>
       <c r="O22" s="20" t="s">
-        <v>661</v>
+        <v>635</v>
       </c>
       <c r="P22" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="23" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12349,7 +12392,7 @@
       <c r="M23" s="37"/>
       <c r="N23" s="36"/>
       <c r="O23" s="43" t="s">
-        <v>780</v>
+        <v>729</v>
       </c>
       <c r="P23" s="42" t="s">
         <v>37</v>
@@ -12392,10 +12435,10 @@
       <c r="M24" s="37"/>
       <c r="N24" s="36"/>
       <c r="O24" s="43" t="s">
-        <v>725</v>
+        <v>674</v>
       </c>
       <c r="P24" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="25" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12433,10 +12476,10 @@
       <c r="M25" s="37"/>
       <c r="N25" s="36"/>
       <c r="O25" s="43" t="s">
-        <v>726</v>
+        <v>675</v>
       </c>
       <c r="P25" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="26" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12474,7 +12517,7 @@
       <c r="M26" s="37"/>
       <c r="N26" s="36"/>
       <c r="O26" s="43" t="s">
-        <v>781</v>
+        <v>730</v>
       </c>
       <c r="P26" s="42" t="s">
         <v>37</v>
@@ -12515,10 +12558,10 @@
       <c r="M27" s="37"/>
       <c r="N27" s="36"/>
       <c r="O27" s="43" t="s">
-        <v>727</v>
+        <v>676</v>
       </c>
       <c r="P27" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="28" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12556,10 +12599,10 @@
       <c r="M28" s="37"/>
       <c r="N28" s="36"/>
       <c r="O28" s="43" t="s">
-        <v>665</v>
+        <v>636</v>
       </c>
       <c r="P28" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="29" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12597,10 +12640,10 @@
       <c r="M29" s="37"/>
       <c r="N29" s="36"/>
       <c r="O29" s="43" t="s">
-        <v>666</v>
+        <v>637</v>
       </c>
       <c r="P29" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="30" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12638,10 +12681,10 @@
       <c r="M30" s="37"/>
       <c r="N30" s="36"/>
       <c r="O30" s="43" t="s">
-        <v>667</v>
+        <v>638</v>
       </c>
       <c r="P30" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="31" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12679,10 +12722,10 @@
       <c r="M31" s="37"/>
       <c r="N31" s="36"/>
       <c r="O31" s="43" t="s">
-        <v>728</v>
+        <v>677</v>
       </c>
       <c r="P31" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="32" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12720,10 +12763,10 @@
       <c r="M32" s="37"/>
       <c r="N32" s="36"/>
       <c r="O32" s="43" t="s">
-        <v>669</v>
+        <v>639</v>
       </c>
       <c r="P32" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12761,10 +12804,10 @@
       <c r="M33" s="37"/>
       <c r="N33" s="36"/>
       <c r="O33" s="43" t="s">
-        <v>670</v>
+        <v>640</v>
       </c>
       <c r="P33" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12804,10 +12847,10 @@
       <c r="M34" s="37"/>
       <c r="N34" s="36"/>
       <c r="O34" s="43" t="s">
-        <v>671</v>
+        <v>641</v>
       </c>
       <c r="P34" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12845,10 +12888,10 @@
       <c r="M35" s="37"/>
       <c r="N35" s="36"/>
       <c r="O35" s="45" t="s">
-        <v>729</v>
+        <v>678</v>
       </c>
       <c r="P35" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12886,10 +12929,10 @@
       <c r="M36" s="37"/>
       <c r="N36" s="36"/>
       <c r="O36" s="59" t="s">
-        <v>673</v>
+        <v>642</v>
       </c>
       <c r="P36" s="40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
   </sheetData>
@@ -12926,85 +12969,86 @@
     <col min="10" max="10" width="6.9140625" style="4" customWidth="1"/>
     <col min="11" max="11" width="90.33203125" style="4" customWidth="1"/>
     <col min="12" max="12" width="9" style="4" customWidth="1"/>
-    <col min="13" max="15" width="8.6640625" style="4" customWidth="1"/>
-    <col min="16" max="16" width="7.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.6640625" style="4" customWidth="1"/>
+    <col min="15" max="15" width="71.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.58203125" style="4" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="8.6640625" style="4" customWidth="1"/>
     <col min="19" max="16384" width="8.6640625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="67" t="s">
-        <v>428</v>
-      </c>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
+      <c r="C3" s="74" t="s">
+        <v>426</v>
+      </c>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="67" t="s">
-        <v>429</v>
-      </c>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
+      <c r="C4" s="74" t="s">
+        <v>427</v>
+      </c>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63"/>
     </row>
     <row r="5" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="61" t="s">
-        <v>430</v>
-      </c>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
+      <c r="C5" s="73" t="s">
+        <v>428</v>
+      </c>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="65"/>
-      <c r="L7" s="63" t="s">
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="65"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="66"/>
+      <c r="O7" s="66"/>
+      <c r="P7" s="67"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B8" s="10" t="s">
@@ -13064,23 +13108,23 @@
         <v>1</v>
       </c>
       <c r="E9" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>430</v>
+      </c>
+      <c r="G9" s="23" t="s">
         <v>431</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>432</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>433</v>
       </c>
       <c r="H9" s="24" t="s">
         <v>26</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J9" s="23"/>
       <c r="K9" s="50" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L9" s="26" t="s">
         <v>36</v>
@@ -13088,10 +13132,10 @@
       <c r="M9" s="37"/>
       <c r="N9" s="36"/>
       <c r="O9" s="20" t="s">
-        <v>674</v>
+        <v>643</v>
       </c>
       <c r="P9" s="52" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13105,23 +13149,23 @@
         <v>2</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H10" s="24" t="s">
         <v>56</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="J10" s="23"/>
       <c r="K10" s="25" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="L10" s="26" t="s">
         <v>36</v>
@@ -13129,10 +13173,10 @@
       <c r="M10" s="37"/>
       <c r="N10" s="36"/>
       <c r="O10" s="20" t="s">
-        <v>675</v>
+        <v>644</v>
       </c>
       <c r="P10" s="52" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13146,23 +13190,23 @@
         <v>3</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H11" s="24" t="s">
         <v>56</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="J11" s="23"/>
       <c r="K11" s="25" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="L11" s="26" t="s">
         <v>36</v>
@@ -13170,10 +13214,10 @@
       <c r="M11" s="37"/>
       <c r="N11" s="36"/>
       <c r="O11" s="20" t="s">
-        <v>676</v>
+        <v>645</v>
       </c>
       <c r="P11" s="52" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13187,7 +13231,7 @@
         <v>4</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F12" s="23" t="s">
         <v>24</v>
@@ -13203,7 +13247,7 @@
       </c>
       <c r="J12" s="23"/>
       <c r="K12" s="25" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="L12" s="26" t="s">
         <v>36</v>
@@ -13211,10 +13255,10 @@
       <c r="M12" s="37"/>
       <c r="N12" s="36"/>
       <c r="O12" s="20" t="s">
-        <v>677</v>
+        <v>646</v>
       </c>
       <c r="P12" s="52" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13228,7 +13272,7 @@
         <v>5</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F13" s="23" t="s">
         <v>240</v>
@@ -13240,11 +13284,11 @@
         <v>56</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="J13" s="23"/>
       <c r="K13" s="25" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="L13" s="26" t="s">
         <v>36</v>
@@ -13252,10 +13296,10 @@
       <c r="M13" s="37"/>
       <c r="N13" s="36"/>
       <c r="O13" s="20" t="s">
-        <v>730</v>
+        <v>679</v>
       </c>
       <c r="P13" s="52" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13269,23 +13313,23 @@
         <v>6</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F14" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="G14" s="23" t="s">
         <v>296</v>
-      </c>
-      <c r="G14" s="23" t="s">
-        <v>297</v>
       </c>
       <c r="H14" s="24" t="s">
         <v>56</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J14" s="23"/>
       <c r="K14" s="25" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="L14" s="26" t="s">
         <v>36</v>
@@ -13293,10 +13337,10 @@
       <c r="M14" s="37"/>
       <c r="N14" s="36"/>
       <c r="O14" s="20" t="s">
-        <v>679</v>
+        <v>647</v>
       </c>
       <c r="P14" s="52" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13310,23 +13354,23 @@
         <v>7</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H15" s="24" t="s">
         <v>26</v>
       </c>
       <c r="I15" s="25" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="J15" s="23"/>
       <c r="K15" s="25" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="L15" s="26" t="s">
         <v>36</v>
@@ -13334,10 +13378,10 @@
       <c r="M15" s="37"/>
       <c r="N15" s="36"/>
       <c r="O15" s="20" t="s">
-        <v>731</v>
+        <v>680</v>
       </c>
       <c r="P15" s="52" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13351,23 +13395,23 @@
         <v>1</v>
       </c>
       <c r="E16" s="23" t="s">
+        <v>448</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>449</v>
+      </c>
+      <c r="G16" s="23" t="s">
         <v>450</v>
-      </c>
-      <c r="F16" s="23" t="s">
-        <v>451</v>
-      </c>
-      <c r="G16" s="23" t="s">
-        <v>452</v>
       </c>
       <c r="H16" s="24" t="s">
         <v>56</v>
       </c>
       <c r="I16" s="25" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J16" s="23"/>
       <c r="K16" s="25" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="L16" s="26" t="s">
         <v>36</v>
@@ -13375,10 +13419,10 @@
       <c r="M16" s="37"/>
       <c r="N16" s="36"/>
       <c r="O16" s="20" t="s">
-        <v>732</v>
+        <v>681</v>
       </c>
       <c r="P16" s="52" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13392,23 +13436,23 @@
         <v>2</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="H17" s="24" t="s">
         <v>56</v>
       </c>
       <c r="I17" s="25" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="J17" s="23"/>
       <c r="K17" s="25" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L17" s="26" t="s">
         <v>36</v>
@@ -13416,10 +13460,10 @@
       <c r="M17" s="37"/>
       <c r="N17" s="36"/>
       <c r="O17" s="20" t="s">
-        <v>733</v>
+        <v>682</v>
       </c>
       <c r="P17" s="52" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13433,23 +13477,23 @@
         <v>3</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F18" s="30" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G18" s="30" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H18" s="31" t="s">
         <v>26</v>
       </c>
       <c r="I18" s="32" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J18" s="30"/>
       <c r="K18" s="32" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L18" s="26" t="s">
         <v>36</v>
@@ -13499,85 +13543,85 @@
     <col min="11" max="11" width="90.9140625" style="4" customWidth="1"/>
     <col min="12" max="12" width="9" style="4" customWidth="1"/>
     <col min="13" max="14" width="8.6640625" style="4" customWidth="1"/>
-    <col min="15" max="15" width="39" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="37.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.58203125" style="4" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="8.6640625" style="4" customWidth="1"/>
     <col min="19" max="16384" width="8.6640625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="67" t="s">
-        <v>464</v>
-      </c>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
+      <c r="C3" s="74" t="s">
+        <v>462</v>
+      </c>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="67" t="s">
-        <v>465</v>
-      </c>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
+      <c r="C4" s="74" t="s">
+        <v>463</v>
+      </c>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63"/>
     </row>
     <row r="5" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="61" t="s">
-        <v>466</v>
-      </c>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
+      <c r="C5" s="73" t="s">
+        <v>464</v>
+      </c>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="65"/>
-      <c r="L7" s="63" t="s">
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="65"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="66"/>
+      <c r="O7" s="66"/>
+      <c r="P7" s="67"/>
     </row>
     <row r="8" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="10" t="s">
@@ -13637,23 +13681,23 @@
         <v>1</v>
       </c>
       <c r="E9" s="23" t="s">
+        <v>465</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>466</v>
+      </c>
+      <c r="G9" s="23" t="s">
         <v>467</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>468</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>469</v>
       </c>
       <c r="H9" s="24" t="s">
         <v>56</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="J9" s="23"/>
       <c r="K9" s="25" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="L9" s="26" t="s">
         <v>36</v>
@@ -13661,10 +13705,10 @@
       <c r="M9" s="37"/>
       <c r="N9" s="36"/>
       <c r="O9" s="20" t="s">
-        <v>683</v>
+        <v>648</v>
       </c>
       <c r="P9" s="51" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13678,25 +13722,25 @@
         <v>2</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="H10" s="24" t="s">
         <v>86</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="J10" s="23" t="s">
         <v>83</v>
       </c>
       <c r="K10" s="25" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L10" s="35" t="s">
         <v>36</v>
@@ -13704,10 +13748,10 @@
       <c r="M10" s="37"/>
       <c r="N10" s="36"/>
       <c r="O10" s="43" t="s">
-        <v>782</v>
-      </c>
-      <c r="P10" s="75" t="s">
-        <v>604</v>
+        <v>731</v>
+      </c>
+      <c r="P10" s="61" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13721,23 +13765,23 @@
         <v>3</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="H11" s="24" t="s">
         <v>26</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="J11" s="23"/>
       <c r="K11" s="25" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="L11" s="35" t="s">
         <v>36</v>
@@ -13745,10 +13789,10 @@
       <c r="M11" s="37"/>
       <c r="N11" s="36"/>
       <c r="O11" s="43" t="s">
-        <v>783</v>
-      </c>
-      <c r="P11" s="75" t="s">
-        <v>604</v>
+        <v>732</v>
+      </c>
+      <c r="P11" s="61" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13762,23 +13806,23 @@
         <v>4</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="H12" s="24" t="s">
         <v>56</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="J12" s="23"/>
       <c r="K12" s="25" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="L12" s="26" t="s">
         <v>36</v>
@@ -13786,10 +13830,10 @@
       <c r="M12" s="37"/>
       <c r="N12" s="36"/>
       <c r="O12" s="20" t="s">
-        <v>734</v>
+        <v>683</v>
       </c>
       <c r="P12" s="51" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13803,25 +13847,25 @@
         <v>5</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H13" s="24" t="s">
         <v>86</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="J13" s="23" t="s">
         <v>83</v>
       </c>
       <c r="K13" s="25" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="L13" s="35" t="s">
         <v>36</v>
@@ -13829,10 +13873,10 @@
       <c r="M13" s="37"/>
       <c r="N13" s="36"/>
       <c r="O13" s="43" t="s">
-        <v>784</v>
-      </c>
-      <c r="P13" s="75" t="s">
-        <v>604</v>
+        <v>733</v>
+      </c>
+      <c r="P13" s="61" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13846,10 +13890,10 @@
         <v>6</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G14" s="23" t="s">
         <v>161</v>
@@ -13858,11 +13902,11 @@
         <v>26</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J14" s="23"/>
       <c r="K14" s="25" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="L14" s="35" t="s">
         <v>36</v>
@@ -13870,10 +13914,10 @@
       <c r="M14" s="37"/>
       <c r="N14" s="36"/>
       <c r="O14" s="43" t="s">
-        <v>785</v>
-      </c>
-      <c r="P14" s="75" t="s">
-        <v>604</v>
+        <v>734</v>
+      </c>
+      <c r="P14" s="61" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13887,23 +13931,23 @@
         <v>7</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="H15" s="24" t="s">
         <v>56</v>
       </c>
       <c r="I15" s="25" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="J15" s="23"/>
       <c r="K15" s="25" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="L15" s="26" t="s">
         <v>36</v>
@@ -13911,10 +13955,10 @@
       <c r="M15" s="37"/>
       <c r="N15" s="36"/>
       <c r="O15" s="20" t="s">
-        <v>685</v>
+        <v>649</v>
       </c>
       <c r="P15" s="51" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13928,23 +13972,23 @@
         <v>8</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H16" s="24" t="s">
         <v>56</v>
       </c>
       <c r="I16" s="25" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="J16" s="23"/>
       <c r="K16" s="25" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="L16" s="35" t="s">
         <v>36</v>
@@ -13952,10 +13996,10 @@
       <c r="M16" s="37"/>
       <c r="N16" s="36"/>
       <c r="O16" s="43" t="s">
-        <v>786</v>
-      </c>
-      <c r="P16" s="75" t="s">
-        <v>604</v>
+        <v>735</v>
+      </c>
+      <c r="P16" s="61" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13969,23 +14013,23 @@
         <v>1</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="H17" s="24" t="s">
         <v>56</v>
       </c>
       <c r="I17" s="25" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="J17" s="23"/>
       <c r="K17" s="25" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="L17" s="26" t="s">
         <v>36</v>
@@ -13993,10 +14037,10 @@
       <c r="M17" s="37"/>
       <c r="N17" s="36"/>
       <c r="O17" s="20" t="s">
-        <v>735</v>
+        <v>684</v>
       </c>
       <c r="P17" s="51" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14010,23 +14054,23 @@
         <v>2</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="H18" s="24" t="s">
         <v>26</v>
       </c>
       <c r="I18" s="25" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="J18" s="23"/>
       <c r="K18" s="25" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="L18" s="26" t="s">
         <v>36</v>
@@ -14034,10 +14078,10 @@
       <c r="M18" s="37"/>
       <c r="N18" s="36"/>
       <c r="O18" s="20" t="s">
-        <v>736</v>
+        <v>685</v>
       </c>
       <c r="P18" s="51" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="19" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14051,23 +14095,23 @@
         <v>3</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="H19" s="24" t="s">
         <v>56</v>
       </c>
       <c r="I19" s="25" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J19" s="23"/>
       <c r="K19" s="25" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="L19" s="26" t="s">
         <v>36</v>
@@ -14075,10 +14119,10 @@
       <c r="M19" s="37"/>
       <c r="N19" s="36"/>
       <c r="O19" s="20" t="s">
-        <v>688</v>
+        <v>650</v>
       </c>
       <c r="P19" s="51" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="20" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14092,23 +14136,23 @@
         <v>1</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="H20" s="24" t="s">
         <v>26</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="J20" s="23"/>
       <c r="K20" s="25" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="L20" s="26" t="s">
         <v>36</v>
@@ -14116,10 +14160,10 @@
       <c r="M20" s="37"/>
       <c r="N20" s="36"/>
       <c r="O20" s="20" t="s">
-        <v>737</v>
+        <v>686</v>
       </c>
       <c r="P20" s="51" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="21" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14133,23 +14177,23 @@
         <v>2</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H21" s="24" t="s">
         <v>26</v>
       </c>
       <c r="I21" s="25" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="J21" s="23"/>
       <c r="K21" s="25" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="L21" s="26" t="s">
         <v>36</v>
@@ -14157,10 +14201,10 @@
       <c r="M21" s="37"/>
       <c r="N21" s="36"/>
       <c r="O21" s="20" t="s">
-        <v>738</v>
+        <v>687</v>
       </c>
       <c r="P21" s="51" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="22" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14174,25 +14218,25 @@
         <v>3</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="H22" s="24" t="s">
         <v>86</v>
       </c>
       <c r="I22" s="25" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="J22" s="23" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K22" s="25" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="L22" s="35" t="s">
         <v>36</v>
@@ -14200,7 +14244,7 @@
       <c r="M22" s="37"/>
       <c r="N22" s="36"/>
       <c r="O22" s="20" t="s">
-        <v>787</v>
+        <v>736</v>
       </c>
       <c r="P22" s="22" t="s">
         <v>37</v>
@@ -14217,25 +14261,25 @@
         <v>4</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="H23" s="24" t="s">
         <v>86</v>
       </c>
       <c r="I23" s="25" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="J23" s="23" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K23" s="25" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="L23" s="35" t="s">
         <v>36</v>
@@ -14243,7 +14287,7 @@
       <c r="M23" s="37"/>
       <c r="N23" s="36"/>
       <c r="O23" s="20" t="s">
-        <v>788</v>
+        <v>737</v>
       </c>
       <c r="P23" s="22" t="s">
         <v>37</v>
@@ -14260,25 +14304,25 @@
         <v>5</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="H24" s="24" t="s">
         <v>86</v>
       </c>
       <c r="I24" s="25" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="J24" s="23" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K24" s="25" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="L24" s="35" t="s">
         <v>36</v>
@@ -14286,7 +14330,7 @@
       <c r="M24" s="37"/>
       <c r="N24" s="36"/>
       <c r="O24" s="20" t="s">
-        <v>789</v>
+        <v>738</v>
       </c>
       <c r="P24" s="22" t="s">
         <v>37</v>
@@ -14303,25 +14347,25 @@
         <v>6</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="H25" s="24" t="s">
         <v>86</v>
       </c>
       <c r="I25" s="25" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="J25" s="23" t="s">
         <v>83</v>
       </c>
       <c r="K25" s="25" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="L25" s="26" t="s">
         <v>36</v>
@@ -14329,10 +14373,10 @@
       <c r="M25" s="37"/>
       <c r="N25" s="36"/>
       <c r="O25" s="20" t="s">
-        <v>691</v>
+        <v>651</v>
       </c>
       <c r="P25" s="51" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="26" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14346,25 +14390,25 @@
         <v>7</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="H26" s="24" t="s">
         <v>96</v>
       </c>
       <c r="I26" s="25" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="J26" s="23" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="K26" s="25" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="L26" s="35" t="s">
         <v>36</v>
@@ -14372,7 +14416,7 @@
       <c r="M26" s="37"/>
       <c r="N26" s="36"/>
       <c r="O26" s="20" t="s">
-        <v>790</v>
+        <v>739</v>
       </c>
       <c r="P26" s="22" t="s">
         <v>37</v>
@@ -14389,23 +14433,23 @@
         <v>8</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="H27" s="24" t="s">
         <v>96</v>
       </c>
       <c r="I27" s="25" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="J27" s="23"/>
       <c r="K27" s="25" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="L27" s="26" t="s">
         <v>36</v>
@@ -14413,7 +14457,7 @@
       <c r="M27" s="37"/>
       <c r="N27" s="36"/>
       <c r="O27" s="20" t="s">
-        <v>791</v>
+        <v>740</v>
       </c>
       <c r="P27" s="51" t="s">
         <v>32</v>
@@ -14430,23 +14474,23 @@
         <v>1</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H28" s="24" t="s">
         <v>26</v>
       </c>
       <c r="I28" s="25" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="J28" s="23"/>
       <c r="K28" s="25" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="L28" s="35" t="s">
         <v>36</v>
@@ -14454,7 +14498,7 @@
       <c r="M28" s="37"/>
       <c r="N28" s="36"/>
       <c r="O28" s="20" t="s">
-        <v>792</v>
+        <v>741</v>
       </c>
       <c r="P28" s="22" t="s">
         <v>37</v>
@@ -14471,23 +14515,23 @@
         <v>2</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="G29" s="23" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="H29" s="24" t="s">
         <v>26</v>
       </c>
       <c r="I29" s="25" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="J29" s="23"/>
       <c r="K29" s="25" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L29" s="35" t="s">
         <v>36</v>
@@ -14495,7 +14539,7 @@
       <c r="M29" s="37"/>
       <c r="N29" s="36"/>
       <c r="O29" s="20" t="s">
-        <v>793</v>
+        <v>742</v>
       </c>
       <c r="P29" s="22" t="s">
         <v>37</v>
@@ -14512,23 +14556,23 @@
         <v>3</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="G30" s="23" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="H30" s="24" t="s">
         <v>26</v>
       </c>
       <c r="I30" s="25" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="J30" s="23"/>
       <c r="K30" s="25" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="L30" s="35" t="s">
         <v>36</v>
@@ -14536,7 +14580,7 @@
       <c r="M30" s="37"/>
       <c r="N30" s="36"/>
       <c r="O30" s="20" t="s">
-        <v>794</v>
+        <v>743</v>
       </c>
       <c r="P30" s="22" t="s">
         <v>37</v>
@@ -14553,23 +14597,23 @@
         <v>4</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F31" s="30" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="G31" s="30" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="H31" s="31" t="s">
         <v>26</v>
       </c>
       <c r="I31" s="32" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="J31" s="30"/>
       <c r="K31" s="32" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="L31" s="26" t="s">
         <v>36</v>
@@ -14577,10 +14621,10 @@
       <c r="M31" s="37"/>
       <c r="N31" s="36"/>
       <c r="O31" s="34" t="s">
-        <v>739</v>
+        <v>688</v>
       </c>
       <c r="P31" s="52" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
   </sheetData>
@@ -14619,85 +14663,85 @@
     <col min="11" max="11" width="93.58203125" style="4" customWidth="1"/>
     <col min="12" max="12" width="9" style="4" customWidth="1"/>
     <col min="13" max="14" width="8.6640625" style="4" customWidth="1"/>
-    <col min="15" max="15" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.9140625" style="4" customWidth="1"/>
+    <col min="15" max="15" width="97.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.58203125" style="4" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="8.6640625" style="4" customWidth="1"/>
     <col min="19" max="16384" width="8.6640625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="67" t="s">
-        <v>541</v>
-      </c>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
+      <c r="C3" s="74" t="s">
+        <v>538</v>
+      </c>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="67" t="s">
-        <v>542</v>
-      </c>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
+      <c r="C4" s="74" t="s">
+        <v>539</v>
+      </c>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63"/>
     </row>
     <row r="5" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="74" t="s">
-        <v>543</v>
-      </c>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
+      <c r="C5" s="75" t="s">
+        <v>540</v>
+      </c>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="65"/>
-      <c r="L7" s="63" t="s">
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="65"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="66"/>
+      <c r="O7" s="66"/>
+      <c r="P7" s="67"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B8" s="10" t="s">
@@ -14742,8 +14786,8 @@
       <c r="O8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="P8" s="13" t="s">
-        <v>5</v>
+      <c r="P8" s="76" t="s">
+        <v>746</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14757,25 +14801,25 @@
         <v>1</v>
       </c>
       <c r="E9" s="23" t="s">
+        <v>541</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>542</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>543</v>
+      </c>
+      <c r="H9" s="24" t="s">
         <v>544</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="I9" s="25" t="s">
         <v>545</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>546</v>
-      </c>
-      <c r="H9" s="24" t="s">
-        <v>547</v>
-      </c>
-      <c r="I9" s="25" t="s">
-        <v>548</v>
       </c>
       <c r="J9" s="23" t="s">
         <v>40</v>
       </c>
       <c r="K9" s="25" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="L9" s="26" t="s">
         <v>36</v>
@@ -14783,10 +14827,10 @@
       <c r="M9" s="37"/>
       <c r="N9" s="36"/>
       <c r="O9" s="20" t="s">
-        <v>740</v>
+        <v>689</v>
       </c>
       <c r="P9" s="51" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14800,25 +14844,25 @@
         <v>1</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="F10" s="23" t="s">
         <v>236</v>
       </c>
       <c r="G10" s="23" t="s">
+        <v>548</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>544</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>549</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>550</v>
+      </c>
+      <c r="K10" s="25" t="s">
         <v>551</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>547</v>
-      </c>
-      <c r="I10" s="25" t="s">
-        <v>552</v>
-      </c>
-      <c r="J10" s="23" t="s">
-        <v>553</v>
-      </c>
-      <c r="K10" s="25" t="s">
-        <v>554</v>
       </c>
       <c r="L10" s="38" t="s">
         <v>36</v>
@@ -14826,7 +14870,7 @@
       <c r="M10" s="37"/>
       <c r="N10" s="36"/>
       <c r="O10" s="43" t="s">
-        <v>795</v>
+        <v>744</v>
       </c>
       <c r="P10" s="22" t="s">
         <v>37</v>
@@ -14843,23 +14887,23 @@
         <v>1</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="J11" s="23"/>
       <c r="K11" s="25" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="L11" s="26" t="s">
         <v>36</v>
@@ -14867,10 +14911,10 @@
       <c r="M11" s="37"/>
       <c r="N11" s="36"/>
       <c r="O11" s="20" t="s">
-        <v>741</v>
+        <v>690</v>
       </c>
       <c r="P11" s="51" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14884,23 +14928,23 @@
         <v>1</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="F12" s="23" t="s">
         <v>191</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="J12" s="23"/>
       <c r="K12" s="25" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="L12" s="26" t="s">
         <v>36</v>
@@ -14908,10 +14952,10 @@
       <c r="M12" s="37"/>
       <c r="N12" s="36"/>
       <c r="O12" s="20" t="s">
-        <v>742</v>
+        <v>691</v>
       </c>
       <c r="P12" s="51" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14925,23 +14969,23 @@
         <v>1</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="J13" s="23"/>
       <c r="K13" s="25" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="L13" s="26" t="s">
         <v>36</v>
@@ -14949,10 +14993,10 @@
       <c r="M13" s="37"/>
       <c r="N13" s="36"/>
       <c r="O13" s="20" t="s">
-        <v>743</v>
+        <v>692</v>
       </c>
       <c r="P13" s="51" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -14966,23 +15010,23 @@
         <v>1</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="J14" s="23"/>
       <c r="K14" s="25" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="L14" s="26" t="s">
         <v>36</v>
@@ -14990,10 +15034,10 @@
       <c r="M14" s="37"/>
       <c r="N14" s="36"/>
       <c r="O14" s="20" t="s">
-        <v>744</v>
+        <v>693</v>
       </c>
       <c r="P14" s="51" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -15007,23 +15051,23 @@
         <v>1</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="I15" s="25" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="J15" s="23"/>
       <c r="K15" s="25" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="L15" s="26" t="s">
         <v>36</v>
@@ -15031,10 +15075,10 @@
       <c r="M15" s="37"/>
       <c r="N15" s="36"/>
       <c r="O15" s="20" t="s">
-        <v>745</v>
+        <v>694</v>
       </c>
       <c r="P15" s="51" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -15048,25 +15092,25 @@
         <v>1</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="F16" s="23" t="s">
         <v>107</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="I16" s="25" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="J16" s="23" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="K16" s="25" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="L16" s="26" t="s">
         <v>36</v>
@@ -15074,10 +15118,10 @@
       <c r="M16" s="37"/>
       <c r="N16" s="36"/>
       <c r="O16" s="20" t="s">
-        <v>746</v>
+        <v>695</v>
       </c>
       <c r="P16" s="51" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -15091,23 +15135,23 @@
         <v>1</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="I17" s="25" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="J17" s="23"/>
       <c r="K17" s="25" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="L17" s="26" t="s">
         <v>36</v>
@@ -15115,10 +15159,10 @@
       <c r="M17" s="37"/>
       <c r="N17" s="36"/>
       <c r="O17" s="20" t="s">
-        <v>747</v>
+        <v>696</v>
       </c>
       <c r="P17" s="51" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -15132,23 +15176,23 @@
         <v>1</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="I18" s="25" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="J18" s="23"/>
       <c r="K18" s="25" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="L18" s="26" t="s">
         <v>36</v>
@@ -15156,10 +15200,10 @@
       <c r="M18" s="37"/>
       <c r="N18" s="36"/>
       <c r="O18" s="20" t="s">
-        <v>748</v>
+        <v>697</v>
       </c>
       <c r="P18" s="51" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="19" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -15173,25 +15217,25 @@
         <v>1</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="I19" s="25" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="J19" s="23" t="s">
         <v>40</v>
       </c>
       <c r="K19" s="25" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="L19" s="38" t="s">
         <v>36</v>
@@ -15199,7 +15243,7 @@
       <c r="M19" s="37"/>
       <c r="N19" s="36"/>
       <c r="O19" s="43" t="s">
-        <v>796</v>
+        <v>745</v>
       </c>
       <c r="P19" s="22" t="s">
         <v>37</v>
@@ -15216,23 +15260,23 @@
         <v>1</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="G20" s="30" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="H20" s="31" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="I20" s="32" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="J20" s="30"/>
       <c r="K20" s="32" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="L20" s="33" t="s">
         <v>36</v>
@@ -15240,10 +15284,10 @@
       <c r="M20" s="53"/>
       <c r="N20" s="54"/>
       <c r="O20" s="34" t="s">
-        <v>749</v>
+        <v>698</v>
       </c>
       <c r="P20" s="52" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
   </sheetData>

--- a/docs/結合試験項目一覧.xlsx
+++ b/docs/結合試験項目一覧.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="759">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="761">
   <si>
     <t>●参加者ビュー</t>
   </si>
@@ -2342,6 +2342,12 @@
   </si>
   <si>
     <t>evidence/3-6-2_20260731_*.png（2枚）／evidence/3-6-2_20260731_applications_ev_public.csv</t>
+  </si>
+  <si>
+    <t>対象外</t>
+  </si>
+  <si>
+    <t>実装区分の一覧は画面から削除済み（F-36 廃止）。確認するものが無い。削除されたことは smoke.js が検査している</t>
   </si>
 </sst>
 </file>
@@ -13499,8 +13505,12 @@
         <v>36</v>
       </c>
       <c r="M18" s="37"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="34"/>
+      <c r="N18" s="36" t="s">
+        <v>759</v>
+      </c>
+      <c r="O18" s="34" t="s">
+        <v>760</v>
+      </c>
       <c r="P18" s="52" t="s">
         <v>32</v>
       </c>
